--- a/tables/N-Retention/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
+++ b/tables/N-Retention/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,10 +668,10 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301524983055982</v>
+        <v>0.2306347362834478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2102321700738213</v>
+        <v>0.2139717519039619</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.41245498585054</v>
       </c>
       <c r="P2" t="n">
-        <v>4.38795138658381</v>
+        <v>4.428027272095276</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9926330326554672</v>
+        <v>0.9928798272182282</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005276037209361281</v>
+        <v>0.005186910372713974</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9910499848048351</v>
+        <v>0.9921068956002747</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.006860628209600643</v>
+        <v>0.006442818869549126</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.999723928937432</v>
+        <v>0.9997455576661759</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001093268504117215</v>
+        <v>0.0001049569202043909</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9988932753648455</v>
+        <v>0.9991391223597588</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001403667237398405</v>
+        <v>0.001237984162028732</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9567661688749975</v>
+        <v>0.9558640799878323</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008847709267111415</v>
+        <v>0.008939537992363963</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7155843131930304</v>
+        <v>0.7143230577306785</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001604854604664225</v>
+        <v>0.001608409072058359</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -772,28 +772,28 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1224260723227339</v>
+        <v>0.1232120795919104</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1558349249174037</v>
+        <v>0.1574610681810748</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9898506833074057</v>
+        <v>0.9899152127727258</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9828526628219209</v>
+        <v>0.9830143494385797</v>
       </c>
       <c r="O3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.33964224043698</v>
       </c>
       <c r="P3" t="n">
-        <v>4.318374524190768</v>
+        <v>4.338782073077034</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.990556833754945</v>
+        <v>0.9906571464334931</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005909198609577241</v>
+        <v>0.005877728753378776</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.995648709630936</v>
+        <v>0.9959254163896009</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004238738012794468</v>
+        <v>0.004101749736191257</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-1.057186228100418</v>
+        <v>-1.057186228100309</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.00351221099636463</v>
+        <v>0.003512210996364536</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9822054637132546</v>
+        <v>0.9825752785922954</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.006469791739786348</v>
+        <v>0.006402209554158521</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8574974742231971</v>
+        <v>0.8570375362960841</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009155062035940416</v>
+        <v>0.009169824469328437</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3338676572530441</v>
+        <v>0.3332112990436396</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003330102340786911</v>
+        <v>0.003331742556789961</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -876,10 +876,10 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4340590818808676</v>
+        <v>0.4182134418056933</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2125962488366459</v>
+        <v>0.2208594485135457</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.293495891699291</v>
       </c>
       <c r="P4" t="n">
-        <v>4.430889526628489</v>
+        <v>4.556602342455461</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9579877946497399</v>
+        <v>0.9607964551961967</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01340824105445743</v>
+        <v>0.01295229532806168</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9753659945383404</v>
+        <v>0.9851941532454184</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01381990689240657</v>
+        <v>0.010714063731892</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9976121790701041</v>
+        <v>0.9985442196193263</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0006081474467586714</v>
+        <v>0.0004748494524258263</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.4437297938562914</v>
+        <v>0.4346038484660159</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02427450024978466</v>
+        <v>0.02447280906145297</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9753269659781754</v>
+        <v>0.969599831718468</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006515445618055883</v>
+        <v>0.007232206854740965</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.3754367660374518</v>
+        <v>0.3487408446412722</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.00400485731447248</v>
+        <v>0.004089552245753408</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -980,10 +980,10 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851828485504524</v>
+        <v>0.183837851295302</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2268830152812718</v>
+        <v>0.2238263143116071</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.308694500962631</v>
       </c>
       <c r="P5" t="n">
-        <v>4.405690012696408</v>
+        <v>4.348799656553713</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9975464377093314</v>
+        <v>0.9975645951211797</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002931813119983263</v>
+        <v>0.002920944638374979</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9986145844474023</v>
+        <v>0.9986341256968937</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00266598475511225</v>
+        <v>0.00264711616156805</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999962605707647</v>
+        <v>0.9999958712056961</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.191674858137712e-05</v>
+        <v>1.252179935866721e-05</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9983663489003208</v>
+        <v>0.9983410305587128</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001878857895803476</v>
+        <v>0.00189336119830271</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9739700530996925</v>
+        <v>0.9742049323665801</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005364263247220236</v>
+        <v>0.005340006390386004</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9678247657871317</v>
+        <v>0.9674414162148932</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008363421730996402</v>
+        <v>0.0008413096907191719</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1084,28 +1084,28 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1720532088902192</v>
+        <v>0.1701916451553553</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2210627535789722</v>
+        <v>0.2186875923145526</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9894088352884388</v>
+        <v>0.9892467693566445</v>
       </c>
       <c r="N6" t="n">
-        <v>0.984101258826221</v>
+        <v>0.9837898177280916</v>
       </c>
       <c r="O6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.378395834553357</v>
       </c>
       <c r="P6" t="n">
-        <v>4.466734327072568</v>
+        <v>4.391829889632508</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9770155161136699</v>
+        <v>0.9772129130450882</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009164900528508886</v>
+        <v>0.009125460349448335</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9914391054869185</v>
+        <v>0.9921267179908332</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005337068858094674</v>
+        <v>0.005118245778830672</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>-1.052399706356034</v>
+        <v>-1.052399706355871</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.00382633279519135</v>
+        <v>0.003826332795191198</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9964892448069708</v>
+        <v>0.9969519038513933</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002430209778872294</v>
+        <v>0.002264424378096487</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6735474596888713</v>
+        <v>0.6738368229955096</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0185620085610867</v>
+        <v>0.01855378017522338</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4093658803742369</v>
+        <v>0.4084380759999942</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001810968643542361</v>
+        <v>0.001812390475807902</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1188,28 +1188,28 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2350473166772497</v>
+        <v>0.2317281644358207</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1539814828010271</v>
+        <v>0.1567341053516102</v>
       </c>
       <c r="M7" t="n">
-        <v>0.161081477628093</v>
+        <v>0.1417626463179144</v>
       </c>
       <c r="N7" t="n">
-        <v>0.006431032005123458</v>
+        <v>0.005343845688049327</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.265203801522019</v>
       </c>
       <c r="P7" t="n">
-        <v>4.318568224900813</v>
+        <v>4.378363345136592</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9905548675049179</v>
+        <v>0.990775766353896</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005904932031836494</v>
+        <v>0.005835472453123137</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9924372400367846</v>
+        <v>0.9931977233845325</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006598141026371501</v>
+        <v>0.006257611256841111</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9996230737618532</v>
+        <v>0.9996502880983449</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.37597049829302e-05</v>
+        <v>8.067930722263177e-05</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9403152375436959</v>
+        <v>0.9399908492301664</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.009739284883401447</v>
+        <v>0.009765715658696992</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9926192241800675</v>
+        <v>0.9926501729215893</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002262322589158903</v>
+        <v>0.002257574471204742</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.3108777989914245</v>
+        <v>0.3080632907430052</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004382516978787864</v>
+        <v>0.004391457382657783</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1292,28 +1292,28 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.173449561258173</v>
+        <v>0.1755031604752748</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1467253069446457</v>
+        <v>0.15174576798274</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07953247023270538</v>
+        <v>0.08213333455056815</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002067820264295084</v>
+        <v>0.002204845580817327</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.444307466489452</v>
       </c>
       <c r="P8" t="n">
-        <v>4.281314621587587</v>
+        <v>4.408437917072764</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9923588343115711</v>
+        <v>0.9924101337693199</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004709205936828367</v>
+        <v>0.00469337153715132</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9917319471731856</v>
+        <v>0.9917373664197541</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00606746465093599</v>
+        <v>0.006065475883001574</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999981237584381</v>
+        <v>0.9999972574356384</v>
       </c>
       <c r="AD8" t="n">
-        <v>8.990864928101985e-06</v>
+        <v>1.087014935445824e-05</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9855776249644356</v>
+        <v>0.9856723116340524</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005946712216220853</v>
+        <v>0.00592715920908862</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9825372967651024</v>
+        <v>0.9827820190666458</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005595484680873713</v>
+        <v>0.005556138788486537</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9997092464156696</v>
+        <v>0.9996903313898945</v>
       </c>
       <c r="AM8" t="n">
-        <v>6.2287625115784e-05</v>
+        <v>6.428176996349951e-05</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1396,28 +1396,28 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2202316867728543</v>
+        <v>0.2153661717190752</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1649788097785612</v>
+        <v>0.1643420762688951</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08121075077882189</v>
+        <v>0.06232359596124581</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002013509285569959</v>
+        <v>0.001260058754466462</v>
       </c>
       <c r="O9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.234521484447876</v>
       </c>
       <c r="P9" t="n">
-        <v>4.383047537003294</v>
+        <v>4.36316595797072</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9952721720657055</v>
+        <v>0.9952343914761901</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003718711593160996</v>
+        <v>0.003733540342865374</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9956576184690364</v>
+        <v>0.9957038994260116</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004756400433028022</v>
+        <v>0.004730985756148247</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9999478768098931</v>
+        <v>0.999950481996056</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.134693167779568e-05</v>
+        <v>4.030040006622898e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9985042116667779</v>
+        <v>0.9985801129249151</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001564959468226618</v>
+        <v>0.001524736954249111</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9726784906386092</v>
+        <v>0.9720689626890463</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00623668845035141</v>
+        <v>0.006305873266220749</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9843812356730642</v>
+        <v>0.9840105961025097</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007514043554743753</v>
+        <v>0.0007602676454712302</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1500,10 +1500,10 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2213013737149055</v>
+        <v>0.2184121894741882</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1163453785616525</v>
+        <v>0.1178707377254579</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.11415328726214</v>
       </c>
       <c r="P10" t="n">
-        <v>4.177595268430974</v>
+        <v>4.23528492147312</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9928759531933805</v>
+        <v>0.9928800950808492</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005361591105884329</v>
+        <v>0.005360032277290705</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9996542285574641</v>
+        <v>0.999688863589391</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001644771785523067</v>
+        <v>0.001560222387227277</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999682095619357</v>
+        <v>0.9999699892593092</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.712726500284167e-05</v>
+        <v>4.578912425571369e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9300721428435189</v>
+        <v>0.9298620732531865</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01081269598592531</v>
+        <v>0.01082892496375592</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9741443291128398</v>
+        <v>0.9749017566791109</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002544059365951539</v>
+        <v>0.00250651898582266</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7854139595127194</v>
+        <v>0.7845764702381025</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002838606838551068</v>
+        <v>0.002844140720787344</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1604,28 +1604,28 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4160005438509808</v>
+        <v>0.4182813421933623</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3940137476416198</v>
+        <v>0.4003198085406786</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4369716633923226</v>
+        <v>0.4394594276089848</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06197208813969732</v>
+        <v>0.0636255995137141</v>
       </c>
       <c r="O11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.115746786233981</v>
       </c>
       <c r="P11" t="n">
-        <v>4.197429584833889</v>
+        <v>4.272581114654178</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9716958224021772</v>
+        <v>0.9727380326006789</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01251603654452639</v>
+        <v>0.01228344397341881</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9554068056929889</v>
+        <v>0.9571407507055467</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02640248661640634</v>
+        <v>0.025884085136523</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9996807879375696</v>
+        <v>0.9995505247519588</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0001258451109035928</v>
+        <v>0.0001493308685611915</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9349446185092131</v>
+        <v>0.9347267189029522</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00452127032654394</v>
+        <v>0.004528835876274773</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.8984848594140196</v>
+        <v>0.8975654178698704</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003580292276514656</v>
+        <v>0.003596469416381206</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9623018561357644</v>
+        <v>0.9623904796703597</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0008225334744124435</v>
+        <v>0.000821566069800697</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1708,28 +1708,28 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1394923145397872</v>
+        <v>0.1412678730771366</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1891812646947314</v>
+        <v>0.2019682868638971</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4421188299507052</v>
+        <v>0.4480098367810685</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1447696465212321</v>
+        <v>0.1546799415391678</v>
       </c>
       <c r="O12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.107460678751526</v>
       </c>
       <c r="P12" t="n">
-        <v>4.065564327332953</v>
+        <v>4.144149158510897</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9288870647492755</v>
+        <v>0.929877234201177</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02902261968716091</v>
+        <v>0.02881985736448468</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.6190431576548368</v>
+        <v>0.6293097996850736</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.06101165300808342</v>
+        <v>0.06018391770866419</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9999997346969199</v>
+        <v>0.9999990590726391</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.209601235928137e-06</v>
+        <v>2.277975897483368e-06</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.8596765503849341</v>
+        <v>0.827615163862876</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01416474213944261</v>
+        <v>0.01569976228873287</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.5940551921315753</v>
+        <v>0.6070525076138443</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002768142119461227</v>
+        <v>0.002723467197405642</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9835990257864622</v>
+        <v>0.9863797829479125</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002590661461329348</v>
+        <v>0.0002360847072940297</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1812,28 +1812,28 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.317485623382867</v>
+        <v>0.3156537929037181</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2596120006953905</v>
+        <v>0.2727234995589771</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5241971561736598</v>
+        <v>0.4871019817900795</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1654386814722002</v>
+        <v>0.1531391470086671</v>
       </c>
       <c r="O13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.29263277483161</v>
       </c>
       <c r="P13" t="n">
-        <v>4.289743397072598</v>
+        <v>4.506444969616558</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9975470990314339</v>
+        <v>0.9975793876351416</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002834214615662046</v>
+        <v>0.002815498819932141</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.7017068747748603</v>
+        <v>0.7081090287200391</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.004306082870088854</v>
+        <v>0.004259622302234096</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9774430053787569</v>
+        <v>0.9751358007314065</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001150195480218944</v>
+        <v>0.0001207586578590338</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6866602027683086</v>
+        <v>0.6862439360528628</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004002852906659816</v>
+        <v>0.004005510885978173</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.999758738159917</v>
+        <v>0.9998149681037549</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0006275208995905606</v>
+        <v>0.0005495499547685099</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.949606273516487</v>
+        <v>0.9502040943750705</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002278523510057355</v>
+        <v>0.002264968124186884</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1916,28 +1916,28 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2018962647297078</v>
+        <v>0.2068452432900554</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3445901067467204</v>
+        <v>0.3493200022684957</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6074553914254088</v>
+        <v>0.6195338597130369</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5887499323815822</v>
+        <v>0.597394995122581</v>
       </c>
       <c r="O14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.429062464935388</v>
       </c>
       <c r="P14" t="n">
-        <v>4.322730248072627</v>
+        <v>4.375434175866124</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9725325313172768</v>
+        <v>0.9725129024218548</v>
       </c>
       <c r="R14" t="n">
-        <v>0.009869712226386553</v>
+        <v>0.009873238160145889</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9062577761162526</v>
+        <v>0.9061809377475295</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01522302810242839</v>
+        <v>0.01522926580940525</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.9614806109789689</v>
+        <v>0.9614806109789746</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0009625122855061611</v>
+        <v>0.000962512285506089</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9739992378510279</v>
+        <v>0.9736439467993553</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.006968863237001917</v>
+        <v>0.007016315186863646</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.6025866988824895</v>
+        <v>0.6035602401048978</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01424542599324055</v>
+        <v>0.01422796682262591</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.2580709454736888</v>
+        <v>0.2602242228314636</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001700548766256284</v>
+        <v>0.001698079248556434</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2020,10 +2020,10 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1960420645582539</v>
+        <v>0.1895470751595914</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2987234638753284</v>
+        <v>0.2933197078177879</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.12729937470144</v>
       </c>
       <c r="P15" t="n">
-        <v>4.326171788068061</v>
+        <v>4.250834185958639</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9758299264655514</v>
+        <v>0.975807779438401</v>
       </c>
       <c r="R15" t="n">
-        <v>0.008216041372647021</v>
+        <v>0.008219804688209677</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9198479839425594</v>
+        <v>0.9197776878023943</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01394063060324258</v>
+        <v>0.01394674247539276</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.5674697625966263</v>
+        <v>-0.5405604309778897</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003276117533306433</v>
+        <v>0.003247874635409145</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9499523415761748</v>
+        <v>0.9498627388268558</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.008191726342240619</v>
+        <v>0.008199056085422594</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.6580036165260398</v>
+        <v>0.656548015171428</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.006545002167554207</v>
+        <v>0.006558915762710387</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999993764978298</v>
+        <v>0.9999995770694698</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.92198706450867e-06</v>
+        <v>2.406544089539302e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5421174973423735</v>
+        <v>0.5109637156163565</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5411382860905174</v>
+        <v>0.524826409861138</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.305324632016705</v>
       </c>
       <c r="P16" t="n">
-        <v>4.711496521050512</v>
+        <v>4.498954160381471</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9745773048798684</v>
+        <v>0.9758602116143378</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009697799156589715</v>
+        <v>0.00944994150527813</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9936622043350898</v>
+        <v>0.9937953635733858</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005868584924805389</v>
+        <v>0.005806607172569121</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9551799432489315</v>
+        <v>0.9584743548070799</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004363444170341738</v>
+        <v>0.00420002056613056</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9117894692335414</v>
+        <v>0.9091355120823432</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003566147932465987</v>
+        <v>0.003619397056548504</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8337531422819788</v>
+        <v>0.8429217642719108</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01847541587163382</v>
+        <v>0.01795872530642704</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2226,28 +2226,28 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2229860026107122</v>
+        <v>0.2121923977296436</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2786106956681201</v>
+        <v>0.2664672949231575</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1729958242968503</v>
+        <v>0.1529464524077458</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02970217646913065</v>
+        <v>0.02411179959695135</v>
       </c>
       <c r="O17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.89038661935276</v>
       </c>
       <c r="P17" t="n">
-        <v>4.200285067510515</v>
+        <v>4.034503076205769</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9892394937290483</v>
+        <v>0.9892950906979096</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004815189639177017</v>
+        <v>0.00480273406151811</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9676556168106456</v>
+        <v>0.9677225250352443</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.009047565892124385</v>
+        <v>0.009038203061573959</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.6932567764300026</v>
+        <v>0.7035253385502881</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0017129080093702</v>
+        <v>0.001683993234410675</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9980155603541677</v>
+        <v>0.9979228475699531</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001204743715704034</v>
+        <v>0.001232565212302445</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>-0.1012170648849957</v>
+        <v>-0.08572685842334082</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005400330174087645</v>
+        <v>0.005362213942646315</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9944123802097745</v>
+        <v>0.9942949301299103</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0007230355977415721</v>
+        <v>0.000730595074755317</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2393672981629223</v>
+        <v>0.24258952682581</v>
       </c>
       <c r="L18" t="n">
-        <v>0.262747064399152</v>
+        <v>0.2659670730655396</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.300562681691318</v>
       </c>
       <c r="P18" t="n">
-        <v>4.250892789540532</v>
+        <v>4.300546436141598</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9827202968096395</v>
+        <v>0.9827320056158617</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006798400132103566</v>
+        <v>0.006796096428215015</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9166055080799669</v>
+        <v>0.9166678208924395</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01483000205489053</v>
+        <v>0.0148244604909142</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9877503481609227</v>
+        <v>0.9869877379734456</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0003048386530148204</v>
+        <v>0.0003141843593608251</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9954446570369417</v>
+        <v>0.9954260882605082</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.002025778400708347</v>
+        <v>0.002029903004613332</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9756112373990631</v>
+        <v>0.9756653168228163</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002627270099104056</v>
+        <v>0.002624355639990265</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9955658579341767</v>
+        <v>0.9955281379648904</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002510137965868611</v>
+        <v>0.0002520791866744827</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2434,10 +2434,10 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1872651872905624</v>
+        <v>0.1618647634163979</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2401256141083021</v>
+        <v>0.2266520304402777</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.597747250805167</v>
+        <v>4.01013022703957</v>
       </c>
       <c r="P19" t="n">
-        <v>4.655386642815689</v>
+        <v>4.378894525126992</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9879336459867739</v>
+        <v>0.9880043984450059</v>
       </c>
       <c r="R19" t="n">
-        <v>0.007739487098694492</v>
+        <v>0.007716763050895845</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.622721673326854</v>
+        <v>0.6261862384808998</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.009145703645993698</v>
+        <v>0.009103614075635955</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.04774448265522935</v>
+        <v>-0.02407581613210419</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003049542932421957</v>
+        <v>0.003014901415834792</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7662419785943408</v>
+        <v>0.7666055143525095</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01364623034304395</v>
+        <v>0.01363561504322373</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8474625418062679</v>
+        <v>0.8511452672964697</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004505893059207675</v>
+        <v>0.004451167641450874</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9962539860275457</v>
+        <v>0.9960400729158702</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001789431217902211</v>
+        <v>0.0001839813951152159</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2538,10 +2538,10 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2655681489740055</v>
+        <v>0.270337140109575</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3008207078222745</v>
+        <v>0.306474044431695</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.622332151259288</v>
       </c>
       <c r="P20" t="n">
-        <v>4.510600408283932</v>
+        <v>4.589270355176144</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9762103648614167</v>
+        <v>0.9761708549923681</v>
       </c>
       <c r="R20" t="n">
-        <v>0.00905531570841459</v>
+        <v>0.009062832131237158</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8803079551071945</v>
+        <v>0.8787468901710448</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01007862075707494</v>
+        <v>0.01014413226734182</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8280280070612986</v>
+        <v>0.8252929229952188</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.00282968168037066</v>
+        <v>0.002852094885726183</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9728822971329379</v>
+        <v>0.9733227802322076</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.00439421516037828</v>
+        <v>0.004358380596989807</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7919072746511157</v>
+        <v>0.7922480009568221</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01675178518364538</v>
+        <v>0.01673806506865897</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4672811318595945</v>
+        <v>0.4651814554570201</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006903509277416156</v>
+        <v>0.0006917100762121532</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1248690725745343</v>
+        <v>0.1205682193591666</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1431679535447021</v>
+        <v>0.1424141123167814</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.116445283604787</v>
       </c>
       <c r="P21" t="n">
-        <v>4.339785910113336</v>
+        <v>4.120922169320235</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.874488071611137</v>
+        <v>0.8640998623691123</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02305595960368221</v>
+        <v>0.02399112699908035</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9517999569680639</v>
+        <v>0.9562227590827219</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008624054597936286</v>
+        <v>0.008218867471995793</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9953852012563222</v>
+        <v>0.9945489868070292</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002242398755649204</v>
+        <v>0.002437109695667851</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-3.602913264123998</v>
+        <v>-4.073243951911832</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04699213855396434</v>
+        <v>0.04933460861720036</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.273237339816524</v>
+        <v>-0.2741046317810907</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01922881058578043</v>
+        <v>0.01923535852204688</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.555802247166186</v>
+        <v>0.552524461766148</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0006895316720808289</v>
+        <v>0.0006920710621326452</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2746,28 +2746,28 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3240298729858146</v>
+        <v>0.3067591657776431</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3339506061964759</v>
+        <v>0.3269574459399416</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1110986438552031</v>
+        <v>0.07207061126445224</v>
       </c>
       <c r="N22" t="n">
-        <v>0.01480992491781281</v>
+        <v>0.007562505240968262</v>
       </c>
       <c r="O22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.138954932523397</v>
       </c>
       <c r="P22" t="n">
-        <v>4.39488133873598</v>
+        <v>4.309908832298483</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9817449022471363</v>
+        <v>0.9818437140563175</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006829957719496613</v>
+        <v>0.006811447925080798</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8904408657285628</v>
+        <v>0.8917331967060136</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009758283063385486</v>
+        <v>0.009700559253528265</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9267719071812226</v>
+        <v>0.9298890734304983</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001499887372921202</v>
+        <v>0.001467616685381284</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3521865892261739</v>
+        <v>0.3544965210653147</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01110916072251942</v>
+        <v>0.01108933686586766</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9588934468584147</v>
+        <v>0.9569179653026106</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002903100555956566</v>
+        <v>0.002972040005860154</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7803364458917907</v>
+        <v>0.7808100365588875</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001981518856127497</v>
+        <v>0.001979381644072312</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2850,28 +2850,28 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3048705428481599</v>
+        <v>0.2857369714597892</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2933312738658588</v>
+        <v>0.2866934206494559</v>
       </c>
       <c r="M23" t="n">
-        <v>0.295827482771332</v>
+        <v>0.2605396243220668</v>
       </c>
       <c r="N23" t="n">
-        <v>0.05594010856002745</v>
+        <v>0.04730702081302307</v>
       </c>
       <c r="O23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.863757349446638</v>
       </c>
       <c r="P23" t="n">
-        <v>4.198878022090678</v>
+        <v>4.119433225787591</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9814915506545245</v>
+        <v>0.9816360588359564</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01018529404479345</v>
+        <v>0.01014545433388278</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8960088430030584</v>
+        <v>0.896802137294897</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02260744124312633</v>
+        <v>0.02252104597331774</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.6534991810856483</v>
+        <v>-0.5891385377725162</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.0012279676704327</v>
+        <v>0.001203831826219805</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.978557129247418</v>
+        <v>0.9789667274992588</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002466392134714494</v>
+        <v>0.002442722243105279</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9997600584147843</v>
+        <v>0.9907196448458544</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.514899428875064e-05</v>
+        <v>0.0001564048293483361</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.999398885475004</v>
+        <v>0.9993945602018566</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0001142239002674151</v>
+        <v>0.000114634108312047</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2954,10 +2954,10 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3751494643248936</v>
+        <v>0.3899491530645845</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4425806758753214</v>
+        <v>0.4733730306956111</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.330915049849626</v>
       </c>
       <c r="P24" t="n">
-        <v>4.128186592578381</v>
+        <v>4.386274849460652</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9945537678825086</v>
+        <v>0.9946398898416594</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004382629081729144</v>
+        <v>0.004347839465796365</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.999566133501516</v>
+        <v>0.9995320269809053</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.001671477852291758</v>
+        <v>0.001735933064475865</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9599406914513025</v>
+        <v>0.9572293091745959</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003160098487630775</v>
+        <v>0.003265292013805306</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8840507310778634</v>
+        <v>0.8876443399180077</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.008391554935814817</v>
+        <v>0.008260491953133008</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9992557077524161</v>
+        <v>0.9998960457205744</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0001843230634473673</v>
+        <v>6.888570670350077e-05</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2172140991091026</v>
+        <v>0.2158934749426978</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2292204832758638</v>
+        <v>0.2288284659952428</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.311008836928643</v>
       </c>
       <c r="P25" t="n">
-        <v>4.343850982506539</v>
+        <v>4.340714662475478</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9845613365229</v>
+        <v>0.9846063623632936</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02060671386574989</v>
+        <v>0.02057664286603977</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1707408655114686</v>
+        <v>-0.1671293684514767</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03983670982053102</v>
+        <v>0.03977521829467955</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5378816542604836</v>
+        <v>0.5396289014954936</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008625667927485663</v>
+        <v>0.0008609345866895428</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.8919468721132126</v>
+        <v>0.891680711966246</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01133202658393375</v>
+        <v>0.0113459747168711</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.6600602660440471</v>
+        <v>0.6599589366982943</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002857253765045187</v>
+        <v>0.002857679578878689</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9805947811455071</v>
+        <v>0.9812367192575829</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002281907238891866</v>
+        <v>0.002243846283148287</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9738345626271234</v>
+        <v>0.9706334713670406</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001010321433814268</v>
+        <v>0.001070340289688523</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02312743380997206</v>
+        <v>-0.02254649128062214</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003349470278728779</v>
+        <v>0.003348519211457814</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3168,10 +3168,10 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3294247814180385</v>
+        <v>0.319605401855295</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3144083729271104</v>
+        <v>0.3068276294006985</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.221808346553291</v>
       </c>
       <c r="P26" t="n">
-        <v>4.388941288746611</v>
+        <v>4.299156165421864</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9809766417136976</v>
+        <v>0.9811515580484123</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02119975890442162</v>
+        <v>0.0211020698554135</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3069129235847603</v>
+        <v>0.3137369123292557</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04088343214703179</v>
+        <v>0.04068166947802393</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3233253272397167</v>
+        <v>-0.3054739183158917</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008064236697790454</v>
+        <v>0.000800965949823007</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9476874383665761</v>
+        <v>0.9472173182030595</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01234825436216102</v>
+        <v>0.01240361562780566</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.2493011061677128</v>
+        <v>-0.238405234485211</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003832457425096157</v>
+        <v>0.003815708295467274</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9123927413903575</v>
+        <v>0.9126467246914984</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003961899192943252</v>
+        <v>0.00395615202870477</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9824082716162537</v>
+        <v>0.9823701306252515</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001128272964912834</v>
+        <v>0.001129495418667469</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.467047362484114</v>
+        <v>0.4634037693418636</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001011612130225969</v>
+        <v>0.001015064242503256</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3280,10 +3280,10 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2426473726089903</v>
+        <v>0.2452896402637705</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3113334292707128</v>
+        <v>0.3101309629421319</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.171003209011483</v>
       </c>
       <c r="P27" t="n">
-        <v>4.155660784901317</v>
+        <v>4.149301127182595</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9963887362304005</v>
+        <v>0.9964015897120301</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009753438309825248</v>
+        <v>0.00973606525155314</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.900394769765877</v>
+        <v>0.9008776392057188</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01656770704296327</v>
+        <v>0.01652749952230578</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.6636502133531045</v>
+        <v>0.6590828011894931</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006499314706697847</v>
+        <v>0.0006543294148296382</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9233151698620651</v>
+        <v>0.9235728252701322</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01174259819647834</v>
+        <v>0.0117228544635618</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9310416949635936</v>
+        <v>0.9298164463228387</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0009602667592423297</v>
+        <v>0.0009687601899360537</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.9021873947343422</v>
+        <v>0.9014770953294831</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.008736723922287188</v>
+        <v>0.008768388881661288</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.6228850456888233</v>
+        <v>0.625950300483904</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003308433505979403</v>
+        <v>0.003294960315557175</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4381201234247535</v>
+        <v>0.4377434781411439</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004880754679166372</v>
+        <v>0.004882390264761079</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3392,10 +3392,10 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4028027310904022</v>
+        <v>0.3983433844077345</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3915066830577246</v>
+        <v>0.4052908569416904</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.109024519998804</v>
       </c>
       <c r="P28" t="n">
-        <v>4.17001940002624</v>
+        <v>4.290280345970089</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9411493485178295</v>
+        <v>0.9429312535765202</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02526267253496361</v>
+        <v>0.02487727583761871</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.5891214422499327</v>
+        <v>0.6035707802519461</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05252391622264473</v>
+        <v>0.05159209813149845</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.8219395114126131</v>
+        <v>0.8422662425991353</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.005046854955511628</v>
+        <v>0.004750062976255752</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5279641332489722</v>
+        <v>0.522085242763175</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01148505175260088</v>
+        <v>0.01155634975994717</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4046802938876518</v>
+        <v>0.4026817583656148</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01676625728247006</v>
+        <v>0.01679437653107811</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9887789673220276</v>
+        <v>0.9893995304586048</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003667246272611076</v>
+        <v>0.0003564398182264405</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3498,10 +3498,10 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.512131704883432</v>
+        <v>0.5340055862294603</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3414401435392915</v>
+        <v>0.3537813427846556</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.257333241600258</v>
       </c>
       <c r="P29" t="n">
-        <v>4.104754557777886</v>
+        <v>4.212624139423042</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9471058787975153</v>
+        <v>0.9513053116423515</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01484129408719915</v>
+        <v>0.01423996307855831</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7678186752560218</v>
+        <v>0.7860660146354843</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03139968479525145</v>
+        <v>0.03014057525530507</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9275470979874074</v>
+        <v>0.9301519174395692</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009323243727810465</v>
+        <v>0.009154115532989501</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6243769738548826</v>
+        <v>0.6855713830580368</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008662529083873403</v>
+        <v>0.00792555410044218</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9923307451840083</v>
+        <v>0.9907652346544472</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.002275430111427265</v>
+        <v>0.00249689252581046</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9071803652831271</v>
+        <v>0.9080252017825244</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001818236037785225</v>
+        <v>0.001809942407007152</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3604,28 +3604,28 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4907901004864869</v>
+        <v>0.5325113215269579</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3861863894114256</v>
+        <v>0.4062765831598397</v>
       </c>
       <c r="M30" t="n">
-        <v>0.06587546321210769</v>
+        <v>0.1181929947757944</v>
       </c>
       <c r="N30" t="n">
-        <v>0.001976335938976019</v>
+        <v>0.005458007710319151</v>
       </c>
       <c r="O30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.515704212940665</v>
       </c>
       <c r="P30" t="n">
-        <v>4.107137158359654</v>
+        <v>4.31409232898503</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9720538630470253</v>
+        <v>0.9728781180226278</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01377928809167478</v>
+        <v>0.01357456119407297</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8597912012743175</v>
+        <v>0.8627321261241871</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02550536742593428</v>
+        <v>0.02523645817753093</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9988030783568658</v>
+        <v>0.9990233779304795</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0001559068700171495</v>
+        <v>0.0001408301558090145</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>0.02275341372772111</v>
+        <v>0.09867875886578292</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01336886571649236</v>
+        <v>0.01283903205214726</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8427566458217426</v>
+        <v>0.840592691875899</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.00829966108844237</v>
+        <v>0.008356575147451356</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4843351004210512</v>
+        <v>0.4864491043803056</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001931279563380735</v>
+        <v>0.001927316790650695</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3710,10 +3710,10 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5036033975236921</v>
+        <v>0.4901448304506785</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4306286015147403</v>
+        <v>0.4307390966259112</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.249026147841872</v>
       </c>
       <c r="P31" t="n">
-        <v>4.404571549628286</v>
+        <v>4.408534161760072</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.985805980365061</v>
+        <v>0.9859673610844005</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007780532430995916</v>
+        <v>0.007736175110345476</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9432709376871298</v>
+        <v>0.9455034404592624</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01272154897674931</v>
+        <v>0.01246871603733657</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8995517533593955</v>
+        <v>0.8982920028100511</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007716004897599537</v>
+        <v>0.007764238466934059</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>0.1285860101680375</v>
+        <v>0.1038843795345048</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.008488034635804543</v>
+        <v>0.008607497454891309</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9694162314579174</v>
+        <v>0.968753259220473</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002744196984223618</v>
+        <v>0.002773780852337383</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05945394724080455</v>
+        <v>0.05028342485048809</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004076238269457521</v>
+        <v>0.004096062156338966</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3816,10 +3816,10 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4586807473470598</v>
+        <v>0.5003028185540506</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3967883814998332</v>
+        <v>0.4274308509856222</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.530139452862152</v>
       </c>
       <c r="P32" t="n">
-        <v>4.108510545515194</v>
+        <v>4.426225949150417</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9792549254251126</v>
+        <v>0.9797467054705858</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01386920112993602</v>
+        <v>0.01370382441077479</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.891185877823179</v>
+        <v>0.9022466566662836</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009408018494476865</v>
+        <v>0.008917052857534644</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.226406781486729</v>
+        <v>0.2271863060437095</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01745877835284029</v>
+        <v>0.01744997981613056</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.6402773739714953</v>
+        <v>-0.5308905534094654</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01628735773514245</v>
+        <v>0.01573490262979552</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2372324392141342</v>
+        <v>0.2304359754871046</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01809619145659767</v>
+        <v>0.01817663362550467</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.07910699016666978</v>
+        <v>0.0737867155481069</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004877751953142133</v>
+        <v>0.004891821777688604</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3920,10 +3920,10 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2751054178962024</v>
+        <v>0.2845720576653915</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2953103347016996</v>
+        <v>0.309385953827798</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.300519149462805</v>
       </c>
       <c r="P33" t="n">
-        <v>4.148037589858846</v>
+        <v>4.268926255577062</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9654287632841264</v>
+        <v>0.9652966305421057</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005898727853838917</v>
+        <v>0.005909989698078893</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9309403751890426</v>
+        <v>0.930858457618045</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01061915981576181</v>
+        <v>0.0106254560993633</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.09764992118680038</v>
+        <v>0.1217477747227871</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006096050935522517</v>
+        <v>0.006014100569510049</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8713131497358847</v>
+        <v>0.8596925635331981</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004278925237478026</v>
+        <v>0.004467946433780625</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7720987787496164</v>
+        <v>0.7777413070225867</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002265194757533726</v>
+        <v>0.002236977416460872</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3798157655786184</v>
+        <v>0.3825736347723331</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007786210821800718</v>
+        <v>0.0007768879458624871</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4024,10 +4024,10 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5165578838213738</v>
+        <v>0.5337173211659239</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4381577432281694</v>
+        <v>0.4597037194164731</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.254011730907492</v>
       </c>
       <c r="P34" t="n">
-        <v>4.126564361733847</v>
+        <v>4.289569332936278</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8919539226295353</v>
+        <v>0.884790543811793</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02292221682132348</v>
+        <v>0.02366988660435418</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8230729551224383</v>
+        <v>0.8106991218732373</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.05035338778649552</v>
+        <v>0.0520844278401577</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9911263759144169</v>
+        <v>0.9906423490482188</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.002228307286102835</v>
+        <v>0.00228827379840637</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6922909200676028</v>
+        <v>0.7096376348842103</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004270445178423217</v>
+        <v>0.004148328667916342</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4393357697059542</v>
+        <v>0.4581789492888363</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.008311718532057401</v>
+        <v>0.008170851925575123</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.3322155998597326</v>
+        <v>0.3318348959972142</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0007944031990052936</v>
+        <v>0.0007946296113580733</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4130,10 +4130,10 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3001566209783726</v>
+        <v>0.3017567405934108</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2368757567215266</v>
+        <v>0.2447387101592386</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.047146068348874</v>
       </c>
       <c r="P35" t="n">
-        <v>4.028629229484289</v>
+        <v>4.155126683074013</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9967818954357702</v>
+        <v>0.9967899421229967</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005651374112290477</v>
+        <v>0.005644304220467496</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9820723689218327</v>
+        <v>0.9820833025179087</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.007306441244895003</v>
+        <v>0.007304212900817048</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6750227800969157</v>
+        <v>0.6763340926124476</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.008513541515470648</v>
+        <v>0.00849634769774184</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7321567284353812</v>
+        <v>0.7315717490061899</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002091424257266287</v>
+        <v>0.002093706884864355</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5230971287576718</v>
+        <v>0.5251730074787959</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002344802026378294</v>
+        <v>0.002339693194615889</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4232,10 +4232,10 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4200622561347667</v>
+        <v>0.4303510992459229</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3831600102508279</v>
+        <v>0.3940041415817687</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.305403694774172</v>
       </c>
       <c r="P36" t="n">
-        <v>4.208581070838521</v>
+        <v>4.320738530966725</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9835769469014141</v>
+        <v>0.9836102967342929</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01161252434776945</v>
+        <v>0.01160072774237137</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8060266221175501</v>
+        <v>0.8065746744763604</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01914531271103744</v>
+        <v>0.01911824699751956</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3677947154154995</v>
+        <v>0.367525906756115</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.00815645596527957</v>
+        <v>0.008158189811100849</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.1010078332160818</v>
+        <v>0.1028198803448294</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01322854592546969</v>
+        <v>0.01321520718857418</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7318201298142536</v>
+        <v>0.7311364352005947</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006066798590073802</v>
+        <v>0.006074526980104867</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1612504013843504</v>
+        <v>0.1631199438672212</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004049959099786035</v>
+        <v>0.004045442975723871</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4338,10 +4338,10 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1057540787127461</v>
+        <v>0.1033156315000568</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1089937639589356</v>
+        <v>0.105989240617094</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.2322895226395</v>
       </c>
       <c r="P37" t="n">
-        <v>4.362928199445947</v>
+        <v>4.263467469259709</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9932588349070247</v>
+        <v>0.9932355178273524</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005470868182428546</v>
+        <v>0.005480321633666626</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.0299938843851475</v>
+        <v>0.03028582223180765</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004213428384632135</v>
+        <v>0.0004212794289776973</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9983167693716564</v>
+        <v>0.9983483979738434</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.001947876784427047</v>
+        <v>0.001929489290990243</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5040702741241765</v>
+        <v>-0.5024649171995881</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007765111171380051</v>
+        <v>0.007760966051537448</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9144432373190192</v>
+        <v>0.9137853380899765</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009518724186465195</v>
+        <v>0.009555251799096498</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.940203643404257</v>
+        <v>0.9403141793133138</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002193890175299171</v>
+        <v>0.002191861491347629</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999999970704111</v>
+        <v>0.9999997601921665</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.327937038481826e-08</v>
+        <v>4.82044827755296e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1483762115382365</v>
+        <v>0.1414949912042679</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1138584835256079</v>
+        <v>0.1088639589686587</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.109497407226164</v>
       </c>
       <c r="P38" t="n">
-        <v>4.354336837449976</v>
+        <v>4.195433165024799</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9538121928541338</v>
+        <v>0.9539271641807503</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01205907118288497</v>
+        <v>0.01204405302805255</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1887539275713247</v>
+        <v>0.1847479057418968</v>
       </c>
       <c r="X38" t="n">
-        <v>0.00118057454774713</v>
+        <v>0.001183485861193669</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8109250065975481</v>
+        <v>0.8115797081627778</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02097239677063583</v>
+        <v>0.02093605519128235</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3913229412018957</v>
+        <v>-0.3873194027207028</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01712024780170345</v>
+        <v>0.01709559825877765</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.966710356823042</v>
+        <v>0.9651012801458784</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004235246858030138</v>
+        <v>0.004336395720794464</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.178208910301884</v>
+        <v>-1.138275440562116</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.00487533828142523</v>
+        <v>0.004830441356116479</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999969927291992</v>
+        <v>0.999997220570763</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.950305838317476e-07</v>
+        <v>6.681830546054594e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1491847814540822</v>
+        <v>0.1514588065490762</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1317020544517115</v>
+        <v>0.1342714605126339</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.258033543989585</v>
       </c>
       <c r="P39" t="n">
-        <v>4.188954527563515</v>
+        <v>4.266349377449965</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9827741907063748</v>
+        <v>0.9827773649056697</v>
       </c>
       <c r="R39" t="n">
-        <v>0.00878505941568368</v>
+        <v>0.008784249967092275</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.882220896621827</v>
+        <v>0.8822854639021227</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01148643567358987</v>
+        <v>0.01148328677211925</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1214846240723172</v>
+        <v>0.1222420223291134</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001394463945615677</v>
+        <v>0.001393862708387718</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.06326684280318329</v>
+        <v>-0.06332093944888362</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01476954400789191</v>
+        <v>0.01476991972384337</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7528771644452634</v>
+        <v>0.7529487446492968</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005394450712619433</v>
+        <v>0.005393669392982733</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1190359810737407</v>
+        <v>-0.1190897937720492</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002182677670748964</v>
+        <v>0.002182730150903738</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4658,28 +4658,28 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3948410699014029</v>
+        <v>0.3692825186777028</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4224365810739916</v>
+        <v>0.4127346472607966</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4137099823048692</v>
+        <v>0.3771697981355325</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05653727458959169</v>
+        <v>0.05232942382546467</v>
       </c>
       <c r="O40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.29006395973414</v>
       </c>
       <c r="P40" t="n">
-        <v>4.622821004663956</v>
+        <v>4.521409058919988</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9911389106647891</v>
+        <v>0.9912030911818219</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005654362167226009</v>
+        <v>0.005633847793566522</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9650519979006618</v>
+        <v>0.965387094706591</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.01128165667236612</v>
+        <v>0.01122743965359422</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9210162554526414</v>
+        <v>0.9312082056342028</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0006393685857563706</v>
+        <v>0.0005966927393884434</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.97969587336964</v>
+        <v>0.9797130183523861</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003579113397693936</v>
+        <v>0.003577601961174649</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9983247705647424</v>
+        <v>0.9982048374156118</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.001838077585929036</v>
+        <v>0.001902736220316332</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999975944300202</v>
+        <v>0.9999999578493531</v>
       </c>
       <c r="AM40" t="n">
-        <v>9.430413274478688e-07</v>
+        <v>1.248314024826898e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4762,10 +4762,10 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2672649319402196</v>
+        <v>0.2578830227728073</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2936141599257733</v>
+        <v>0.2872185449577517</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.435303441664242</v>
       </c>
       <c r="P41" t="n">
-        <v>4.613966702450173</v>
+        <v>4.505579411018814</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9938217241621833</v>
+        <v>0.9938802513594176</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006091842314453956</v>
+        <v>0.006062919450929456</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8654570140360451</v>
+        <v>0.8651957122863032</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01068163547436106</v>
+        <v>0.01069200307598809</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.65821335590623</v>
+        <v>0.6519291125382181</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001457974443930432</v>
+        <v>0.001471316881064028</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9799417082493156</v>
+        <v>0.981326285006654</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.003797413001245291</v>
+        <v>0.003664006404089967</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9482024140822396</v>
+        <v>0.9491779253928917</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007337454498623599</v>
+        <v>0.007268032423408722</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8993246890954788</v>
+        <v>0.9001785179227288</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001034941550609193</v>
+        <v>0.00103054352839569</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4866,28 +4866,28 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3175477744289016</v>
+        <v>0.3188781726443401</v>
       </c>
       <c r="L42" t="n">
-        <v>0.430575522969117</v>
+        <v>0.437307270969239</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1069996947754496</v>
+        <v>0.1135544113824459</v>
       </c>
       <c r="N42" t="n">
-        <v>0.006097962645184027</v>
+        <v>0.00667021924092833</v>
       </c>
       <c r="O42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.54271279036458</v>
       </c>
       <c r="P42" t="n">
-        <v>4.516977101908054</v>
+        <v>4.559278581803332</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9637769742165756</v>
+        <v>0.9638135343907865</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01260351566729275</v>
+        <v>0.01259715364967972</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8197424427073532</v>
+        <v>0.8185358813445799</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02329908981227517</v>
+        <v>0.02337693646935403</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9953505463679895</v>
+        <v>0.9955745415084517</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0003644444654621443</v>
+        <v>0.0003555572468164497</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.8481459733051774</v>
+        <v>0.8525155408946281</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01137313603440585</v>
+        <v>0.01120831188960674</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9832535387553607</v>
+        <v>0.9838808844814095</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.004001916456153757</v>
+        <v>0.003926242298911063</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4968,28 +4968,28 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2502194438201192</v>
+        <v>0.2438232441219792</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3764730561912647</v>
+        <v>0.3802626956790793</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3846694687666999</v>
+        <v>0.3726292806413716</v>
       </c>
       <c r="N43" t="n">
-        <v>0.04705980641938726</v>
+        <v>0.0463039522422613</v>
       </c>
       <c r="O43" t="n">
-        <v>4.103051778684014</v>
+        <v>4.004824234178307</v>
       </c>
       <c r="P43" t="n">
-        <v>4.228902174791</v>
+        <v>4.257854625603513</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9399964652631623</v>
+        <v>0.9413958644494801</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01496716524644654</v>
+        <v>0.01479160389108287</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.8693455482657291</v>
+        <v>0.872751047624317</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03108609912761647</v>
+        <v>0.03067829571529064</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.722522040054713</v>
+        <v>0.722215283186465</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002487697592605248</v>
+        <v>0.002489072309950466</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.856987485707146</v>
+        <v>0.8578717863513283</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01198441170979404</v>
+        <v>0.01194730217261699</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.8839855571914267</v>
+        <v>0.885454150100725</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001909370376334255</v>
+        <v>0.001897246806307444</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9826404048487436</v>
+        <v>0.9831036024094448</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0005236029259486463</v>
+        <v>0.0005165701759146208</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5072,10 +5072,10 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1778728783246155</v>
+        <v>0.1750004298657557</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3409782340247858</v>
+        <v>0.3271453757894115</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.26677501303533</v>
       </c>
       <c r="P44" t="n">
-        <v>4.578197656346277</v>
+        <v>4.389336156098157</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9434428387582025</v>
+        <v>0.9436990976759149</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008100194223064095</v>
+        <v>0.008081822512133931</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9155363542052839</v>
+        <v>0.9160532059420502</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01303260108462765</v>
+        <v>0.01299266521197464</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8049811145483285</v>
+        <v>0.8046322025389985</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004897673762934648</v>
+        <v>0.004902053065829957</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9432158617603925</v>
+        <v>0.9424598499734625</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.008334447346035377</v>
+        <v>0.008389745416451655</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8662003735362926</v>
+        <v>0.8693015582673569</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.007946437495022083</v>
+        <v>0.007853807024223858</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6386839128105477</v>
+        <v>0.627820126103811</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001273165940284053</v>
+        <v>0.001292164498384604</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5176,10 +5176,10 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.399617491041528</v>
+        <v>0.3970700662958236</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3249596872346976</v>
+        <v>0.3275258470037932</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.224020019874794</v>
       </c>
       <c r="P45" t="n">
-        <v>4.339423949906405</v>
+        <v>4.375440194607536</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9687494805713318</v>
+        <v>0.9687751708200327</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008633536221117809</v>
+        <v>0.008629986787395804</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9762270971388208</v>
+        <v>0.9762472131166755</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01318771401720371</v>
+        <v>0.01318213329558572</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9228786476909019</v>
+        <v>0.9229489468869232</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007283294530264332</v>
+        <v>0.007279974266374508</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8709161898854615</v>
+        <v>0.8710034196413887</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.00853794338673057</v>
+        <v>0.008535058096236186</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9217748283863004</v>
+        <v>0.9218406137914298</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008511482131808327</v>
+        <v>0.008507902407658757</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9799925233926114</v>
+        <v>0.9800276216909577</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006210900397911031</v>
+        <v>0.000620545024227616</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5280,10 +5280,10 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4729359869420497</v>
+        <v>0.4191548341898909</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4308421582610232</v>
+        <v>0.4168763599596889</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.769550246054656</v>
       </c>
       <c r="P46" t="n">
-        <v>4.573524191133153</v>
+        <v>4.474246364770191</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9665016990216085</v>
+        <v>0.9687411047786199</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008726449747929462</v>
+        <v>0.008429717377463572</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9805865427667279</v>
+        <v>0.9825621906838121</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01074397269041094</v>
+        <v>0.01018261717193388</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9215003125481068</v>
+        <v>0.9244883895932834</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01039959817555755</v>
+        <v>0.01019974845920663</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9736598631809625</v>
+        <v>0.9761741219411049</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002656669684523781</v>
+        <v>0.002526696065791834</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8639800730225278</v>
+        <v>0.8721008938082562</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01221315986281886</v>
+        <v>0.0118429672374478</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9872533160827263</v>
+        <v>0.9873983451204669</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009751240858975513</v>
+        <v>0.0009695608398424529</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5384,10 +5384,10 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.251984504906933</v>
+        <v>0.2534470292225203</v>
       </c>
       <c r="L47" t="n">
-        <v>0.384807069729783</v>
+        <v>0.3804221654864902</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.285238971656212</v>
       </c>
       <c r="P47" t="n">
-        <v>4.397325222758508</v>
+        <v>4.355338806089541</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9501585453197885</v>
+        <v>0.9499675728583342</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008389873890057674</v>
+        <v>0.008405931838519721</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9281394194981591</v>
+        <v>0.9280134275048924</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.0147702245474781</v>
+        <v>0.01478316707485817</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8111492368536617</v>
+        <v>0.8095213335784225</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006790072266121376</v>
+        <v>0.00681927485499712</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.9153074343984091</v>
+        <v>0.9145169469472024</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.008677169484748552</v>
+        <v>0.008717570094534379</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9499897256642864</v>
+        <v>0.9505309367183397</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.003468098191338427</v>
+        <v>0.003449281269043725</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9001869576478293</v>
+        <v>0.9012792860527055</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0006035971847728758</v>
+        <v>0.000600285292119425</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5488,10 +5488,10 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1259930651411941</v>
+        <v>0.1132798991704734</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3915823744017324</v>
+        <v>0.3941761000608428</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.703826593445649</v>
       </c>
       <c r="P48" t="n">
-        <v>4.345145418865432</v>
+        <v>4.323796651864424</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9824236689627371</v>
+        <v>0.9822785264617602</v>
       </c>
       <c r="R48" t="n">
-        <v>0.006835846719772154</v>
+        <v>0.006864013349149739</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.969358872862212</v>
+        <v>0.9685191461319849</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01279963530284998</v>
+        <v>0.01297383824231126</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8624571562506164</v>
+        <v>0.8641702082448598</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006264845236928058</v>
+        <v>0.006225709681120688</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9927038433513082</v>
+        <v>0.993280752478491</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.004953444009906843</v>
+        <v>0.004753576674794105</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.9124507303954397</v>
+        <v>0.913903805183183</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002445137659202598</v>
+        <v>0.002424761510567896</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9991702163929184</v>
+        <v>0.9997081465432875</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0002230390565399479</v>
+        <v>0.0001322759577286648</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5592,28 +5592,28 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3889285704498146</v>
+        <v>0.3643052533076485</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4646794360468078</v>
+        <v>0.4619807277903906</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1387964711447663</v>
+        <v>0.08745240125860532</v>
       </c>
       <c r="N49" t="n">
-        <v>0.004660663914774201</v>
+        <v>0.002440444190641133</v>
       </c>
       <c r="O49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.05609595904365</v>
       </c>
       <c r="P49" t="n">
-        <v>4.417481325596095</v>
+        <v>4.393073580436305</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9238295949966643</v>
+        <v>0.9257488755932365</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01308182726308222</v>
+        <v>0.01291596308872166</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9160590399359168</v>
+        <v>0.9184123146157749</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01954293480444366</v>
+        <v>0.01926704551935028</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9447552401620262</v>
+        <v>0.9450798504891054</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002254007819360161</v>
+        <v>0.002247375948841617</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.6034038836835597</v>
+        <v>0.6055279028350553</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01162650869738725</v>
+        <v>0.01159533330366054</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3128384685394865</v>
+        <v>0.3337477037096268</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01821333771888276</v>
+        <v>0.01793409560041621</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.867906165924152</v>
+        <v>0.8683230939638997</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001327703028781439</v>
+        <v>0.001325606056906469</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5696,10 +5696,10 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5222632463286973</v>
+        <v>0.5041804397675377</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5295673622804894</v>
+        <v>0.527911915006419</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.245466267633814</v>
       </c>
       <c r="P50" t="n">
-        <v>4.631358351710457</v>
+        <v>4.52016536989635</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.966087730383056</v>
+        <v>0.9679338158247377</v>
       </c>
       <c r="R50" t="n">
-        <v>0.009842603193941698</v>
+        <v>0.009570953140782093</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9943927576866218</v>
+        <v>0.9948739840009695</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.006299672858289515</v>
+        <v>0.006023283624087662</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9284897254683484</v>
+        <v>0.9298759515224362</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005698026620616831</v>
+        <v>0.005642528247103462</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.883312307286294</v>
+        <v>0.903708506244548</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.003489996060662606</v>
+        <v>0.003170343885247073</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.7967289153044008</v>
+        <v>0.8068174896992218</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01809400734905745</v>
+        <v>0.0176392803456281</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5798,28 +5798,28 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5242408860059533</v>
+        <v>0.47819434822235</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4559091454132452</v>
+        <v>0.4658553747668711</v>
       </c>
       <c r="M51" t="n">
-        <v>0.185384429015224</v>
+        <v>0.1137929647244488</v>
       </c>
       <c r="N51" t="n">
-        <v>0.00370768858030448</v>
+        <v>0.002275859294488976</v>
       </c>
       <c r="O51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.863171910508307</v>
       </c>
       <c r="P51" t="n">
-        <v>4.414627870341568</v>
+        <v>4.49899044551241</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.862357343692491</v>
+        <v>0.8665655187706761</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01490013564702103</v>
+        <v>0.01467059524389295</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.8596532773809205</v>
+        <v>0.8599286568718753</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.02214825913949232</v>
+        <v>0.02212651951135165</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.6863408123982357</v>
+        <v>0.6731374583569512</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01788260617604364</v>
+        <v>0.01825510697949312</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-1.431694527920324</v>
+        <v>-1.462593380863944</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003911926599983116</v>
+        <v>0.003936702015983787</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.7245776502410852</v>
+        <v>0.7699674094977705</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01684975312937694</v>
+        <v>0.01539886238474701</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9924177533717528</v>
+        <v>0.9901196720142972</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0007210233671328197</v>
+        <v>0.0008230686634059018</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5902,10 +5902,10 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1593376026831239</v>
+        <v>0.1606943136811414</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3352966651949248</v>
+        <v>0.3250751776916631</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.367592709598685</v>
       </c>
       <c r="P52" t="n">
-        <v>4.405472265423097</v>
+        <v>4.305155024986907</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9529886884557746</v>
+        <v>0.9535533906622496</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01047018725675023</v>
+        <v>0.01040711306755313</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9384275285691199</v>
+        <v>0.9383978124110627</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01136289117894953</v>
+        <v>0.01136563283225358</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.8991173154021487</v>
+        <v>0.9006945621791339</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002246888035822697</v>
+        <v>0.002229254395263897</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.8108916809264303</v>
+        <v>0.8134869125326483</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01561549512231153</v>
+        <v>0.01550797518812517</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3769421942942636</v>
+        <v>0.3887951259275094</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01301338099207208</v>
+        <v>0.01288900459740433</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.1731797818790902</v>
+        <v>0.1725753582760886</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0008766592309125617</v>
+        <v>0.0008769796008777883</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.331297244801841</v>
+        <v>0.3301843999480366</v>
       </c>
       <c r="L53" t="n">
-        <v>0.221178422090789</v>
+        <v>0.2246818306660378</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.382101377750191</v>
       </c>
       <c r="P53" t="n">
-        <v>4.342414579871032</v>
+        <v>4.425804736657819</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9866735358359816</v>
+        <v>0.9866128000843535</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004963299225061927</v>
+        <v>0.004974596558670659</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9820908643186255</v>
+        <v>0.9818876075911982</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007755890272792965</v>
+        <v>0.007799778186486004</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9131749387710607</v>
+        <v>0.9134016594240653</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.003024838863117415</v>
+        <v>0.003020886998816808</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9710361836304994</v>
+        <v>0.9708082074032175</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.004201707360180242</v>
+        <v>0.004218210915134934</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9645630027173671</v>
+        <v>0.964875161225224</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.005482031735142666</v>
+        <v>0.00545783318243831</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9822540329560205</v>
+        <v>0.9805745190653832</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.899639528412201e-05</v>
+        <v>6.172506150984947e-05</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6110,28 +6110,28 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2292086573981105</v>
+        <v>0.2281402508795552</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4345283410599436</v>
+        <v>0.4187255501437061</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3754236388444964</v>
+        <v>0.3979237607818497</v>
       </c>
       <c r="N54" t="n">
-        <v>0.03070192832005735</v>
+        <v>0.03248303908755212</v>
       </c>
       <c r="O54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.229450565690408</v>
       </c>
       <c r="P54" t="n">
-        <v>4.476720871894466</v>
+        <v>4.317016730181986</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9284263926878751</v>
+        <v>0.9271086492266981</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009714663614001669</v>
+        <v>0.009803684199211734</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8657763509084045</v>
+        <v>0.8628589693716475</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01887580100534787</v>
+        <v>0.01907983320718</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.4718593688475803</v>
+        <v>0.4853813377876738</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004190990671753674</v>
+        <v>0.00413699189335445</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.9222561710998594</v>
+        <v>0.9201048396836626</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.008268934870822331</v>
+        <v>0.008382563356917614</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.8274687036197566</v>
+        <v>0.8309180127913832</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.00532244623583762</v>
+        <v>0.005268973472779115</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8491409304543411</v>
+        <v>0.8413678098059159</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001144317014877577</v>
+        <v>0.001173427611867087</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6214,28 +6214,28 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1960898588687952</v>
+        <v>0.2002049545341849</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4162674845078112</v>
+        <v>0.4177854171157885</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4738969906476873</v>
+        <v>0.4823724924605222</v>
       </c>
       <c r="N55" t="n">
-        <v>0.04442754670565903</v>
+        <v>0.04521007051845333</v>
       </c>
       <c r="O55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.431189175958969</v>
       </c>
       <c r="P55" t="n">
-        <v>4.374439570715301</v>
+        <v>4.391044395531488</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8753794511952142</v>
+        <v>0.8750699212537558</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0142354786945967</v>
+        <v>0.01425314662435774</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.6949988150844543</v>
+        <v>0.6933886143421923</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02665853989263984</v>
+        <v>0.02672881682489168</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.2274835015488156</v>
+        <v>0.231320963693047</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.003848360132931386</v>
+        <v>0.003838789902446569</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.7622818198098086</v>
+        <v>0.7638933575558995</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.01561774699563379</v>
+        <v>0.01556471910003466</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.7865411077443212</v>
+        <v>0.7841429670545274</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.006598903415212415</v>
+        <v>0.006635868142023708</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8452231373389213</v>
+        <v>0.8438352090411543</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0005450650405661765</v>
+        <v>0.0005475034631435092</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6318,10 +6318,10 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2182594007781727</v>
+        <v>0.2084054602031741</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3624150887034048</v>
+        <v>0.3592757186724401</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.242619804626787</v>
+        <v>4.062930613106723</v>
       </c>
       <c r="P56" t="n">
-        <v>4.366012378101686</v>
+        <v>4.324180579402618</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8297178493993111</v>
+        <v>0.8306672697954849</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01210762902556781</v>
+        <v>0.01207382836633396</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6183503655090751</v>
+        <v>0.6192582351611474</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.0215690001757411</v>
+        <v>0.02154333068974413</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.0866659922730646</v>
+        <v>-0.06835646104013682</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009136396749726355</v>
+        <v>0.009059098945100728</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.7914091926860604</v>
+        <v>0.7918803514418224</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01207500041483076</v>
+        <v>0.01206135537804532</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8309088808158525</v>
+        <v>0.8368266521975809</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005978503520327504</v>
+        <v>0.005872955389156894</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8785233296265451</v>
+        <v>0.8782279299369821</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001652195386024017</v>
+        <v>0.001654203021133236</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6422,10 +6422,10 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3849234920957109</v>
+        <v>0.3825163888057561</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4585099466523619</v>
+        <v>0.4554652399335732</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.276433697976676</v>
       </c>
       <c r="P57" t="n">
-        <v>4.399252767768986</v>
+        <v>4.373218250681789</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9023673164401923</v>
+        <v>0.9029720440596852</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009501489570257088</v>
+        <v>0.00947201819921026</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7773992660316782</v>
+        <v>0.7789594421356788</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01785777869724912</v>
+        <v>0.01779508737129534</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6320095499653745</v>
+        <v>0.6319165373354663</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008745371238518809</v>
+        <v>0.008746476401145379</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.8626202526623995</v>
+        <v>0.861946511184812</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.005690096577915133</v>
+        <v>0.005704032275727567</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9351658871807498</v>
+        <v>0.9373334118817404</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004685760564021472</v>
+        <v>0.004606767898489069</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6645044771451201</v>
+        <v>0.6654703919347933</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001294677967582768</v>
+        <v>0.001292812890534761</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6526,28 +6526,28 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.236072290229756</v>
+        <v>0.2320109535708661</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5204813162909041</v>
+        <v>0.5055868509976839</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7622100708809668</v>
+        <v>0.7681619160271811</v>
       </c>
       <c r="N58" t="n">
-        <v>0.08530460940258404</v>
+        <v>0.07581813381578009</v>
       </c>
       <c r="O58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.248034418056246</v>
       </c>
       <c r="P58" t="n">
-        <v>4.755874974121358</v>
+        <v>4.459472537524188</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9812714964646947</v>
+        <v>0.9781762018213621</v>
       </c>
       <c r="R58" t="n">
-        <v>0.005754688129678863</v>
+        <v>0.00621205685806918</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9808306786875907</v>
+        <v>0.9805646181057444</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.008033439537144646</v>
+        <v>0.008088997481588048</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9878709457898626</v>
+        <v>0.9933521688508213</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001013606759784678</v>
+        <v>0.0007504055193867859</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9723146286180825</v>
+        <v>0.9712054223870946</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.006393213317847416</v>
+        <v>0.006520026708401621</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.9113115660568649</v>
+        <v>0.8728731733660288</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.007640147135344339</v>
+        <v>0.00914717172385575</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9383255603977165</v>
+        <v>0.9384721399962459</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0008795471060052519</v>
+        <v>0.0008785012890036574</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6630,10 +6630,10 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4698313368793378</v>
+        <v>0.4677808511850242</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5164512686575472</v>
+        <v>0.5153612643385489</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.211580767596805</v>
       </c>
       <c r="P59" t="n">
-        <v>4.389073785606209</v>
+        <v>4.384899764120235</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7893275088673677</v>
+        <v>0.7968183518500273</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01964630215318416</v>
+        <v>0.01929386090102111</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7439640592654314</v>
+        <v>0.7650175493332589</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.0317206638500916</v>
+        <v>0.03038851763229069</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4332103449310272</v>
+        <v>0.4193090726360488</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02326591410949451</v>
+        <v>0.02354949960259279</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.3614317879357739</v>
+        <v>0.3572233705470572</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.009270587210481438</v>
+        <v>0.009301085464528673</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.8845838158295363</v>
+        <v>-0.886482971900695</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.0170284648443267</v>
+        <v>0.0170370427512309</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5967847477171018</v>
+        <v>-0.5926203320188457</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.00254367152921646</v>
+        <v>0.002540352415209459</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6734,10 +6734,10 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3312705578089989</v>
+        <v>0.3189569329734549</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2477782911221035</v>
+        <v>0.2355319585675123</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.034948938354199</v>
       </c>
       <c r="P60" t="n">
-        <v>4.306032872794803</v>
+        <v>4.206395293982933</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.882843797393462</v>
+        <v>0.8912738908521161</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02128899630805915</v>
+        <v>0.02050876301984904</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.5746788543561976</v>
+        <v>0.6077686094538537</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.04569034176020055</v>
+        <v>0.04387701686477997</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.407826216436158</v>
+        <v>-1.373376878000312</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008224056142357836</v>
+        <v>0.00816501243654</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.4657752672030933</v>
+        <v>0.4574885809817287</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.008060732921886828</v>
+        <v>0.008123009824027607</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-8.221829363850999</v>
+        <v>-8.08209179734647</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006756847869363325</v>
+        <v>0.006705459495662812</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9379664608663421</v>
+        <v>0.9362937334714371</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004837158861258842</v>
+        <v>0.0004901941772152147</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6838,28 +6838,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.426923729397007</v>
+        <v>0.4024729393044518</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3136430398293664</v>
+        <v>0.3147185593062669</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2159302875700806</v>
+        <v>0.1714814228643597</v>
       </c>
       <c r="N61" t="n">
-        <v>0.008622108341937234</v>
+        <v>0.006446242403185847</v>
       </c>
       <c r="O61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.85745491031177</v>
       </c>
       <c r="P61" t="n">
-        <v>4.180008353689512</v>
+        <v>4.244506533144418</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9737381387236145</v>
+        <v>0.9753655196778852</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01155387597053177</v>
+        <v>0.01119016917151622</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9533901800275978</v>
+        <v>0.956685130190843</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.02406107951981747</v>
+        <v>0.02319502806628342</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.348267581340701</v>
+        <v>0.3548043462130738</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004376215452603836</v>
+        <v>0.004354213798501604</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.4171295211449643</v>
+        <v>0.4202422457274665</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.007735385363663017</v>
+        <v>0.007714702932919657</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.9208133460943089</v>
+        <v>0.9195422298362173</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002249375816741635</v>
+        <v>0.002267357604441034</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.245790023294815</v>
+        <v>0.2464955074801776</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002365787943860999</v>
+        <v>0.002364681211973239</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6944,28 +6944,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4112539384720597</v>
+        <v>0.42062216296563</v>
       </c>
       <c r="L62" t="n">
-        <v>0.27514060746873</v>
+        <v>0.2832598715655401</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6648943357974433</v>
+        <v>0.6726559183355876</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1078872421362186</v>
+        <v>0.1130519136593654</v>
       </c>
       <c r="O62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.186553856872338</v>
       </c>
       <c r="P62" t="n">
-        <v>4.1095565673514</v>
+        <v>4.212795092655835</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.986395896006246</v>
+        <v>0.9864343870020784</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007692238449351785</v>
+        <v>0.007681348660281562</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9824895864675358</v>
+        <v>0.9826660055783344</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01380223861356994</v>
+        <v>0.01373253315195547</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.009170123393360985</v>
+        <v>-0.02956412099124472</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003344259170343084</v>
+        <v>0.003377881687494999</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.5124643534639135</v>
+        <v>0.5074464393920112</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.009348593090016896</v>
+        <v>0.009396579682443939</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9825432863689856</v>
+        <v>0.9827161917176197</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.001961493943803442</v>
+        <v>0.00195175566210324</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8544109247931766</v>
+        <v>0.854668696490902</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001911527664525052</v>
+        <v>0.001909834693993966</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7050,28 +7050,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.426923729397007</v>
+        <v>0.4155137200184437</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3117680888393811</v>
+        <v>0.3143500703584229</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3647450907795452</v>
+        <v>0.3416429060717733</v>
       </c>
       <c r="N63" t="n">
-        <v>0.03463151460363494</v>
+        <v>0.0312747675505007</v>
       </c>
       <c r="O63" t="n">
-        <v>4.076109010387499</v>
+        <v>3.974111759233877</v>
       </c>
       <c r="P63" t="n">
-        <v>4.188208227013842</v>
+        <v>4.243301945649341</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9869899460474997</v>
+        <v>0.9871572765446898</v>
       </c>
       <c r="R63" t="n">
-        <v>0.008342454172540086</v>
+        <v>0.00828863177306823</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9732579521368279</v>
+        <v>0.9736047488243623</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01800682232983046</v>
+        <v>0.01788968312652102</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.9068546020658932</v>
+        <v>0.9119417036210394</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.001332678066680093</v>
+        <v>0.001295775273988986</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9265648550817804</v>
+        <v>0.9296948960129381</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.003013813857753725</v>
+        <v>0.002948885261091324</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8791452584162762</v>
+        <v>0.8762629558348696</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003100369549426216</v>
+        <v>0.003137122549348875</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.234584564674936</v>
+        <v>0.2382963231803489</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002020415039344842</v>
+        <v>0.002015510247695989</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7156,28 +7156,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4112539384720597</v>
+        <v>0.375704959280303</v>
       </c>
       <c r="L64" t="n">
-        <v>0.335246042699896</v>
+        <v>0.3427459815241231</v>
       </c>
       <c r="M64" t="n">
-        <v>0.439609385972852</v>
+        <v>0.3788280742102783</v>
       </c>
       <c r="N64" t="n">
-        <v>0.02614209225024554</v>
+        <v>0.02321061373281829</v>
       </c>
       <c r="O64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.767070855148547</v>
       </c>
       <c r="P64" t="n">
-        <v>4.14224675831912</v>
+        <v>4.246761370509985</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9734920960441704</v>
+        <v>0.9737664315039619</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01090858259870994</v>
+        <v>0.01085198826870839</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9591232252255069</v>
+        <v>0.9596860270536098</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.02135239684324772</v>
+        <v>0.02120489475766767</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.5102205119548886</v>
+        <v>0.4975345627490947</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003779476195001316</v>
+        <v>0.003828110052633945</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.2204764919591309</v>
+        <v>0.2217666591183864</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.01074366128674748</v>
+        <v>0.01073476684106613</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9753706412407457</v>
+        <v>0.9756437271975159</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.00226495529311792</v>
+        <v>0.0022523635810956</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8348930727926731</v>
+        <v>0.8349870499638846</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002296818446267018</v>
+        <v>0.002296164690463276</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7262,28 +7262,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.426923729397007</v>
+        <v>0.4084703604096215</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3786479197071242</v>
+        <v>0.3823118048181775</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3131239600723339</v>
+        <v>0.2786308939210075</v>
       </c>
       <c r="N65" t="n">
-        <v>0.02321842324706401</v>
+        <v>0.02026837493045301</v>
       </c>
       <c r="O65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.911116290363315</v>
       </c>
       <c r="P65" t="n">
-        <v>4.213922128918426</v>
+        <v>4.270253326461974</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9786135571649307</v>
+        <v>0.9787942670426757</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01053372713062927</v>
+        <v>0.01048912909349564</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9647190428963086</v>
+        <v>0.9650752778075267</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02147363575807254</v>
+        <v>0.02136495012024092</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6877233071899745</v>
+        <v>0.6881561642511995</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003784016207988157</v>
+        <v>0.003781392723483971</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6373418064085949</v>
+        <v>0.6381988004626431</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008476252332724912</v>
+        <v>0.008466231334322033</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9373771843915533</v>
+        <v>0.935171339494423</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002159081035552374</v>
+        <v>0.002196778006080013</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5633098294001713</v>
+        <v>0.5643088031642651</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001888365845771141</v>
+        <v>0.001886204693369114</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7368,28 +7368,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4112539384720597</v>
+        <v>0.3961978672711403</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3228044745578309</v>
+        <v>0.3297154923448143</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3582837469163401</v>
+        <v>0.3253060564144216</v>
       </c>
       <c r="N66" t="n">
-        <v>0.02053299990923392</v>
+        <v>0.01841572613194823</v>
       </c>
       <c r="O66" t="n">
-        <v>4.099154174190237</v>
+        <v>3.958594592841257</v>
       </c>
       <c r="P66" t="n">
-        <v>4.150861517264367</v>
+        <v>4.247073921346014</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9788528179313152</v>
+        <v>0.9789198334441849</v>
       </c>
       <c r="R66" t="n">
-        <v>0.00983602889388183</v>
+        <v>0.009820431317493362</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9664866360954629</v>
+        <v>0.9666336632930527</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.0192703603895779</v>
+        <v>0.01922804322023051</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.6570965612366224</v>
+        <v>0.6518611476850424</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003609778606062897</v>
+        <v>0.003637231077236156</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6308292545511197</v>
+        <v>0.6307441892307355</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.009283042688836436</v>
+        <v>0.009284112139119612</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9511209092771907</v>
+        <v>0.951717966850951</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003074858303908485</v>
+        <v>0.003056020921802709</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8478242519885862</v>
+        <v>0.8481154149814953</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.00215939682710073</v>
+        <v>0.002157330014599404</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.418401611669922</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3754883524270142</v>
+        <v>0.3821256938063454</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.381125636492835</v>
       </c>
       <c r="P67" t="n">
-        <v>4.258573603837936</v>
+        <v>4.34406181085281</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8612831125799764</v>
+        <v>0.8652052824349274</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02693869404416841</v>
+        <v>0.02655512234624559</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.8063172820364969</v>
+        <v>0.8071641175971108</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007649927651199615</v>
+        <v>0.0007633185508364196</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.6130647098925764</v>
+        <v>0.6252317559356262</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06409562413825676</v>
+        <v>0.06307984279609716</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7684042961412765</v>
+        <v>0.7694401471717121</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002636494705905672</v>
+        <v>0.00263059201364216</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6599487847196395</v>
+        <v>0.6608983700798354</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01279054950719947</v>
+        <v>0.01277267836156645</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8259491540030421</v>
+        <v>0.8106537736777357</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.008639964098441621</v>
+        <v>0.009011606001879655</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8264333115138845</v>
+        <v>0.8067049225180842</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001111855972821239</v>
+        <v>0.0001173345039910578</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7582,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4256809874704212</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3565393702912077</v>
+        <v>0.3705203685982623</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.452681279498788</v>
       </c>
       <c r="P68" t="n">
-        <v>4.191510109558156</v>
+        <v>4.341592065566686</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7995574008999248</v>
+        <v>0.8049131111357513</v>
       </c>
       <c r="R68" t="n">
-        <v>0.02986599630530236</v>
+        <v>0.02946429375497725</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.491349880273228</v>
+        <v>0.4850167914312021</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001166338273658208</v>
+        <v>0.00117357672073808</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4584299511950864</v>
+        <v>0.4747389252301797</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07158574819068865</v>
+        <v>0.07049963336404443</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.4745931554010342</v>
+        <v>0.4663226440179072</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003868414006119549</v>
+        <v>0.003898741778773778</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.6954191670648295</v>
+        <v>0.6887807616993085</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.008115642144618556</v>
+        <v>0.008203606518553111</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.7159478551499857</v>
+        <v>0.6970705455301829</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01201846978036402</v>
+        <v>0.01241140337891528</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.2993138242386173</v>
+        <v>0.249383837800332</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.000743945279597945</v>
+        <v>0.0007699954760900591</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7690,10 +7690,10 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1547738540766385</v>
+        <v>0.1578375667668122</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2113040000718849</v>
+        <v>0.2142730074772703</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.342039872316217</v>
       </c>
       <c r="P69" t="n">
-        <v>4.256185192496</v>
+        <v>4.303413304182833</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9734656079337696</v>
+        <v>0.973466531904749</v>
       </c>
       <c r="R69" t="n">
-        <v>0.00954709243755102</v>
+        <v>0.009546926213408365</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9648035545181619</v>
+        <v>0.9649308018052815</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01039350733473922</v>
+        <v>0.01037470226615612</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.4534318991265486</v>
+        <v>0.458396391489205</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004694912786907527</v>
+        <v>0.004673542140826365</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8644266184939671</v>
+        <v>0.8640858595624259</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01491012855586839</v>
+        <v>0.01492885483844594</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9076541033518778</v>
+        <v>0.9076361642234667</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009220341024997931</v>
+        <v>0.009221236553957691</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5180018623746242</v>
+        <v>0.5180123767864011</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004282644871103801</v>
+        <v>0.004282598159577627</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7794,10 +7794,10 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.153202753067615</v>
+        <v>0.1548404427189273</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2806403425895768</v>
+        <v>0.2798005208792019</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.394470536415335</v>
       </c>
       <c r="P70" t="n">
-        <v>4.369359318589514</v>
+        <v>4.362379885776532</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9659445971481412</v>
+        <v>0.965987268471406</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009056194328969694</v>
+        <v>0.009050518857660008</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9103630653369571</v>
+        <v>0.9105946226162333</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01336850055648339</v>
+        <v>0.01335122210202667</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9219866558655925</v>
+        <v>0.9219389840196544</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.00323992427581504</v>
+        <v>0.003240914039709335</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9626947848226376</v>
+        <v>0.9627215048588192</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.008770335173139167</v>
+        <v>0.008767193713566931</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8229049525683023</v>
+        <v>0.8229355510279825</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01178667983435102</v>
+        <v>0.01178566153984561</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7539241257198928</v>
+        <v>0.7529163503012019</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.00223936634160263</v>
+        <v>0.002243947189856084</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7898,10 +7898,10 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3261006684563419</v>
+        <v>0.3259506110927289</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3495488083686846</v>
+        <v>0.3486347098873965</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.436154054572222</v>
       </c>
       <c r="P71" t="n">
-        <v>4.457003126826023</v>
+        <v>4.440396206872959</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9607422787290285</v>
+        <v>0.9607948920053613</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01081851722040209</v>
+        <v>0.01081126529064855</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9430222570030538</v>
+        <v>0.9432467069920062</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01420634270854847</v>
+        <v>0.01417833387835802</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7405474700312662</v>
+        <v>0.7407857206215123</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004512007366406257</v>
+        <v>0.004509935243005926</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9024779376253617</v>
+        <v>0.9024282342438994</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009959921946509499</v>
+        <v>0.009962459724770861</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8435373599385118</v>
+        <v>0.8435488309205408</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01621223827861748</v>
+        <v>0.01621164397155933</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9353651492544783</v>
+        <v>0.9354870836204331</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009932146949270201</v>
+        <v>0.0009922773973696391</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -8002,10 +8002,10 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3263018165925168</v>
+        <v>0.3237573962818418</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4214831291060785</v>
+        <v>0.4159121970215693</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.514536388254673</v>
       </c>
       <c r="P72" t="n">
-        <v>4.561848912256965</v>
+        <v>4.505731237331502</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9583660087194081</v>
+        <v>0.9584956209223118</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01165209045993593</v>
+        <v>0.01163393906122562</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.870177595442528</v>
+        <v>0.8706524050963869</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01504844604738395</v>
+        <v>0.01502090190897186</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.8080623011334103</v>
+        <v>0.8083387442247059</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004825728943423075</v>
+        <v>0.004822252502559896</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9534331659834825</v>
+        <v>0.9535455239329719</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006762516676927697</v>
+        <v>0.006754353341282688</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8562765374041598</v>
+        <v>0.8567071382991861</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.01952851540042021</v>
+        <v>0.01949923937294363</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9029273479746046</v>
+        <v>0.9028636026677657</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001420607829788853</v>
+        <v>0.001421074192962858</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8106,10 +8106,10 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.07823057899988078</v>
+        <v>0.08006297265283152</v>
       </c>
       <c r="L73" t="n">
-        <v>0.07924232650042848</v>
+        <v>0.08137571817139509</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.341883758983041</v>
       </c>
       <c r="P73" t="n">
-        <v>4.219362957573282</v>
+        <v>4.328693886773427</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9940101586958018</v>
+        <v>0.9939987049766698</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005147066669713649</v>
+        <v>0.005151985406082198</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9491220529728542</v>
+        <v>0.9490814218129882</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007744567208881133</v>
+        <v>0.007747658999801856</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6112191276303769</v>
+        <v>0.6117652657776269</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001246431655692332</v>
+        <v>0.001245555888451064</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9650589371089653</v>
+        <v>0.9649111723746878</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.006271650348714358</v>
+        <v>0.006284897670915332</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8259568047831244</v>
+        <v>0.8256670362030982</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005100856807103439</v>
+        <v>0.005105101308953068</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07146806416313956</v>
+        <v>-0.07106758937209445</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361614939844022</v>
+        <v>0.002361173556815051</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8210,10 +8210,10 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08513405677699858</v>
+        <v>0.08447647533141782</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1689500257276514</v>
+        <v>0.1658804054347571</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.39908900615176</v>
       </c>
       <c r="P74" t="n">
-        <v>4.457653597315279</v>
+        <v>4.387802555380378</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9726805935556744</v>
+        <v>0.9727065298452893</v>
       </c>
       <c r="R74" t="n">
-        <v>0.007829806103325421</v>
+        <v>0.007826088519988738</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8502940075525092</v>
+        <v>0.8506090202983611</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.009244054869493116</v>
+        <v>0.009234324034623946</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8618552135348991</v>
+        <v>0.8619261917317049</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001235135747736637</v>
+        <v>0.001234818403252835</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8980445214266097</v>
+        <v>0.89799882772458</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01257305838411271</v>
+        <v>0.01257587552172969</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.859723041967477</v>
+        <v>0.8601894009539437</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007572832694606644</v>
+        <v>0.007560234051106085</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7041811815150292</v>
+        <v>0.703507128170933</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002030176145563128</v>
+        <v>0.002032487811158591</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8314,10 +8314,10 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.210319821056764</v>
+        <v>0.207879713293752</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2645787813378834</v>
+        <v>0.2635591019267816</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.205773976883957</v>
       </c>
       <c r="P75" t="n">
-        <v>4.299243597059222</v>
+        <v>4.285134295724109</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9700469662964879</v>
+        <v>0.9700352220929257</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006834941210109994</v>
+        <v>0.006836281025551389</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8953969963061648</v>
+        <v>0.8952312768612467</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01155696709680736</v>
+        <v>0.01156611815438031</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8422532245447558</v>
+        <v>0.8435216367826263</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002396519932061428</v>
+        <v>0.002386865501858177</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9316235622403947</v>
+        <v>0.9316537784967639</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.006862866271430834</v>
+        <v>0.006861349718007638</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8717042078087577</v>
+        <v>0.8718459282597438</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006794252979355332</v>
+        <v>0.006790499346298951</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9731654708789172</v>
+        <v>0.9732191547832254</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.00100722562508203</v>
+        <v>0.001006217616439601</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8418,10 +8418,10 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.01998426772365844</v>
+        <v>0.02053128902279143</v>
       </c>
       <c r="L76" t="n">
-        <v>0.0244471553205033</v>
+        <v>0.0250756029909988</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.358945393733942</v>
       </c>
       <c r="P76" t="n">
-        <v>4.216706931406385</v>
+        <v>4.318133971111876</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931298525769812</v>
+        <v>0.9931292052762066</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005201076866576898</v>
+        <v>0.005201321881827598</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9362493832985253</v>
+        <v>0.9362500312685267</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007183614015913946</v>
+        <v>0.007183577508202707</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8851311178970535</v>
+        <v>0.8852010893653117</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0009344300591946267</v>
+        <v>0.0009341454155121317</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9547803547190364</v>
+        <v>0.9547729376552964</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008976853148706818</v>
+        <v>0.008977589323897476</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887632244198661</v>
+        <v>0.9887546082770504</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008909203122735641</v>
+        <v>0.0008912618170783924</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.5685367290460438</v>
+        <v>0.568544772413443</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183596864973831</v>
+        <v>0.001183585832576119</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8522,10 +8522,10 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03972700182767472</v>
+        <v>0.03789390692492493</v>
       </c>
       <c r="L77" t="n">
-        <v>0.09014497000828862</v>
+        <v>0.08293632886498861</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.275909837651753</v>
       </c>
       <c r="P77" t="n">
-        <v>4.553917325990885</v>
+        <v>4.243293106379868</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9729265937794692</v>
+        <v>0.9728371946158348</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009866872038998255</v>
+        <v>0.009883149324401437</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.541006760314628</v>
+        <v>0.5403022448950849</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01234336128498687</v>
+        <v>0.01235283065536421</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.6213109965600363</v>
+        <v>-0.6297403391754275</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.001245197882691078</v>
+        <v>0.00124843063454326</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9218685259864257</v>
+        <v>0.9210674752498865</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01211719118503445</v>
+        <v>0.01217914913857419</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1686206329248439</v>
+        <v>0.1692933316843996</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01361647822552445</v>
+        <v>0.01361096832113987</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8769632662559022</v>
+        <v>0.8749901634310162</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007949415765946151</v>
+        <v>0.0008012903431373562</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8626,10 +8626,10 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02841134719532212</v>
+        <v>0.02722131315634268</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0822024536638621</v>
+        <v>0.07764629252821463</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.411801604657093</v>
       </c>
       <c r="P78" t="n">
-        <v>4.642155854354315</v>
+        <v>4.3775281730888</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9796106245546224</v>
+        <v>0.9790410756732091</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01036892834776415</v>
+        <v>0.01051275169436136</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.1234549371150698</v>
+        <v>0.1225301556099971</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.01134972650874777</v>
+        <v>0.01135571208248658</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7411142668666199</v>
+        <v>0.7096709745839889</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0005951425047757586</v>
+        <v>0.0006302489600751789</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8426017678716911</v>
+        <v>0.8348689263672254</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01631530084187625</v>
+        <v>0.01671127413344865</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2282322311572544</v>
+        <v>-0.2437225258503379</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.0116755727891755</v>
+        <v>0.01174896745641607</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.70414381024056</v>
+        <v>-1.722751445451205</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.00242793069602666</v>
+        <v>0.002436269859700756</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8730,10 +8730,10 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2899193890845111</v>
+        <v>0.291298707758667</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3201897700289114</v>
+        <v>0.3304035059681816</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.395075630781815</v>
       </c>
       <c r="P79" t="n">
-        <v>4.431605501335618</v>
+        <v>4.439066110577246</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9808407750009602</v>
+        <v>0.9810896195208271</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0203610209736673</v>
+        <v>0.02022836194988157</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9160159304869085</v>
+        <v>0.9173823247709172</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04501303030117679</v>
+        <v>0.04464535478460659</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3632543748068622</v>
+        <v>0.3691180979314987</v>
       </c>
       <c r="X79" t="n">
-        <v>0.002245803912084987</v>
+        <v>0.00223543930990148</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9958872603664474</v>
+        <v>0.9955889158578903</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005011922950510258</v>
+        <v>0.005190526931061067</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5828360033729389</v>
+        <v>0.5906689916039923</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.004881611045587533</v>
+        <v>0.0048355634456624</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9877891831635069</v>
+        <v>0.9850466385376752</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003545412870967139</v>
+        <v>0.00392341162287957</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8681224779967041</v>
+        <v>0.8652278378842142</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009704252803032248</v>
+        <v>0.009810176261362718</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1594873656769697</v>
+        <v>0.1623021847871931</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2380167376080126</v>
+        <v>0.2458325049296386</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.51750010072576</v>
       </c>
       <c r="P80" t="n">
-        <v>4.462538015820062</v>
+        <v>4.474103812650267</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9939163145647836</v>
+        <v>0.9937421742225868</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01078061741123134</v>
+        <v>0.01093382183032316</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.979650390290028</v>
+        <v>0.9791557110882316</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02265282804904696</v>
+        <v>0.02292650890581743</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7877400810217022</v>
+        <v>0.7965904666481212</v>
       </c>
       <c r="X80" t="n">
-        <v>0.0012323865532568</v>
+        <v>0.001206420214992126</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9982504634269294</v>
+        <v>0.9983500140171362</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.002685480051424597</v>
+        <v>0.002607957713187918</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8134058294090788</v>
+        <v>0.8223784533859008</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.003594111847223956</v>
+        <v>0.003506633486720634</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9786946622250571</v>
+        <v>0.9764504627317075</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.007742101094082864</v>
+        <v>0.008139651575354715</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.970153656990044</v>
+        <v>0.969382218542139</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.005659930212852742</v>
+        <v>0.005732609682370402</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8946,66 +8946,66 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2816063271155299</v>
+        <v>0.281196440943406</v>
       </c>
       <c r="L81" t="n">
-        <v>0.252705326622038</v>
+        <v>0.2614933935880142</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>0.005183724718742067</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>0.0001036744943748413</v>
       </c>
       <c r="O81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.547853617806929</v>
       </c>
       <c r="P81" t="n">
-        <v>4.557058862037469</v>
+        <v>4.585223414227971</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9912748324093862</v>
+        <v>0.9915070434125417</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01269413939526513</v>
+        <v>0.01252407980522361</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9745494361674315</v>
+        <v>0.9755491937755753</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02390761040522475</v>
+        <v>0.02343333266215862</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9801012999543643</v>
+        <v>0.9789298012528225</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009296905693797732</v>
+        <v>0.009566661091336063</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7534847335186534</v>
+        <v>0.7594040422916682</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.003014928017584105</v>
+        <v>0.002978510949065003</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9564107507306058</v>
+        <v>0.9579940932269724</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.006698113981745495</v>
+        <v>0.006575337073305629</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9601608178762675</v>
+        <v>0.9611088731917771</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009682203380484391</v>
+        <v>0.009566305746989707</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9050,66 +9050,66 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2406107375126686</v>
+        <v>0.2355470167542912</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1482789748777058</v>
+        <v>0.1488024249767209</v>
       </c>
       <c r="M82" t="n">
-        <v>0.1933648479161773</v>
+        <v>0.1740023896155605</v>
       </c>
       <c r="N82" t="n">
-        <v>0.0106705557991725</v>
+        <v>0.008462144799708044</v>
       </c>
       <c r="O82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.463853060787375</v>
       </c>
       <c r="P82" t="n">
-        <v>4.541670804232746</v>
+        <v>4.585312245728836</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9681253796400844</v>
+        <v>0.9684451220406297</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02408394203559763</v>
+        <v>0.02396284150736804</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9117974268383728</v>
+        <v>0.9128186336580602</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04636780874906869</v>
+        <v>0.04609860470264915</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9471010756132539</v>
+        <v>0.9473579185218206</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01540018970314645</v>
+        <v>0.01536275753884477</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.3030238810965565</v>
+        <v>0.3239863661843387</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.002450265880775227</v>
+        <v>0.002413137069901971</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.6777467068401222</v>
+        <v>0.6782834484682327</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.02042294927894889</v>
+        <v>0.02040593406829236</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9677842115922655</v>
+        <v>0.9685626653524042</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.009483729680353194</v>
+        <v>0.009368447848503682</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1872142165502269</v>
+        <v>0.189934792401037</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1744343568656718</v>
+        <v>0.1826267284946377</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.578578953049799</v>
       </c>
       <c r="P83" t="n">
-        <v>4.496770193524266</v>
+        <v>4.571960649035538</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9757351283802572</v>
+        <v>0.975739278735116</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01864969681783473</v>
+        <v>0.01864810179250103</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9247042042227489</v>
+        <v>0.9247478164506443</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03556262014093663</v>
+        <v>0.03555231950112275</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9589703294091785</v>
+        <v>0.9595067108214487</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009767537762755551</v>
+        <v>0.009703482150566864</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2678064322599043</v>
+        <v>0.2721584302524647</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009563662233708191</v>
+        <v>0.009535197718484453</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9226521792167981</v>
+        <v>0.92071581695676</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01067618138995927</v>
+        <v>0.01080899162941539</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8751591374784887</v>
+        <v>0.8756106397787032</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01317219523688434</v>
+        <v>0.01314835423107227</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1659043674747134</v>
+        <v>0.171344845273151</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2938338308490022</v>
+        <v>0.3144608188889046</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.585710978228106</v>
       </c>
       <c r="P84" t="n">
-        <v>4.341325581286786</v>
+        <v>4.51504935164796</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9907038002269452</v>
+        <v>0.9903344577308121</v>
       </c>
       <c r="R84" t="n">
-        <v>0.01132252969980373</v>
+        <v>0.01154526369606604</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.987138796729058</v>
+        <v>0.9873913956404577</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01516784808686528</v>
+        <v>0.01501815830575804</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9944013672726111</v>
+        <v>0.9933130550836702</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.00510472761096804</v>
+        <v>0.005578859917414843</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.4879190518881908</v>
+        <v>0.5270393210160504</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.006478758690384553</v>
+        <v>0.006226371265389735</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.8005550704679345</v>
+        <v>0.7830435084276691</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01840575374196602</v>
+        <v>0.01919678194774724</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9960190108711754</v>
+        <v>0.9975782452931089</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.00203235072469209</v>
+        <v>0.0015851422332806</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2307899480131057</v>
+        <v>0.2347111018878213</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2857637698969581</v>
+        <v>0.2950582658013271</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9368,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.499856930037251</v>
       </c>
       <c r="P85" t="n">
-        <v>4.439386013214333</v>
+        <v>4.494335338061362</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9784447043439806</v>
+        <v>0.9804738895804873</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0183486138085498</v>
+        <v>0.01746361459638317</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9437043886202918</v>
+        <v>0.9535757123586837</v>
       </c>
       <c r="U85" t="n">
-        <v>0.03046067680985256</v>
+        <v>0.02766144752124787</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9942412419406904</v>
+        <v>0.9918666485371912</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.005848009430268191</v>
+        <v>0.006949897789780429</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.101578750083466</v>
+        <v>-0.08764342376728562</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01640118423367383</v>
+        <v>0.01629711392139493</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.5690478649430026</v>
+        <v>0.572784553447327</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.02120279747901276</v>
+        <v>0.02111067502000964</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9966263493138098</v>
+        <v>0.9997841094756301</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.001657899955602232</v>
+        <v>0.0004193967435592211</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1218510305567165</v>
+        <v>0.1247724149338163</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1551652986346165</v>
+        <v>0.1593436216466051</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9470,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.570462719990509</v>
       </c>
       <c r="P86" t="n">
-        <v>4.395433839038261</v>
+        <v>4.515742961794027</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.990282802309974</v>
+        <v>0.9903940418722199</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01175686320578157</v>
+        <v>0.01168937498319476</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.984862085679888</v>
+        <v>0.9850744497473672</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01710222292237146</v>
+        <v>0.01698183892126025</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9965056007730628</v>
+        <v>0.9963065060987834</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.00343853972956603</v>
+        <v>0.003535138875647679</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.3863211730011531</v>
+        <v>-0.3773211717237219</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.01762419116738577</v>
+        <v>0.01756688986452823</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.980574327110707</v>
+        <v>0.9812247563569276</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.007125767026673223</v>
+        <v>0.007005455428793422</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9759319261294759</v>
+        <v>0.9766567408923517</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.005041915094091606</v>
+        <v>0.004965415611374016</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1823831187847791</v>
+        <v>0.1836932525307708</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3078900839765812</v>
+        <v>0.3212089024650849</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9572,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.671001137082393</v>
       </c>
       <c r="P87" t="n">
-        <v>4.466751208604983</v>
+        <v>4.625012894559749</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9518656200216894</v>
+        <v>0.9528373348785328</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02459552777609906</v>
+        <v>0.02434600038411214</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9070150786347414</v>
+        <v>0.9101216501858823</v>
       </c>
       <c r="U87" t="n">
-        <v>0.03953906989600713</v>
+        <v>0.0388729705995589</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.842365017111372</v>
+        <v>0.8400135795326471</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.02219044444489006</v>
+        <v>0.02235533897543889</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.7637144533278863</v>
+        <v>0.7703664535196264</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.005697776363993149</v>
+        <v>0.005617000820560498</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.3011189833442504</v>
+        <v>0.3036929249166189</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.02953727504245141</v>
+        <v>0.02948283276357546</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9747029455617909</v>
+        <v>0.9794633256672065</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.00800192399324752</v>
+        <v>0.007209821328705651</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2319557577696864</v>
+        <v>0.2269187336146035</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1636344729465923</v>
+        <v>0.161092772703215</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9674,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.508038569021577</v>
       </c>
       <c r="P88" t="n">
-        <v>4.563873858658869</v>
+        <v>4.616014896168517</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.99058810513725</v>
+        <v>0.9911677522753494</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01137439219436958</v>
+        <v>0.01101857129381207</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9722704853876759</v>
+        <v>0.9747456996005284</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02098777753374793</v>
+        <v>0.02002917169113984</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9848126834828588</v>
+        <v>0.9859123750878857</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.006972749676232797</v>
+        <v>0.006715563222680828</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5602732690421336</v>
+        <v>0.5661360560631665</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004136424321866487</v>
+        <v>0.004108756738976216</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9554240205345266</v>
+        <v>0.9549355258833319</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.006293028073189432</v>
+        <v>0.006327415812534392</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9512849066276079</v>
+        <v>0.9499380395057382</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01005314560735598</v>
+        <v>0.01019117196147346</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9764,66 +9764,66 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3543155928022084</v>
+        <v>0.3488188784207902</v>
       </c>
       <c r="L89" t="n">
-        <v>0.328929700576932</v>
+        <v>0.3411761504532672</v>
       </c>
       <c r="M89" t="n">
-        <v>0.05562070257093243</v>
+        <v>0.04057975262183888</v>
       </c>
       <c r="N89" t="n">
-        <v>0.001207434685508586</v>
+        <v>0.0008115950524367776</v>
       </c>
       <c r="O89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.501604676162365</v>
       </c>
       <c r="P89" t="n">
-        <v>4.622394810978187</v>
+        <v>4.601841240036634</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9948166899016061</v>
+        <v>0.9957349728921592</v>
       </c>
       <c r="R89" t="n">
-        <v>0.008519901234064764</v>
+        <v>0.007728440403138749</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9905649042151842</v>
+        <v>0.9944766261694264</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01327442244119631</v>
+        <v>0.01015651458759061</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9958482037511744</v>
+        <v>0.9956230963153566</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.004910396079078434</v>
+        <v>0.005041758082311287</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7712276256238247</v>
+        <v>0.7664862038334285</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004635289134358399</v>
+        <v>0.004683077138536186</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9615612841969441</v>
+        <v>0.9539081176324975</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.004763389449170466</v>
+        <v>0.005216075606604636</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9428034938421265</v>
+        <v>0.9416031832680545</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01088326789097635</v>
+        <v>0.01099687164499745</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9866,66 +9866,66 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5131582127201041</v>
+        <v>0.5583518477656447</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4979649196547463</v>
+        <v>0.5219359551048091</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6172366085026122</v>
+        <v>0.6485924380199451</v>
       </c>
       <c r="N90" t="n">
-        <v>0.112063332363426</v>
+        <v>0.1245034669297462</v>
       </c>
       <c r="O90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.519091781875822</v>
       </c>
       <c r="P90" t="n">
-        <v>4.098235276344655</v>
+        <v>4.27504208100537</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9889933509262018</v>
+        <v>0.9895720182869033</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01387290293524999</v>
+        <v>0.01350330005250666</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9789685760633579</v>
+        <v>0.9805878235629527</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02348660402106436</v>
+        <v>0.02256435905850731</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9885852061625621</v>
+        <v>0.9880291793120841</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.0138019070276965</v>
+        <v>0.01413406304948875</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8213646879870014</v>
+        <v>0.8292730326799973</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004815379079556557</v>
+        <v>0.004707581940714791</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9947262241701217</v>
+        <v>0.9946266928499801</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005531347804219088</v>
+        <v>0.0005583300049998928</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9840852947601308</v>
+        <v>0.9842748942254244</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.004135042097734514</v>
+        <v>0.004110336932945308</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>

--- a/tables/N-Retention/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
+++ b/tables/N-Retention/Local_perf_matrix_protection_True_vo_True_CUE_True.xlsx
@@ -653,25 +653,25 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2306347362834478</v>
+        <v>0.1674339432438329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2139717519039619</v>
+        <v>0.203535937666269</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.41245498585054</v>
+        <v>4.387465324381761</v>
       </c>
       <c r="P2" t="n">
-        <v>4.428027272095276</v>
+        <v>4.42887075888491</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9928798272182282</v>
+        <v>0.9905464683428621</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005186910372713974</v>
+        <v>0.005976687089561895</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9921068956002747</v>
+        <v>0.9888421261448189</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.006442818869549126</v>
+        <v>0.007660246092134771</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9997455576661759</v>
+        <v>0.9996788169655345</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001049569202043909</v>
+        <v>0.0001179214176905098</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9991391223597588</v>
+        <v>0.9968215165562385</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001237984162028732</v>
+        <v>0.002378780401010257</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9558640799878323</v>
+        <v>0.9452747628455158</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008939537992363963</v>
+        <v>0.009954347750636574</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.7143230577306785</v>
+        <v>0.6399208281962545</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001608409072058359</v>
+        <v>0.001805751221634309</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -757,43 +757,43 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1232120795919104</v>
+        <v>0.07218375034073646</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1574610681810748</v>
+        <v>0.1188584681043094</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9899152127727258</v>
+        <v>0.08822410456946805</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9830143494385797</v>
+        <v>0.00313696381396785</v>
       </c>
       <c r="O3" t="n">
-        <v>4.33964224043698</v>
+        <v>4.326733286264945</v>
       </c>
       <c r="P3" t="n">
-        <v>4.338782073077034</v>
+        <v>4.325935508128786</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9906571464334931</v>
+        <v>0.9896781173151756</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005877728753378776</v>
+        <v>0.006178018842782079</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9959254163896009</v>
+        <v>0.9961843974396017</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004101749736191257</v>
+        <v>0.003969255979543122</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-1.057186228100309</v>
+        <v>0.9999701937971854</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003512210996364536</v>
+        <v>1.336894449803795e-05</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9825752785922954</v>
+        <v>0.974744790914708</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.006402209554158521</v>
+        <v>0.007707658200280037</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8570375362960841</v>
+        <v>0.8446902113167125</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.009169824469328437</v>
+        <v>0.009557612642596913</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.3332112990436396</v>
+        <v>0.3028545737488311</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003331742556789961</v>
+        <v>0.003406740175945235</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -861,25 +861,25 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4182134418056933</v>
+        <v>0.3797396150587981</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2208594485135457</v>
+        <v>0.3057565171719283</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.293495891699291</v>
+        <v>4.273399903936915</v>
       </c>
       <c r="P4" t="n">
-        <v>4.556602342455461</v>
+        <v>4.55369389410242</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9607964551961967</v>
+        <v>0.9569255171575618</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01295229532806168</v>
+        <v>0.01357669636498565</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9851941532454184</v>
+        <v>0.9814527421564614</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.010714063731892</v>
+        <v>0.01199160888551269</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9985442196193263</v>
+        <v>0.9972244780820529</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004748494524258263</v>
+        <v>0.0006556624936029858</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.4346038484660159</v>
+        <v>0.3677662399929601</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02447280906145297</v>
+        <v>0.02587892542001821</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.969599831718468</v>
+        <v>0.9841888648188712</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007232206854740965</v>
+        <v>0.005215721232469521</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.3487408446412722</v>
+        <v>0.2529880350820396</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004089552245753408</v>
+        <v>0.004379884108388915</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -965,43 +965,43 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.183837851295302</v>
+        <v>0.1252238931351918</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2238263143116071</v>
+        <v>0.2162935905143465</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.9147851115099852</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.867110421440475</v>
       </c>
       <c r="O5" t="n">
-        <v>4.308694500962631</v>
+        <v>4.317207381413163</v>
       </c>
       <c r="P5" t="n">
-        <v>4.348799656553713</v>
+        <v>4.351840006965973</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9975645951211797</v>
+        <v>0.99376357769534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002920944638374979</v>
+        <v>0.004674180700986544</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9986341256968937</v>
+        <v>0.9995841253893079</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00264711616156805</v>
+        <v>0.001460658990257724</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999958712056961</v>
+        <v>-1.022627241983535</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.252179935866721e-05</v>
+        <v>0.00876421541151433</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9983410305587128</v>
+        <v>0.9978118289321809</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00189336119830271</v>
+        <v>0.00217447748284994</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9742049323665801</v>
+        <v>0.9607674731116153</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005340006390386004</v>
+        <v>0.006585618699743561</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9674414162148932</v>
+        <v>0.9762056887387</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0008413096907191719</v>
+        <v>0.0007192166096612172</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1069,43 +1069,43 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1701916451553553</v>
+        <v>0.1117312252274767</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2186875923145526</v>
+        <v>0.1725720347500298</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9892467693566445</v>
+        <v>0.05844526816262352</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9837898177280916</v>
+        <v>0.001708052346320512</v>
       </c>
       <c r="O6" t="n">
-        <v>4.378395834553357</v>
+        <v>4.373623920156238</v>
       </c>
       <c r="P6" t="n">
-        <v>4.391829889632508</v>
+        <v>4.375901035984163</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9772129130450882</v>
+        <v>0.9760463066925256</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009125460349448335</v>
+        <v>0.009356138022986136</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9921267179908332</v>
+        <v>0.9922379428664266</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005118245778830672</v>
+        <v>0.005081964776424954</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>-1.052399706355871</v>
+        <v>0.9999965003170471</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.003826332795191198</v>
+        <v>4.996502616647151e-06</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9969519038513933</v>
+        <v>0.9908559861400317</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002264424378096487</v>
+        <v>0.003922039189386735</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.6738368229955096</v>
+        <v>0.6553979924881559</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01855378017522338</v>
+        <v>0.01907101658108899</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.4084380759999942</v>
+        <v>0.3525587387762179</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001812390475807902</v>
+        <v>0.001896059023168669</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1173,43 +1173,43 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2317281644358207</v>
+        <v>0.1705952756742617</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1567341053516102</v>
+        <v>0.1608943523966046</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1417626463179144</v>
+        <v>0.2354175851972045</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005343845688049327</v>
+        <v>0.009165692826775172</v>
       </c>
       <c r="O7" t="n">
-        <v>4.265203801522019</v>
+        <v>4.238648069175182</v>
       </c>
       <c r="P7" t="n">
-        <v>4.378363345136592</v>
+        <v>4.380067775964964</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.990775766353896</v>
+        <v>0.991160347094028</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005835472453123137</v>
+        <v>0.005712529845383224</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9931977233845325</v>
+        <v>0.9962860990585576</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006257611256841111</v>
+        <v>0.004623773946160768</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9996502880983449</v>
+        <v>0.9997843979059177</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.067930722263177e-05</v>
+        <v>6.334807778468424e-05</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9399908492301664</v>
+        <v>0.9315292989064075</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.009765715658696992</v>
+        <v>0.01043152305379643</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9926501729215893</v>
+        <v>0.9983369177979611</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002257574471204742</v>
+        <v>0.001073891444573549</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.3080632907430052</v>
+        <v>0.2488421791169226</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004391457382657783</v>
+        <v>0.004575526586750049</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1277,43 +1277,43 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1755031604752748</v>
+        <v>0.1151345143695899</v>
       </c>
       <c r="L8" t="n">
-        <v>0.15174576798274</v>
+        <v>0.1547131020018682</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08213333455056815</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002204845580817327</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.444307466489452</v>
+        <v>4.414448270647103</v>
       </c>
       <c r="P8" t="n">
-        <v>4.408437917072764</v>
+        <v>4.412986054188962</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9924101337693199</v>
+        <v>0.9941192892060596</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00469337153715132</v>
+        <v>0.004131262446858248</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9917373664197541</v>
+        <v>0.9948173015185464</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.006065475883001574</v>
+        <v>0.004803785480812676</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999972574356384</v>
+        <v>0.9999987199410557</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.087014935445824e-05</v>
+        <v>7.426293023326294e-06</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9856723116340524</v>
+        <v>0.9859589274157563</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00592715920908862</v>
+        <v>0.005867575291740451</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9827820190666458</v>
+        <v>0.9876582453848569</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005556138788486537</v>
+        <v>0.004704033742136383</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9996903313898945</v>
+        <v>0.9988929469350667</v>
       </c>
       <c r="AM8" t="n">
-        <v>6.428176996349951e-05</v>
+        <v>0.0001215411818256799</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1381,43 +1381,43 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2153661717190752</v>
+        <v>0.1549872242120613</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1643420762688951</v>
+        <v>0.1628365407576097</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06232359596124581</v>
+        <v>0.09062411284169591</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001260058754466462</v>
+        <v>0.001812482256833918</v>
       </c>
       <c r="O9" t="n">
-        <v>4.234521484447876</v>
+        <v>4.210724940548642</v>
       </c>
       <c r="P9" t="n">
-        <v>4.36316595797072</v>
+        <v>4.362749003408215</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9952343914761901</v>
+        <v>0.9950286029644555</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003733540342865374</v>
+        <v>0.003813299276594023</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9957038994260116</v>
+        <v>0.9981201478795554</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004730985756148247</v>
+        <v>0.003129509425703269</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.999950481996056</v>
+        <v>0.999923399681598</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.030040006622898e-05</v>
+        <v>5.012369513519603e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9985801129249151</v>
+        <v>0.9985086014558108</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001524736954249111</v>
+        <v>0.001562661384958981</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9720689626890463</v>
+        <v>0.9615044556734009</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006305873266220749</v>
+        <v>0.007402986173781799</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9840105961025097</v>
+        <v>0.9773840044771849</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007602676454712302</v>
+        <v>0.0009041869338713378</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1485,25 +1485,25 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2184121894741882</v>
+        <v>0.1598414097710008</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1178707377254579</v>
+        <v>0.1276623973367958</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.11415328726214</v>
+        <v>4.094150303545265</v>
       </c>
       <c r="P10" t="n">
-        <v>4.23528492147312</v>
+        <v>4.236447636475451</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9928800950808492</v>
+        <v>0.9917514290461289</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005360032277290705</v>
+        <v>0.005769254071888926</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.999688863589391</v>
+        <v>0.9992487828677845</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001560222387227277</v>
+        <v>0.002424341683174713</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999699892593092</v>
+        <v>0.9999564639201787</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.578912425571369e-05</v>
+        <v>5.515039669526257e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9298620732531865</v>
+        <v>0.9174006803842604</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01082892496375592</v>
+        <v>0.01175160314762931</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9749017566791109</v>
+        <v>0.9904057938228614</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.00250651898582266</v>
+        <v>0.001549722219725487</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.7845764702381025</v>
+        <v>0.7617725261145389</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002844140720787344</v>
+        <v>0.002990889958312578</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1589,43 +1589,43 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4182813421933623</v>
+        <v>0.3840542250418848</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4003198085406786</v>
+        <v>0.399307046607309</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4394594276089848</v>
+        <v>0.5534286563339468</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0636255995137141</v>
+        <v>0.06839945605034328</v>
       </c>
       <c r="O11" t="n">
-        <v>4.115746786233981</v>
+        <v>4.07733279147739</v>
       </c>
       <c r="P11" t="n">
-        <v>4.272581114654178</v>
+        <v>4.275717490300391</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9727380326006789</v>
+        <v>0.988340258166698</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01228344397341881</v>
+        <v>0.008033152645296655</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9571407507055467</v>
+        <v>0.9830180656336077</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.025884085136523</v>
+        <v>0.01629311484282568</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9995505247519588</v>
+        <v>0.9999138023193999</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0001493308685611915</v>
+        <v>6.539499196476809e-05</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9347267189029522</v>
+        <v>0.9124702373073287</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.004528835876274773</v>
+        <v>0.005244411199127367</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.8975654178698704</v>
+        <v>0.9394084419221264</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003596469416381206</v>
+        <v>0.002766044298896734</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9623904796703597</v>
+        <v>0.9708081148382405</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.000821566069800697</v>
+        <v>0.0007238101490193837</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1693,43 +1693,43 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1412678730771366</v>
+        <v>0.08879437573964823</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2019682868638971</v>
+        <v>0.1746593087602454</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4480098367810685</v>
+        <v>0.1282470092785314</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1546799415391678</v>
+        <v>0.04564770883860726</v>
       </c>
       <c r="O12" t="n">
-        <v>4.107460678751526</v>
+        <v>4.097766389364954</v>
       </c>
       <c r="P12" t="n">
-        <v>4.144149158510897</v>
+        <v>4.131509223078499</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.929877234201177</v>
+        <v>0.9374658109723982</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02881985736448468</v>
+        <v>0.02721579778643543</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.6293097996850736</v>
+        <v>0.6627995038929626</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.06018391770866419</v>
+        <v>0.05740094005994648</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9999990590726391</v>
+        <v>0.9999754420751035</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.277975897483368e-06</v>
+        <v>1.163769334701753e-05</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.827615163862876</v>
+        <v>0.8966686840879367</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01569976228873287</v>
+        <v>0.01215512772372276</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.6070525076138443</v>
+        <v>0.2603169521474478</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002723467197405642</v>
+        <v>0.003736609577648683</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9863797829479125</v>
+        <v>0.9948751801812045</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002360847072940297</v>
+        <v>0.0001448155310808671</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1797,43 +1797,43 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3156537929037181</v>
+        <v>0.2601628982742144</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2727234995589771</v>
+        <v>0.2410390490267107</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4871019817900795</v>
+        <v>0.4545616435388495</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1531391470086671</v>
+        <v>0.1288765159602824</v>
       </c>
       <c r="O13" t="n">
-        <v>4.29263277483161</v>
+        <v>4.286409256864677</v>
       </c>
       <c r="P13" t="n">
-        <v>4.506444969616558</v>
+        <v>4.510634440505953</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9975793876351416</v>
+        <v>0.9977815046005126</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002815498819932141</v>
+        <v>0.002695392356005711</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.7081090287200391</v>
+        <v>0.7764168867464913</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.004259622302234096</v>
+        <v>0.003728037383133207</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9751358007314065</v>
+        <v>0.9840390514679125</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001207586578590338</v>
+        <v>9.675209713182953e-05</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6862439360528628</v>
+        <v>0.6639080225003237</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004005510885978173</v>
+        <v>0.004145633678834814</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9998149681037549</v>
+        <v>0.9999237310931569</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0005495499547685099</v>
+        <v>0.0003528236095108787</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9502040943750705</v>
+        <v>0.9504250916364856</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002264968124186884</v>
+        <v>0.002259936496279094</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1901,43 +1901,43 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2068452432900554</v>
+        <v>0.1445754358802914</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3493200022684957</v>
+        <v>0.2523281648239149</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6195338597130369</v>
+        <v>0.08546802250920016</v>
       </c>
       <c r="N14" t="n">
-        <v>0.597394995122581</v>
+        <v>0.1300729067506982</v>
       </c>
       <c r="O14" t="n">
-        <v>4.429062464935388</v>
+        <v>4.413656766676655</v>
       </c>
       <c r="P14" t="n">
-        <v>4.375434175866124</v>
+        <v>4.355983827854987</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9725129024218548</v>
+        <v>0.9707329598416724</v>
       </c>
       <c r="R14" t="n">
-        <v>0.009873238160145889</v>
+        <v>0.01018789763574823</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9061809377475295</v>
+        <v>0.8930089262682152</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01522926580940525</v>
+        <v>0.01626324467539341</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.9614806109789746</v>
+        <v>0.9598394503726968</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.000962512285506089</v>
+        <v>0.0009828028574754293</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9736439467993553</v>
+        <v>0.9849769846568868</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.007016315186863646</v>
+        <v>0.005297213261815634</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.6035602401048978</v>
+        <v>0.5648408196878816</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01422796682262591</v>
+        <v>0.01490659039136743</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.2602242228314636</v>
+        <v>0.1686631145976666</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001698079248556434</v>
+        <v>0.001800099140848878</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2005,25 +2005,25 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1895470751595914</v>
+        <v>0.1316028009711741</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2933197078177879</v>
+        <v>0.2398210285828282</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.12729937470144</v>
+        <v>4.10389600519784</v>
       </c>
       <c r="P15" t="n">
-        <v>4.250834185958639</v>
+        <v>4.229309989855801</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.975807779438401</v>
+        <v>0.9723719010837693</v>
       </c>
       <c r="R15" t="n">
-        <v>0.008219804688209677</v>
+        <v>0.008784137649752883</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9197776878023943</v>
+        <v>0.9122309846182808</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01394674247539276</v>
+        <v>0.01458800181605403</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-0.5405604309778897</v>
+        <v>-0.2793519889950717</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003247874635409145</v>
+        <v>0.00295974920418698</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9498627388268558</v>
+        <v>0.9341697294443785</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.008199056085422594</v>
+        <v>0.009394991091547898</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.656548015171428</v>
+        <v>0.5988272842315192</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.006558915762710387</v>
+        <v>0.007088669615262781</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999995770694698</v>
+        <v>0.999999309430799</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.406544089539302e-06</v>
+        <v>3.075125948709012e-06</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2109,25 +2109,25 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5109637156163565</v>
+        <v>0.5058025943758175</v>
       </c>
       <c r="L16" t="n">
-        <v>0.524826409861138</v>
+        <v>0.5112679067249624</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.305324632016705</v>
+        <v>4.349769392665977</v>
       </c>
       <c r="P16" t="n">
-        <v>4.498954160381471</v>
+        <v>4.494212568469672</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9758602116143378</v>
+        <v>0.9780806864735132</v>
       </c>
       <c r="R16" t="n">
-        <v>0.00944994150527813</v>
+        <v>0.009004837194415022</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9937953635733858</v>
+        <v>0.9931187910124818</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005806607172569121</v>
+        <v>0.006115002670665429</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9584743548070799</v>
+        <v>0.9606768476260641</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.00420002056613056</v>
+        <v>0.004087119968068924</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9091355120823432</v>
+        <v>0.9586049850166881</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003619397056548504</v>
+        <v>0.002442942018882891</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8429217642719108</v>
+        <v>0.8581194634580227</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01795872530642704</v>
+        <v>0.01706785368915487</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2211,43 +2211,43 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2121923977296436</v>
+        <v>0.1560962956401372</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2664672949231575</v>
+        <v>0.2175514994452316</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1529464524077458</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02411179959695135</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.89038661935276</v>
+        <v>3.850449758009987</v>
       </c>
       <c r="P17" t="n">
-        <v>4.034503076205769</v>
+        <v>4.003179503233808</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9892950906979096</v>
+        <v>0.989395773756511</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00480273406151811</v>
+        <v>0.004780095086875108</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9677225250352443</v>
+        <v>0.9671886010536744</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.009038203061573959</v>
+        <v>0.009112650025133584</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.7035253385502881</v>
+        <v>0.7637638902948169</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001683993234410675</v>
+        <v>0.001503210125636759</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9979228475699531</v>
+        <v>0.9951995204429213</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001232565212302445</v>
+        <v>0.001873777567383604</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>-0.08572685842334082</v>
+        <v>0.06028482131748891</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005362213942646315</v>
+        <v>0.004988637692951708</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9942949301299103</v>
+        <v>0.9941325061227066</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.000730595074755317</v>
+        <v>0.0007409221496791715</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2315,25 +2315,25 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.24258952682581</v>
+        <v>0.181582972876025</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2659670730655396</v>
+        <v>0.2290876771575064</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.300562681691318</v>
+        <v>4.287479093745305</v>
       </c>
       <c r="P18" t="n">
-        <v>4.300546436141598</v>
+        <v>4.290293133107553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9827320056158617</v>
+        <v>0.9834307340455976</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006796096428215015</v>
+        <v>0.006657178736919413</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9166678208924395</v>
+        <v>0.9188971460343478</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0148244604909142</v>
+        <v>0.01462482226341714</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.9869877379734456</v>
+        <v>0.9950960822804436</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0003141843593608251</v>
+        <v>0.0001928766918933566</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9954260882605082</v>
+        <v>0.997063837665212</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.002029903004613332</v>
+        <v>0.001626377754650541</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9756653168228163</v>
+        <v>0.9825587128979482</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002624355639990265</v>
+        <v>0.002221770049806808</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9955281379648904</v>
+        <v>0.9939373011154781</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002520791866744827</v>
+        <v>0.0002935119530814854</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2419,25 +2419,25 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1618647634163979</v>
+        <v>0.1080512787950732</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2266520304402777</v>
+        <v>0.1790722548535144</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.01013022703957</v>
+        <v>4.009989320724906</v>
       </c>
       <c r="P19" t="n">
-        <v>4.378894525126992</v>
+        <v>4.367861340697792</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9880043984450059</v>
+        <v>0.9874880419236483</v>
       </c>
       <c r="R19" t="n">
-        <v>0.007716763050895845</v>
+        <v>0.007881099117136484</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6261862384808998</v>
+        <v>0.6061652585070408</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.009103614075635955</v>
+        <v>0.009344223277594219</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.02407581613210419</v>
+        <v>-0.08336883317022514</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003014901415834792</v>
+        <v>0.003100953324724859</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7666055143525095</v>
+        <v>0.7548656808224014</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01363561504322373</v>
+        <v>0.01397434611544685</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.8511452672964697</v>
+        <v>0.8624702772165457</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004451167641450874</v>
+        <v>0.00427849384267343</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9960400729158702</v>
+        <v>0.9952810327469641</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001839813951152159</v>
+        <v>0.0002008416562685653</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2523,25 +2523,25 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.270337140109575</v>
+        <v>0.2057008732256997</v>
       </c>
       <c r="L20" t="n">
-        <v>0.306474044431695</v>
+        <v>0.2526578928640004</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.622332151259288</v>
+        <v>4.630704694731168</v>
       </c>
       <c r="P20" t="n">
-        <v>4.589270355176144</v>
+        <v>4.594532944806889</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9761708549923681</v>
+        <v>0.9754314623975737</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009062832131237158</v>
+        <v>0.009202362966604805</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8787468901710448</v>
+        <v>0.8760234864453152</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01014413226734182</v>
+        <v>0.01025742073304349</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.8252929229952188</v>
+        <v>0.8598776904134131</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.002852094885726183</v>
+        <v>0.002554243898056018</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9733227802322076</v>
+        <v>0.9633945976303636</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.004358380596989807</v>
+        <v>0.00510537282433304</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7922480009568221</v>
+        <v>0.7885841436497428</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01673806506865897</v>
+        <v>0.01688501398373737</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4651814554570201</v>
+        <v>0.4298738448077102</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006917100762121532</v>
+        <v>0.0007141778166719271</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2627,25 +2627,25 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1205682193591666</v>
+        <v>0.07288078000139452</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1424141123167814</v>
+        <v>0.1367673415201617</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.116445283604787</v>
+        <v>4.177714502255803</v>
       </c>
       <c r="P21" t="n">
-        <v>4.120922169320235</v>
+        <v>4.130381200405711</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8640998623691123</v>
+        <v>0.7989176483960193</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02399112699908035</v>
+        <v>0.02918284840588656</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9562227590827219</v>
+        <v>0.9722703901857831</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.008218867471995793</v>
+        <v>0.006541233651922158</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9945489868070292</v>
+        <v>0.9887950074904146</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.002437109695667851</v>
+        <v>0.003494155642657436</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-4.073243951911832</v>
+        <v>-6.945409851308082</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.04933460861720036</v>
+        <v>0.06174004864604357</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>-0.2741046317810907</v>
+        <v>-0.3456658601142357</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01923535852204688</v>
+        <v>0.0197681648706782</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.552524461766148</v>
+        <v>0.4558915442913252</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0006920710621326452</v>
+        <v>0.000763148013481959</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2731,43 +2731,43 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3067591657776431</v>
+        <v>0.2533994605117408</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3269574459399416</v>
+        <v>0.27968496220302</v>
       </c>
       <c r="M22" t="n">
-        <v>0.07207061126445224</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.007562505240968262</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.138954932523397</v>
+        <v>4.12741070069084</v>
       </c>
       <c r="P22" t="n">
-        <v>4.309908832298483</v>
+        <v>4.297532263907768</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9818437140563175</v>
+        <v>0.9813794767452618</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006811447925080798</v>
+        <v>0.006897979101460696</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8917331967060136</v>
+        <v>0.8948923903623964</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009700559253528265</v>
+        <v>0.009557981711974761</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9298890734304983</v>
+        <v>0.8824736985539618</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001467616685381284</v>
+        <v>0.001900147531612422</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3544965210653147</v>
+        <v>0.3206820783252198</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01108933686586766</v>
+        <v>0.01137608476929768</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9569179653026106</v>
+        <v>0.9534285454374214</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002972040005860154</v>
+        <v>0.003090056693940743</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.7808100365588875</v>
+        <v>0.7772689070465226</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001979381644072312</v>
+        <v>0.001995306573584923</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2835,43 +2835,43 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2857369714597892</v>
+        <v>0.236563796036645</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2866934206494559</v>
+        <v>0.2489721025718278</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2605396243220668</v>
+        <v>0.296793595790445</v>
       </c>
       <c r="N23" t="n">
-        <v>0.04730702081302307</v>
+        <v>0.04839832599250853</v>
       </c>
       <c r="O23" t="n">
-        <v>3.863757349446638</v>
+        <v>3.857771998428968</v>
       </c>
       <c r="P23" t="n">
-        <v>4.119433225787591</v>
+        <v>4.098774036820456</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9816360588359564</v>
+        <v>0.983129227521609</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01014545433388278</v>
+        <v>0.009724248270060859</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.896802137294897</v>
+        <v>0.9056711561539066</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02252104597331774</v>
+        <v>0.02153155828736749</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.5891385377725162</v>
+        <v>-0.4694832932340054</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001203831826219805</v>
+        <v>0.001157623321063894</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9789667274992588</v>
+        <v>0.9733198291733706</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002442722243105279</v>
+        <v>0.002751154394675184</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9907196448458544</v>
+        <v>0.8941716092291691</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0001564048293483361</v>
+        <v>0.0005281642015110802</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9993945602018566</v>
+        <v>0.9995798115717722</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.000114634108312047</v>
+        <v>9.54993509655643e-05</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2939,25 +2939,25 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3899491530645845</v>
+        <v>0.3438194492405634</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4733730306956111</v>
+        <v>0.4370754758342919</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.330915049849626</v>
+        <v>4.306058852366302</v>
       </c>
       <c r="P24" t="n">
-        <v>4.386274849460652</v>
+        <v>4.362205987875905</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9946398898416594</v>
+        <v>0.9924754700166334</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004347839465796365</v>
+        <v>0.005151412552851958</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9995320269809053</v>
+        <v>0.9998174282838287</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.001735933064475865</v>
+        <v>0.001084274681937463</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9572293091745959</v>
+        <v>0.9533619187960144</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003265292013805306</v>
+        <v>0.003409724033920006</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8876443399180077</v>
+        <v>0.833920957804832</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.008260491953133008</v>
+        <v>0.01004305527790222</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9998960457205744</v>
+        <v>0.9708841993311144</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6.888570670350077e-05</v>
+        <v>0.001152848660305331</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3041,25 +3041,25 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2158934749426978</v>
+        <v>0.1556531723472595</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2288284659952428</v>
+        <v>0.179981678237344</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.311008836928643</v>
+        <v>4.318162033299422</v>
       </c>
       <c r="P25" t="n">
-        <v>4.340714662475478</v>
+        <v>4.341427466773419</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9846063623632936</v>
+        <v>0.9853071365363835</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02057664286603977</v>
+        <v>0.02010282591377737</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.1671293684514767</v>
+        <v>-0.1010552173370118</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03977521829467955</v>
+        <v>0.03863292782602717</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.5396289014954936</v>
+        <v>0.5625258423556363</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0008609345866895428</v>
+        <v>0.0008392518966037371</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.891680711966246</v>
+        <v>0.8851903906322472</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0113459747168711</v>
+        <v>0.01168094643692828</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.6599589366982943</v>
+        <v>0.5179388739532054</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.002857679578878689</v>
+        <v>0.003402506033728945</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9812367192575829</v>
+        <v>0.8905160488125115</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.002243846283148287</v>
+        <v>0.00542018298426477</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9706334713670406</v>
+        <v>0.858321224010683</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001070340289688523</v>
+        <v>0.002350974698048462</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.02254649128062214</v>
+        <v>-0.01505143120291974</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003348519211457814</v>
+        <v>0.003336224627519976</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3153,25 +3153,25 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.319605401855295</v>
+        <v>0.2654673820478013</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3068276294006985</v>
+        <v>0.2648773224868717</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.221808346553291</v>
+        <v>4.203760876198466</v>
       </c>
       <c r="P26" t="n">
-        <v>4.299156165421864</v>
+        <v>4.287796380406703</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9811515580484123</v>
+        <v>0.981881702079807</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0211020698554135</v>
+        <v>0.02068931092760875</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.3137369123292557</v>
+        <v>0.3413798759521499</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04068166947802393</v>
+        <v>0.03985391087389716</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.3054739183158917</v>
+        <v>-0.3217583309895442</v>
       </c>
       <c r="X26" t="n">
-        <v>0.000800965949823007</v>
+        <v>0.0008059460709795743</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9472173182030595</v>
+        <v>0.9476588692718971</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01240361562780566</v>
+        <v>0.01235162572699503</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.238405234485211</v>
+        <v>-0.236966017219387</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.003815708295467274</v>
+        <v>0.003813490431085914</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9126467246914984</v>
+        <v>0.9082374109049972</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.00395615202870477</v>
+        <v>0.004054769803590008</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9823701306252515</v>
+        <v>0.9828872426332702</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001129495418667469</v>
+        <v>0.001112807196600675</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.4634037693418636</v>
+        <v>0.4357263571757508</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.001015064242503256</v>
+        <v>0.00104091340858113</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3265,25 +3265,25 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2452896402637705</v>
+        <v>0.1860906494832026</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3101309629421319</v>
+        <v>0.2607653987707845</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.171003209011483</v>
+        <v>4.150022463863345</v>
       </c>
       <c r="P27" t="n">
-        <v>4.149301127182595</v>
+        <v>4.128570591900765</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9964015897120301</v>
+        <v>0.9964395706014962</v>
       </c>
       <c r="R27" t="n">
-        <v>0.00973606525155314</v>
+        <v>0.009684547312754982</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9008776392057188</v>
+        <v>0.9021838115673453</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01652749952230578</v>
+        <v>0.01641824388675052</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.6590828011894931</v>
+        <v>0.7273096774152902</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0006543294148296382</v>
+        <v>0.0005852034142300281</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.9235728252701322</v>
+        <v>0.9268511346765662</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.0117228544635618</v>
+        <v>0.01146867556174578</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.9298164463228387</v>
+        <v>0.954722055955601</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0009687601899360537</v>
+        <v>0.0007781117179898312</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.9014770953294831</v>
+        <v>0.8954597434535414</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.008768388881661288</v>
+        <v>0.009032188262673085</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.625950300483904</v>
+        <v>0.5861519284753167</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.003294960315557175</v>
+        <v>0.003465819961290841</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4377434781411439</v>
+        <v>0.4409162238694539</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004882390264761079</v>
+        <v>0.004868595415099214</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3377,25 +3377,25 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3983433844077345</v>
+        <v>0.3628997599405132</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4052908569416904</v>
+        <v>0.3889457506766575</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.109024519998804</v>
+        <v>4.105048742406989</v>
       </c>
       <c r="P28" t="n">
-        <v>4.290280345970089</v>
+        <v>4.285679441466086</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9429312535765202</v>
+        <v>0.9417275840405985</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02487727583761871</v>
+        <v>0.02513825730940722</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6035707802519461</v>
+        <v>0.5942104530148915</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05159209813149845</v>
+        <v>0.05219763052410342</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.8422662425991353</v>
+        <v>0.7821617319660152</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.004750062976255752</v>
+        <v>0.005582183805071616</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.522085242763175</v>
+        <v>0.5395062491534799</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01155634975994717</v>
+        <v>0.01134376776304701</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.4026817583656148</v>
+        <v>0.4008925018139573</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01679437653107811</v>
+        <v>0.01681951134692959</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9893995304586048</v>
+        <v>0.9900161165015631</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003564398182264405</v>
+        <v>0.0003459182018541039</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3483,25 +3483,25 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5340055862294603</v>
+        <v>0.5406426407248554</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3537813427846556</v>
+        <v>0.5159633858091727</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.257333241600258</v>
+        <v>4.311389929681745</v>
       </c>
       <c r="P29" t="n">
-        <v>4.212624139423042</v>
+        <v>4.268928312171505</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9513053116423515</v>
+        <v>0.9367424776906661</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01423996307855831</v>
+        <v>0.01623021064203043</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7860660146354843</v>
+        <v>0.7166297277960055</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03014057525530507</v>
+        <v>0.03468876108814913</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9301519174395692</v>
+        <v>0.9296525780633477</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009154115532989501</v>
+        <v>0.009186778343636718</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6855713830580368</v>
+        <v>0.6586437614714842</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.00792555410044218</v>
+        <v>0.008257955166226995</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9907652346544472</v>
+        <v>0.9635099446641047</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.00249689252581046</v>
+        <v>0.004963341723281445</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9080252017825244</v>
+        <v>0.9321117304022962</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001809942407007152</v>
+        <v>0.001554990366296473</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3589,43 +3589,43 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5325113215269579</v>
+        <v>0.5203645174949575</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4062765831598397</v>
+        <v>0.4552969850969608</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1181929947757944</v>
+        <v>0.1794523734564147</v>
       </c>
       <c r="N30" t="n">
-        <v>0.005458007710319151</v>
+        <v>0.01098532522112199</v>
       </c>
       <c r="O30" t="n">
-        <v>4.515704212940665</v>
+        <v>4.521684421917743</v>
       </c>
       <c r="P30" t="n">
-        <v>4.31409232898503</v>
+        <v>4.32183717215381</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9728781180226278</v>
+        <v>0.972057998118064</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01357456119407297</v>
+        <v>0.01377826862242246</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8627321261241871</v>
+        <v>0.8563254057647731</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02523645817753093</v>
+        <v>0.02581867434391722</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9990233779304795</v>
+        <v>0.9984882712176338</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0001408301558090145</v>
+        <v>0.000175214217600106</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>0.09867875886578292</v>
+        <v>0.06866441750329477</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01283903205214726</v>
+        <v>0.01305105379720088</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.840592691875899</v>
+        <v>0.8603306103138426</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.008356575147451356</v>
+        <v>0.007822126358414059</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.4864491043803056</v>
+        <v>0.5011387491969093</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001927316790650695</v>
+        <v>0.001899552243963621</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3695,25 +3695,25 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4901448304506785</v>
+        <v>0.4758642080817636</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4307390966259112</v>
+        <v>0.440730465403657</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.249026147841872</v>
+        <v>4.25445111063005</v>
       </c>
       <c r="P31" t="n">
-        <v>4.408534161760072</v>
+        <v>4.406586360079447</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9859673610844005</v>
+        <v>0.9863371577821206</v>
       </c>
       <c r="R31" t="n">
-        <v>0.007736175110345476</v>
+        <v>0.007633560343934555</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9455034404592624</v>
+        <v>0.9478575063333322</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01246871603733657</v>
+        <v>0.01219644018026552</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8982920028100511</v>
+        <v>0.9078559546203802</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.007764238466934059</v>
+        <v>0.007390178906657691</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>0.1038843795345048</v>
+        <v>0.06387997556877245</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.008607497454891309</v>
+        <v>0.008797527826739641</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.968753259220473</v>
+        <v>0.9706691252251705</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002773780852337383</v>
+        <v>0.002687399858427753</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05028342485048809</v>
+        <v>0.03637723251015268</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004096062156338966</v>
+        <v>0.004125941406032561</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3801,25 +3801,25 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003028185540506</v>
+        <v>0.4784031200138491</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4274308509856222</v>
+        <v>0.439342754298783</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.530139452862152</v>
+        <v>4.543747350314697</v>
       </c>
       <c r="P32" t="n">
-        <v>4.426225949150417</v>
+        <v>4.42327411692884</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9797467054705858</v>
+        <v>0.9797145492792403</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01370382441077479</v>
+        <v>0.01371469888950881</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.9022466566662836</v>
+        <v>0.8829612493193515</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.008917052857534644</v>
+        <v>0.009757091318487524</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2271863060437095</v>
+        <v>0.2241076532917549</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01744997981613056</v>
+        <v>0.01748470300064492</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.5308905534094654</v>
+        <v>-0.5407369447280272</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01573490262979552</v>
+        <v>0.01578542348501133</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.2304359754871046</v>
+        <v>0.2695019688636628</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01817663362550467</v>
+        <v>0.01770926756719963</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.0737867155481069</v>
+        <v>0.07979660580422476</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004891821777688604</v>
+        <v>0.004875925263071819</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3905,25 +3905,25 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2845720576653915</v>
+        <v>0.2253351707878397</v>
       </c>
       <c r="L33" t="n">
-        <v>0.309385953827798</v>
+        <v>0.2836881609170623</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.300519149462805</v>
+        <v>4.284692602034447</v>
       </c>
       <c r="P33" t="n">
-        <v>4.268926255577062</v>
+        <v>4.261159703030888</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9652966305421057</v>
+        <v>0.9631504538818184</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005909989698078893</v>
+        <v>0.006089995523445896</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.930858457618045</v>
+        <v>0.9266112143651719</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0106254560993633</v>
+        <v>0.01094694410000108</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.1217477747227871</v>
+        <v>-0.01301735255472813</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006014100569510049</v>
+        <v>0.006459062645712495</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.8596925635331981</v>
+        <v>0.8628040376576007</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.004467946433780625</v>
+        <v>0.004418127832775455</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7777413070225867</v>
+        <v>0.8298583952955196</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002236977416460872</v>
+        <v>0.001957210252354471</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3825736347723331</v>
+        <v>0.4530862169841673</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0007768879458624871</v>
+        <v>0.0007311815571399508</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4009,25 +4009,25 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5337173211659239</v>
+        <v>0.5349204065807047</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4597037194164731</v>
+        <v>0.5196710249322933</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.254011730907492</v>
+        <v>4.266981556961285</v>
       </c>
       <c r="P34" t="n">
-        <v>4.289569332936278</v>
+        <v>4.30879922454559</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.884790543811793</v>
+        <v>0.9359184571647376</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02366988660435418</v>
+        <v>0.01765300294935502</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.8106991218732373</v>
+        <v>0.8973782844154106</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.0520844278401577</v>
+        <v>0.03834875056764673</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9906423490482188</v>
+        <v>0.9933416258310109</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.00228827379840637</v>
+        <v>0.001930228243301977</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.7096376348842103</v>
+        <v>0.7224700749082362</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004148328667916342</v>
+        <v>0.004055626075440664</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4581789492888363</v>
+        <v>0.4521431696809568</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.008170851925575123</v>
+        <v>0.008216236725118377</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.3318348959972142</v>
+        <v>0.1884799510435298</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0007946296113580733</v>
+        <v>0.000875734525807103</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4115,25 +4115,25 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3017567405934108</v>
+        <v>0.2503626538263644</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2447387101592386</v>
+        <v>0.2453617369460943</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.047146068348874</v>
+        <v>4.042303821541178</v>
       </c>
       <c r="P35" t="n">
-        <v>4.155126683074013</v>
+        <v>4.150547923019706</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9967899421229967</v>
+        <v>0.9960908700017697</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005644304220467496</v>
+        <v>0.006228651593670391</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9820833025179087</v>
+        <v>0.9736807264410772</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.007304212900817048</v>
+        <v>0.008852815067839881</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6763340926124476</v>
+        <v>0.658123933994359</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.00849634769774184</v>
+        <v>0.008732088884506835</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7315717490061899</v>
+        <v>0.7252724679452519</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002093706884864355</v>
+        <v>0.002118131219592847</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5251730074787959</v>
+        <v>0.4990580597081085</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002339693194615889</v>
+        <v>0.002403172298119602</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4217,25 +4217,25 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4303510992459229</v>
+        <v>0.3952543891983995</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3940041415817687</v>
+        <v>0.374846467773324</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.305403694774172</v>
+        <v>4.294431636644179</v>
       </c>
       <c r="P36" t="n">
-        <v>4.320738530966725</v>
+        <v>4.313974128141081</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9836102967342929</v>
+        <v>0.9833676561162499</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01160072774237137</v>
+        <v>0.01168628347461962</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8065746744763604</v>
+        <v>0.7999614290772936</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01911824699751956</v>
+        <v>0.01944232826491277</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.367525906756115</v>
+        <v>0.3887434750196476</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008158189811100849</v>
+        <v>0.008020181463785039</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.1028198803448294</v>
+        <v>0.1072239133883213</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01321520718857418</v>
+        <v>0.01318273226316066</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7311364352005947</v>
+        <v>0.7363838781743055</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006074526980104867</v>
+        <v>0.006014956256179966</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1631199438672212</v>
+        <v>0.1481979617625339</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004045442975723871</v>
+        <v>0.004081349744541902</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4323,25 +4323,25 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1033156315000568</v>
+        <v>0.05739037544262496</v>
       </c>
       <c r="L37" t="n">
-        <v>0.105989240617094</v>
+        <v>0.07228330439348842</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.2322895226395</v>
+        <v>4.220030963149969</v>
       </c>
       <c r="P37" t="n">
-        <v>4.263467469259709</v>
+        <v>4.254859614301782</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9932355178273524</v>
+        <v>0.9930230072873667</v>
       </c>
       <c r="R37" t="n">
-        <v>0.005480321633666626</v>
+        <v>0.005565739859991835</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>0.03028582223180765</v>
+        <v>0.1026155043353122</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0004212794289776973</v>
+        <v>0.0004052636591472696</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9983483979738434</v>
+        <v>0.9987582652911129</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.001929489290990243</v>
+        <v>0.001673031350135655</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.5024649171995881</v>
+        <v>-0.5171799534715542</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.007760966051537448</v>
+        <v>0.007798878523200177</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9137853380899765</v>
+        <v>0.9094781454965661</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009555251799096498</v>
+        <v>0.009791028018575766</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9403141793133138</v>
+        <v>0.9302063765600646</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.002191861491347629</v>
+        <v>0.002370202181982599</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999997601921665</v>
+        <v>0.9999993435116497</v>
       </c>
       <c r="AM37" t="n">
-        <v>4.82044827755296e-07</v>
+        <v>7.975708171174633e-07</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4431,25 +4431,25 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1414949912042679</v>
+        <v>0.08860067203198282</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1088639589686587</v>
+        <v>0.07293721235908138</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.109497407226164</v>
+        <v>4.08380765192147</v>
       </c>
       <c r="P38" t="n">
-        <v>4.195433165024799</v>
+        <v>4.186533632916368</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9539271641807503</v>
+        <v>0.9589362293045761</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01204405302805255</v>
+        <v>0.01137050096935783</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.1847479057418968</v>
+        <v>0.02361633944584107</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001183485861193669</v>
+        <v>0.001295171752197655</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.8115797081627778</v>
+        <v>0.8474225581793295</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02093605519128235</v>
+        <v>0.01883979547072534</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.3873194027207028</v>
+        <v>-0.3385750184694458</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01709559825877765</v>
+        <v>0.01679257981986883</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9651012801458784</v>
+        <v>0.9432759963134295</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.004336395720794464</v>
+        <v>0.005528503570625018</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-1.138275440562116</v>
+        <v>-0.917704313608851</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.004830441356116479</v>
+        <v>0.004574523254234405</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.999997220570763</v>
+        <v>0.9999949787051727</v>
       </c>
       <c r="AM38" t="n">
-        <v>6.681830546054594e-07</v>
+        <v>8.98101701931208e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4539,25 +4539,25 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514588065490762</v>
+        <v>0.09603082938732513</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1342714605126339</v>
+        <v>0.0975585124493681</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.258033543989585</v>
+        <v>4.238213191185915</v>
       </c>
       <c r="P39" t="n">
-        <v>4.266349377449965</v>
+        <v>4.257540678441487</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9827773649056697</v>
+        <v>0.9836023776255305</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008784249967092275</v>
+        <v>0.008571272963500078</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8822854639021227</v>
+        <v>0.8975048503453751</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01148328677211925</v>
+        <v>0.01071526262419945</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.1222420223291134</v>
+        <v>0.1061210277456606</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001393862708387718</v>
+        <v>0.001406604384784172</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.06332093944888362</v>
+        <v>-0.05969536745992166</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01476991972384337</v>
+        <v>0.01474471795802389</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7529487446492968</v>
+        <v>0.7587896540650656</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005393669392982733</v>
+        <v>0.005329528093693399</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1190897937720492</v>
+        <v>-0.1104749122313691</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002182730150903738</v>
+        <v>0.002174312468376622</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4643,43 +4643,43 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3692825186777028</v>
+        <v>0.3243370001581284</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4127346472607966</v>
+        <v>0.3987808216330879</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3771697981355325</v>
+        <v>0.3382530463189636</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05232942382546467</v>
+        <v>0.03990262771502921</v>
       </c>
       <c r="O40" t="n">
-        <v>4.29006395973414</v>
+        <v>4.313508293409634</v>
       </c>
       <c r="P40" t="n">
-        <v>4.521409058919988</v>
+        <v>4.514107931481615</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9912030911818219</v>
+        <v>0.991753903735568</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005633847793566522</v>
+        <v>0.005454617037753072</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.965387094706591</v>
+        <v>0.9696186372119666</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.01122743965359422</v>
+        <v>0.01051877893166299</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.9312082056342028</v>
+        <v>0.96119135668498</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0005966927393884434</v>
+        <v>0.0004481740069628622</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9797130183523861</v>
+        <v>0.9805558636193871</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003577601961174649</v>
+        <v>0.003502495861090487</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9982048374156118</v>
+        <v>0.9946573787002626</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.001902736220316332</v>
+        <v>0.003282493593633902</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999999578493531</v>
+        <v>0.9999998618343721</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.248314024826898e-07</v>
+        <v>2.260069167787376e-07</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4747,25 +4747,25 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2578830227728073</v>
+        <v>0.1959685484207236</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2872185449577517</v>
+        <v>0.2458536912225803</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.435303441664242</v>
+        <v>4.442693945177335</v>
       </c>
       <c r="P41" t="n">
-        <v>4.505579411018814</v>
+        <v>4.502759779420948</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9938802513594176</v>
+        <v>0.993649385023967</v>
       </c>
       <c r="R41" t="n">
-        <v>0.006062919450929456</v>
+        <v>0.006176221997767967</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8651957122863032</v>
+        <v>0.8666687699358036</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01069200307598809</v>
+        <v>0.01063342481970775</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.6519291125382181</v>
+        <v>0.6752164154814844</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001471316881064028</v>
+        <v>0.00142124648268689</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.981326285006654</v>
+        <v>0.9741343885202679</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.003664006404089967</v>
+        <v>0.00431223317106709</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9491779253928917</v>
+        <v>0.9461314491228436</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.007268032423408722</v>
+        <v>0.007482699554816799</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.9001785179227288</v>
+        <v>0.9010471595969356</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.00103054352839569</v>
+        <v>0.001026049861522908</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4851,43 +4851,43 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3188781726443401</v>
+        <v>0.2600786066317703</v>
       </c>
       <c r="L42" t="n">
-        <v>0.437307270969239</v>
+        <v>0.3998306884293399</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1135544113824459</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.00667021924092833</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.54271279036458</v>
+        <v>4.567760363662879</v>
       </c>
       <c r="P42" t="n">
-        <v>4.559278581803332</v>
+        <v>4.548212925879714</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9638135343907865</v>
+        <v>0.9570215456452013</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01259715364967972</v>
+        <v>0.01372855220491212</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8185358813445799</v>
+        <v>0.8070315351170408</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02337693646935403</v>
+        <v>0.02410656802374577</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9955745415084517</v>
+        <v>0.9531091451321457</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0003555572468164497</v>
+        <v>0.00115737600458301</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.8525155408946281</v>
+        <v>0.7316639101471062</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01120831188960674</v>
+        <v>0.0151184274902302</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9838808844814095</v>
+        <v>0.9940565438480077</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.003926242298911063</v>
+        <v>0.002384108549578743</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4953,43 +4953,43 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2438232441219792</v>
+        <v>0.1847770070587039</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3802626956790793</v>
+        <v>0.3201851347892893</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3726292806413716</v>
+        <v>0.3308639228857645</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0463039522422613</v>
+        <v>0.03565812410199521</v>
       </c>
       <c r="O43" t="n">
-        <v>4.004824234178307</v>
+        <v>3.931281342421583</v>
       </c>
       <c r="P43" t="n">
-        <v>4.257854625603513</v>
+        <v>4.236232121389937</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9413958644494801</v>
+        <v>0.9520495892645926</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01479160389108287</v>
+        <v>0.01337972853203909</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.872751047624317</v>
+        <v>0.9152411288242992</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03067829571529064</v>
+        <v>0.02503783098972313</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.722215283186465</v>
+        <v>0.7727380834711661</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002489072309950466</v>
+        <v>0.002251368948435594</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.8578717863513283</v>
+        <v>0.7403317943893686</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01194730217261699</v>
+        <v>0.01614875658923249</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.885454150100725</v>
+        <v>0.9366797271329271</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.001897246806307444</v>
+        <v>0.00141060539200616</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9831036024094448</v>
+        <v>0.9777187187894295</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0005165701759146208</v>
+        <v>0.0005932016462790607</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5057,25 +5057,25 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1750004298657557</v>
+        <v>0.1168265495049782</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3271453757894115</v>
+        <v>0.2994081960988988</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.26677501303533</v>
+        <v>4.250053691127665</v>
       </c>
       <c r="P44" t="n">
-        <v>4.389336156098157</v>
+        <v>4.370005680540043</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9436990976759149</v>
+        <v>0.9347306317150316</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008081822512133931</v>
+        <v>0.008701744665127126</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9160532059420502</v>
+        <v>0.9123185714714283</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01299266521197464</v>
+        <v>0.01327852999748711</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8046322025389985</v>
+        <v>0.8018588932526468</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004902053065829957</v>
+        <v>0.004936723576667084</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9424598499734625</v>
+        <v>0.9160373553013601</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.008389745416451655</v>
+        <v>0.01013459370535977</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.8693015582673569</v>
+        <v>0.8437560386802269</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.007853807024223858</v>
+        <v>0.008587102389063305</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.627820126103811</v>
+        <v>0.6739174048644032</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001292164498384604</v>
+        <v>0.001209498038767343</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5161,25 +5161,25 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3970700662958236</v>
+        <v>0.3530798955686953</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3275258470037932</v>
+        <v>0.438882466947964</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.224020019874794</v>
+        <v>4.170472779500921</v>
       </c>
       <c r="P45" t="n">
-        <v>4.375440194607536</v>
+        <v>4.431580090448737</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9687751708200327</v>
+        <v>0.9704543770865897</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008629986787395804</v>
+        <v>0.008394728800950511</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9762472131166755</v>
+        <v>0.977866647905786</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01318213329558572</v>
+        <v>0.01272483058369885</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9229489468869232</v>
+        <v>0.9258866503986516</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007279974266374508</v>
+        <v>0.007139844867595662</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8710034196413887</v>
+        <v>0.8713113067914287</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008535058096236186</v>
+        <v>0.008524866343177898</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9218406137914298</v>
+        <v>0.9282568240875458</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008507902407658757</v>
+        <v>0.008151212755507172</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9800276216909577</v>
+        <v>0.9822076343583939</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.000620545024227616</v>
+        <v>0.0005857000390816052</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5265,25 +5265,25 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4191548341898909</v>
+        <v>0.4067201208266214</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4168763599596889</v>
+        <v>0.4651192217474678</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.769550246054656</v>
+        <v>3.808282305100428</v>
       </c>
       <c r="P46" t="n">
-        <v>4.474246364770191</v>
+        <v>4.464640131032324</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9687411047786199</v>
+        <v>0.9755176126925588</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008429717377463572</v>
+        <v>0.007460244894914106</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9825621906838121</v>
+        <v>0.9876104445831971</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01018261717193388</v>
+        <v>0.008583043539077554</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9244883895932834</v>
+        <v>0.9394068385419058</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01019974845920663</v>
+        <v>0.009136805955219807</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9761741219411049</v>
+        <v>0.9666203419057247</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002526696065791834</v>
+        <v>0.002990676844390995</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8721008938082562</v>
+        <v>0.8984930464433223</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.0118429672374478</v>
+        <v>0.0105505395579633</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9873983451204669</v>
+        <v>0.9883591206559087</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009695608398424529</v>
+        <v>0.000931867507585639</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5369,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2534470292225203</v>
+        <v>0.1898361565792907</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3804221654864902</v>
+        <v>0.3169032945385671</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.285238971656212</v>
+        <v>4.207363086855939</v>
       </c>
       <c r="P47" t="n">
-        <v>4.355338806089541</v>
+        <v>4.332208809417659</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9499675728583342</v>
+        <v>0.9422344135229537</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008405931838519721</v>
+        <v>0.009032223420366551</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9280134275048924</v>
+        <v>0.9340796280954476</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01478316707485817</v>
+        <v>0.01414658331459803</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8095213335784225</v>
+        <v>0.8430142070877258</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.00681927485499712</v>
+        <v>0.006190777561609706</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.9145169469472024</v>
+        <v>0.8168267329271227</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.008717570094534379</v>
+        <v>0.01276105208855585</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9505309367183397</v>
+        <v>0.9738090136769656</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.003449281269043725</v>
+        <v>0.002509791788499669</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9012792860527055</v>
+        <v>0.915003322683424</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.000600285292119425</v>
+        <v>0.0005569991512027919</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5473,25 +5473,25 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1132798991704734</v>
+        <v>0.07057579079882771</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3941761000608428</v>
+        <v>0.4720007512014078</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.703826593445649</v>
+        <v>3.801459647451884</v>
       </c>
       <c r="P48" t="n">
-        <v>4.323796651864424</v>
+        <v>4.343627455556366</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9822785264617602</v>
+        <v>0.9814312171008718</v>
       </c>
       <c r="R48" t="n">
-        <v>0.006864013349149739</v>
+        <v>0.007026190546959434</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9685191461319849</v>
+        <v>0.9695301940322909</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01297383824231126</v>
+        <v>0.0127638023770996</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8641702082448598</v>
+        <v>0.8525345616848152</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.006225709681120688</v>
+        <v>0.006486889054935323</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.993280752478491</v>
+        <v>0.9892177781084788</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.004753576674794105</v>
+        <v>0.006021633461030734</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.913903805183183</v>
+        <v>0.9184292895740682</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.002424761510567896</v>
+        <v>0.002360174822177773</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9997081465432875</v>
+        <v>0.9998016291181303</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001322759577286648</v>
+        <v>0.0001090529594766197</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5577,43 +5577,43 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3643052533076485</v>
+        <v>0.3223441909441093</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4619807277903906</v>
+        <v>0.4524705173230785</v>
       </c>
       <c r="M49" t="n">
-        <v>0.08745240125860532</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0.002440444190641133</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.05609595904365</v>
+        <v>4.043607044971687</v>
       </c>
       <c r="P49" t="n">
-        <v>4.393073580436305</v>
+        <v>4.381750913413947</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9257488755932365</v>
+        <v>0.9259987085580834</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01291596308872166</v>
+        <v>0.012894215590958</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9184123146157749</v>
+        <v>0.9234620013922974</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01926704551935028</v>
+        <v>0.01866127736981387</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9450798504891054</v>
+        <v>0.9428261356784841</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002247375948841617</v>
+        <v>0.00229302424499428</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.6055279028350553</v>
+        <v>0.3775760053403944</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01159533330366054</v>
+        <v>0.01456526045341957</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3337477037096268</v>
+        <v>0.4531337396093245</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01793409560041621</v>
+        <v>0.0162480290238472</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8683230939638997</v>
+        <v>0.8757974439744302</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001325606056906469</v>
+        <v>0.001287433894821116</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5681,25 +5681,25 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5041804397675377</v>
+        <v>0.4969413621409701</v>
       </c>
       <c r="L50" t="n">
-        <v>0.527911915006419</v>
+        <v>0.5553044354690182</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.245466267633814</v>
+        <v>4.269727495470134</v>
       </c>
       <c r="P50" t="n">
-        <v>4.52016536989635</v>
+        <v>4.548757021969247</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9679338158247377</v>
+        <v>0.9678559888381575</v>
       </c>
       <c r="R50" t="n">
-        <v>0.009570953140782093</v>
+        <v>0.009582560807423363</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9948739840009695</v>
+        <v>0.9891594584304694</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.006023283624087662</v>
+        <v>0.008759288378582608</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9298759515224362</v>
+        <v>0.9333387564326594</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005642528247103462</v>
+        <v>0.005501447296656798</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.903708506244548</v>
+        <v>0.9224738018722216</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.003170343885247073</v>
+        <v>0.002844701176735095</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8068174896992218</v>
+        <v>0.8291500497736886</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.0176392803456281</v>
+        <v>0.0165883957746635</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5783,43 +5783,43 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.47819434822235</v>
+        <v>0.4799319100595422</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4658553747668711</v>
+        <v>0.5530320514064616</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1137929647244488</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.002275859294488976</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.863171910508307</v>
+        <v>3.888757795315895</v>
       </c>
       <c r="P51" t="n">
-        <v>4.49899044551241</v>
+        <v>4.438191855078272</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.8665655187706761</v>
+        <v>0.9380349752801062</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01467059524389295</v>
+        <v>0.009997398720551878</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.8599286568718753</v>
+        <v>0.9533882300368478</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.02212651951135165</v>
+        <v>0.01276398414948861</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.6731374583569512</v>
+        <v>0.7884320000375069</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01825510697949312</v>
+        <v>0.01468678698328693</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-1.462593380863944</v>
+        <v>-1.162343268271194</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003936702015983787</v>
+        <v>0.003688913822760039</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.7699674094977705</v>
+        <v>0.8960340585384622</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01539886238474701</v>
+        <v>0.01035236312321744</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9901196720142972</v>
+        <v>0.9950500031188587</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0008230686634059018</v>
+        <v>0.0005825763477143982</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5887,25 +5887,25 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1606943136811414</v>
+        <v>0.1030582047638746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3250751776916631</v>
+        <v>0.2453096720579171</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.367592709598685</v>
+        <v>4.3471512475704</v>
       </c>
       <c r="P52" t="n">
-        <v>4.305155024986907</v>
+        <v>4.280027701675652</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9535533906622496</v>
+        <v>0.9476854399683274</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01040711306755313</v>
+        <v>0.01104497033751219</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9383978124110627</v>
+        <v>0.9203373852114963</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.01136563283225358</v>
+        <v>0.01292477028628217</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.9006945621791339</v>
+        <v>0.8765969541237223</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002229254395263897</v>
+        <v>0.002485055290944442</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.8134869125326483</v>
+        <v>0.8138331205181377</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01550797518812517</v>
+        <v>0.01549357545635527</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.3887951259275094</v>
+        <v>0.2796267424050218</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01288900459740433</v>
+        <v>0.01399280449607417</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.1725753582760886</v>
+        <v>0.0508858028980399</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0008769796008777883</v>
+        <v>0.0009392571230924022</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -5991,25 +5991,25 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3301843999480366</v>
+        <v>0.2718345787311342</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2246818306660378</v>
+        <v>0.2634149802841641</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.382101377750191</v>
+        <v>4.337572452346413</v>
       </c>
       <c r="P53" t="n">
-        <v>4.425804736657819</v>
+        <v>4.430537292061633</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9866128000843535</v>
+        <v>0.9855847065833223</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004974596558670659</v>
+        <v>0.00516208003826434</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9818876075911982</v>
+        <v>0.9758571800734815</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.007799778186486004</v>
+        <v>0.009005095866673571</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.9134016594240653</v>
+        <v>0.9339715887437132</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.003020886998816808</v>
+        <v>0.002637819769958912</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9708082074032175</v>
+        <v>0.9694189581196966</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.004218210915134934</v>
+        <v>0.00431741749530783</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.964875161225224</v>
+        <v>0.9765670210422174</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.00545783318243831</v>
+        <v>0.00445786424728602</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.9805745190653832</v>
+        <v>0.9245965504993117</v>
       </c>
       <c r="AM53" t="n">
-        <v>6.172506150984947e-05</v>
+        <v>0.0001216105482566218</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6095,43 +6095,43 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2281402508795552</v>
+        <v>0.1679007494998932</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4187255501437061</v>
+        <v>0.3983691349926012</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3979237607818497</v>
+        <v>0.2307541693217291</v>
       </c>
       <c r="N54" t="n">
-        <v>0.03248303908755212</v>
+        <v>0.01713316293103193</v>
       </c>
       <c r="O54" t="n">
-        <v>4.229450565690408</v>
+        <v>4.211201045403707</v>
       </c>
       <c r="P54" t="n">
-        <v>4.317016730181986</v>
+        <v>4.295899594025704</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9271086492266981</v>
+        <v>0.9078479819992129</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009803684199211734</v>
+        <v>0.01102309979067667</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.8628589693716475</v>
+        <v>0.8452806825404316</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01907983320718</v>
+        <v>0.02026577140257138</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.4853813377876738</v>
+        <v>0.4795056211285448</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.00413699189335445</v>
+        <v>0.004160542148157754</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.9201048396836626</v>
+        <v>0.8530504026428081</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.008382563356917614</v>
+        <v>0.01136843830602679</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.8309180127913832</v>
+        <v>0.7006918680348214</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.005268973472779115</v>
+        <v>0.007010299944279351</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8413678098059159</v>
+        <v>0.8679326584957702</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001173427611867087</v>
+        <v>0.001070676721285423</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6199,43 +6199,43 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2002049545341849</v>
+        <v>0.1395613002756289</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4177854171157885</v>
+        <v>0.4408182909966935</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4823724924605222</v>
+        <v>0.4964590335539547</v>
       </c>
       <c r="N55" t="n">
-        <v>0.04521007051845333</v>
+        <v>0.05045547971736959</v>
       </c>
       <c r="O55" t="n">
-        <v>4.431189175958969</v>
+        <v>4.453912052964032</v>
       </c>
       <c r="P55" t="n">
-        <v>4.391044395531488</v>
+        <v>4.388324304267855</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8750699212537558</v>
+        <v>0.8439772314339398</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01425314662435774</v>
+        <v>0.01592836635661855</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.6933886143421923</v>
+        <v>0.6610035679232249</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02672881682489168</v>
+        <v>0.02810497215723335</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.231320963693047</v>
+        <v>0.2002206497069333</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.003838789902446569</v>
+        <v>0.003915677527778463</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.7638933575558995</v>
+        <v>0.5837905266081154</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.01556471910003466</v>
+        <v>0.02066536903705769</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.7841429670545274</v>
+        <v>0.8236907672988221</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.006635868142023708</v>
+        <v>0.005997250294209821</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.8438352090411543</v>
+        <v>0.8344396279701179</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0005475034631435092</v>
+        <v>0.0005637330606718574</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6303,25 +6303,25 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2084054602031741</v>
+        <v>0.1490350938530598</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3592757186724401</v>
+        <v>0.3125216993416861</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.062930613106723</v>
+        <v>4.00125006971951</v>
       </c>
       <c r="P56" t="n">
-        <v>4.324180579402618</v>
+        <v>4.299404185760473</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8306672697954849</v>
+        <v>0.8174901852503408</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01207382836633396</v>
+        <v>0.01253480709345885</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.6192582351611474</v>
+        <v>0.6142392245008291</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.02154333068974413</v>
+        <v>0.02168485993586439</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.06835646104013682</v>
+        <v>-0.004804287138294061</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009059098945100728</v>
+        <v>0.008785523654689277</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.7918803514418224</v>
+        <v>0.6954007335875005</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01206135537804532</v>
+        <v>0.01459163638707931</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.8368266521975809</v>
+        <v>0.8940138697282077</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.005872955389156894</v>
+        <v>0.004733219094339752</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.8782279299369821</v>
+        <v>0.8723197530774978</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001654203021133236</v>
+        <v>0.001693857307511539</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6407,25 +6407,25 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3825163888057561</v>
+        <v>0.3369187868683771</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4554652399335732</v>
+        <v>0.4317429546646928</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.276433697976676</v>
+        <v>4.255979924055767</v>
       </c>
       <c r="P57" t="n">
-        <v>4.373218250681789</v>
+        <v>4.360199978275563</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9029720440596852</v>
+        <v>0.8968403047892316</v>
       </c>
       <c r="R57" t="n">
-        <v>0.00947201819921026</v>
+        <v>0.009766728332298099</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.7789594421356788</v>
+        <v>0.7764367289373596</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01779508737129534</v>
+        <v>0.01789634602317635</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6319165373354663</v>
+        <v>0.6613530782949664</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008746476401145379</v>
+        <v>0.008389451001929902</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.861946511184812</v>
+        <v>0.7122760588478749</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.005704032275727567</v>
+        <v>0.00823467153110621</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9373334118817404</v>
+        <v>0.949724634310491</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.004606767898489069</v>
+        <v>0.004126253699102189</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6654703919347933</v>
+        <v>0.7103703286468852</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001292812890534761</v>
+        <v>0.001202928790479239</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6511,43 +6511,43 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2320109535708661</v>
+        <v>0.1709595803976834</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5055868509976839</v>
+        <v>0.504125104268745</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7681619160271811</v>
+        <v>0.6765499319055661</v>
       </c>
       <c r="N58" t="n">
-        <v>0.07581813381578009</v>
+        <v>0.08057422126127893</v>
       </c>
       <c r="O58" t="n">
-        <v>4.248034418056246</v>
+        <v>4.217413991612381</v>
       </c>
       <c r="P58" t="n">
-        <v>4.459472537524188</v>
+        <v>4.444683802700315</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9781762018213621</v>
+        <v>0.9692466668205632</v>
       </c>
       <c r="R58" t="n">
-        <v>0.00621205685806918</v>
+        <v>0.007374224420203144</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9805646181057444</v>
+        <v>0.9765703721875881</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.008088997481588048</v>
+        <v>0.008881388254209683</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9933521688508213</v>
+        <v>0.9904541418963824</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.0007504055193867859</v>
+        <v>0.0008992149462069747</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9712054223870946</v>
+        <v>0.9621052162475993</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.006520026708401621</v>
+        <v>0.00747969235142692</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.8728731733660288</v>
+        <v>0.7940500388582368</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.00914717172385575</v>
+        <v>0.01164257612340215</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9384721399962459</v>
+        <v>0.9431644191515405</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0008785012890036574</v>
+        <v>0.0008443386138854169</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6615,25 +6615,25 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4677808511850242</v>
+        <v>0.4429337950329169</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5153612643385489</v>
+        <v>0.5114740174138053</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.211580767596805</v>
+        <v>4.170892786605078</v>
       </c>
       <c r="P59" t="n">
-        <v>4.384899764120235</v>
+        <v>4.381655194938801</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7968183518500273</v>
+        <v>0.8130744715364817</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01929386090102111</v>
+        <v>0.01850594266619156</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7650175493332589</v>
+        <v>0.8069397210222856</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03038851763229069</v>
+        <v>0.02754471390780444</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4193090726360488</v>
+        <v>0.4250805879115527</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02354949960259279</v>
+        <v>0.02343217754817799</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.3572233705470572</v>
+        <v>-0.1037890286713492</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.009301085464528673</v>
+        <v>0.01218839811416335</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-0.886482971900695</v>
+        <v>-0.6248736759685991</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.0170370427512309</v>
+        <v>0.01581166374199917</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.5926203320188457</v>
+        <v>-0.4821114616609457</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002540352415209459</v>
+        <v>0.002450632985643054</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6719,25 +6719,25 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3189569329734549</v>
+        <v>0.2695921991018025</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2355319585675123</v>
+        <v>0.2153563064280021</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.034948938354199</v>
+        <v>4.021231498279722</v>
       </c>
       <c r="P60" t="n">
-        <v>4.206395293982933</v>
+        <v>4.20531273593707</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8912738908521161</v>
+        <v>0.9363902886404148</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02050876301984904</v>
+        <v>0.01568679625642222</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.6077686094538537</v>
+        <v>0.784835337458864</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.04387701686477997</v>
+        <v>0.0324976077527894</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.373376878000312</v>
+        <v>-1.457786684198819</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.00816501243654</v>
+        <v>0.008308939381095335</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.4574885809817287</v>
+        <v>0.458911623941109</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.008123009824027607</v>
+        <v>0.008112349221362352</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-8.08209179734647</v>
+        <v>-6.915135659825919</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006705459495662812</v>
+        <v>0.006259862362424788</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9362937334714371</v>
+        <v>0.9340339281176424</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004901941772152147</v>
+        <v>0.0004988125637908041</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6823,43 +6823,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4024729393044518</v>
+        <v>0.3818847677041697</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3147185593062669</v>
+        <v>0.3621326599208873</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1714814228643597</v>
+        <v>0.3342449232233369</v>
       </c>
       <c r="N61" t="n">
-        <v>0.006446242403185847</v>
+        <v>0.01708842766687407</v>
       </c>
       <c r="O61" t="n">
-        <v>3.85745491031177</v>
+        <v>3.900428030503486</v>
       </c>
       <c r="P61" t="n">
-        <v>4.244506533144418</v>
+        <v>4.261731033227699</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9753655196778852</v>
+        <v>0.9821580777271967</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01119016917151622</v>
+        <v>0.00952326284608784</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.956685130190843</v>
+        <v>0.9697354931437328</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.02319502806628342</v>
+        <v>0.01938845471031273</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.3548043462130738</v>
+        <v>0.3400525933743143</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.004354213798501604</v>
+        <v>0.004403709795482534</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.4202422457274665</v>
+        <v>0.514733219418924</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.007714702932919657</v>
+        <v>0.007058073984497965</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.9195422298362173</v>
+        <v>0.9371137935020964</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002267357604441034</v>
+        <v>0.002004535376692754</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.2464955074801776</v>
+        <v>0.2717793422320725</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002364681211973239</v>
+        <v>0.002324669254606117</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6929,43 +6929,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.42062216296563</v>
+        <v>0.3869191955124425</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2832598715655401</v>
+        <v>0.3441653785864084</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6726559183355876</v>
+        <v>0.697883262187865</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1130519136593654</v>
+        <v>0.1241712680933425</v>
       </c>
       <c r="O62" t="n">
-        <v>4.186553856872338</v>
+        <v>4.172221392446892</v>
       </c>
       <c r="P62" t="n">
-        <v>4.212795092655835</v>
+        <v>4.236064170825101</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9864343870020784</v>
+        <v>0.9874770866567498</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007681348660281562</v>
+        <v>0.007380239480953297</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9826660055783344</v>
+        <v>0.9838438404002928</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01373253315195547</v>
+        <v>0.01325776746063656</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.02956412099124472</v>
+        <v>-0.0910035699683609</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003377881687494999</v>
+        <v>0.00347720919525737</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.5074464393920112</v>
+        <v>0.5598854740943713</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.009396579682443939</v>
+        <v>0.008882309883413002</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9827161917176197</v>
+        <v>0.9870932813038721</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.00195175566210324</v>
+        <v>0.001686606035453104</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.854668696490902</v>
+        <v>0.8635217044085078</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001909834693993966</v>
+        <v>0.001850750985887181</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7035,43 +7035,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4155137200184437</v>
+        <v>0.3905045757093651</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3143500703584229</v>
+        <v>0.3652440851030533</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3416429060717733</v>
+        <v>0.4640744479634147</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0312747675505007</v>
+        <v>0.04673043063178939</v>
       </c>
       <c r="O63" t="n">
-        <v>3.974111759233877</v>
+        <v>3.982649714136</v>
       </c>
       <c r="P63" t="n">
-        <v>4.243301945649341</v>
+        <v>4.254848722862553</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9871572765446898</v>
+        <v>0.9869586171539049</v>
       </c>
       <c r="R63" t="n">
-        <v>0.00828863177306823</v>
+        <v>0.008352492666718123</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9736047488243623</v>
+        <v>0.9727830679350673</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01788968312652102</v>
+        <v>0.01816600097753112</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.9119417036210394</v>
+        <v>0.8958023238814168</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.001295775273988986</v>
+        <v>0.001409527531892498</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9296948960129381</v>
+        <v>0.9612198717815623</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.002948885261091324</v>
+        <v>0.002190125834728795</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8762629558348696</v>
+        <v>0.8868867507788493</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003137122549348875</v>
+        <v>0.002999427405872409</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.2382963231803489</v>
+        <v>0.2881570341722804</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.002015510247695989</v>
+        <v>0.001948426744847804</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7141,43 +7141,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.375704959280303</v>
+        <v>0.353961587243898</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3427459815241231</v>
+        <v>0.3763316357701335</v>
       </c>
       <c r="M64" t="n">
-        <v>0.3788280742102783</v>
+        <v>0.4463134071072126</v>
       </c>
       <c r="N64" t="n">
-        <v>0.02321061373281829</v>
+        <v>0.0287622921336397</v>
       </c>
       <c r="O64" t="n">
-        <v>3.767070855148547</v>
+        <v>3.838905402431665</v>
       </c>
       <c r="P64" t="n">
-        <v>4.246761370509985</v>
+        <v>4.261686768862483</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9737664315039619</v>
+        <v>0.9798623294384585</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01085198826870839</v>
+        <v>0.00950791402889695</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9596860270536098</v>
+        <v>0.9720387435116506</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.02120489475766767</v>
+        <v>0.01765983587269397</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.4975345627490947</v>
+        <v>0.5075354143499653</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003828110052633945</v>
+        <v>0.003789822085130346</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.2217666591183864</v>
+        <v>0.206671701734242</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.01073476684106613</v>
+        <v>0.01083837497697471</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9756437271975159</v>
+        <v>0.9800017321509857</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.0022523635810956</v>
+        <v>0.00204093546336542</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8349870499638846</v>
+        <v>0.8382770657014703</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002296164690463276</v>
+        <v>0.002273159065571581</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7247,43 +7247,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4084703604096215</v>
+        <v>0.384443089336284</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3823118048181775</v>
+        <v>0.4106563460787599</v>
       </c>
       <c r="M65" t="n">
-        <v>0.2786308939210075</v>
+        <v>0.3913686737308355</v>
       </c>
       <c r="N65" t="n">
-        <v>0.02026837493045301</v>
+        <v>0.03040638445529008</v>
       </c>
       <c r="O65" t="n">
-        <v>3.911116290363315</v>
+        <v>3.924835681335463</v>
       </c>
       <c r="P65" t="n">
-        <v>4.270253326461974</v>
+        <v>4.277590580692039</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9787942670426757</v>
+        <v>0.9775583068338</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01048912909349564</v>
+        <v>0.01079047583587439</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9650752778075267</v>
+        <v>0.9626249841838389</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02136495012024092</v>
+        <v>0.02210172117083958</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6881561642511995</v>
+        <v>0.6993324007108678</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003781392723483971</v>
+        <v>0.003713013394503661</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6381988004626431</v>
+        <v>0.6334130934183502</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008466231334322033</v>
+        <v>0.008522040711644807</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.935171339494423</v>
+        <v>0.939197807672666</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002196778006080013</v>
+        <v>0.002127464234455196</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5643088031642651</v>
+        <v>0.5793409813162057</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001886204693369114</v>
+        <v>0.001853380250321623</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7353,43 +7353,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3961978672711403</v>
+        <v>0.3670357668230109</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3297154923448143</v>
+        <v>0.3771539316868838</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3253060564144216</v>
+        <v>0.3948498300567125</v>
       </c>
       <c r="N66" t="n">
-        <v>0.01841572613194823</v>
+        <v>0.02323247143935767</v>
       </c>
       <c r="O66" t="n">
-        <v>3.958594592841257</v>
+        <v>3.971214758552318</v>
       </c>
       <c r="P66" t="n">
-        <v>4.247073921346014</v>
+        <v>4.263280966259959</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9789198334441849</v>
+        <v>0.9798022527998486</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009820431317493362</v>
+        <v>0.009612691610588395</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9666336632930527</v>
+        <v>0.9680587754358626</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01922804322023051</v>
+        <v>0.01881293724104022</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.6518611476850424</v>
+        <v>0.6583307984482367</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.003637231077236156</v>
+        <v>0.003603276286711637</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6307441892307355</v>
+        <v>0.6402462804305757</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.009284112139119612</v>
+        <v>0.009163879179501887</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.951717966850951</v>
+        <v>0.9610107663150622</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003056020921802709</v>
+        <v>0.002746223618167895</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8481154149814953</v>
+        <v>0.8535283664712932</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002157330014599404</v>
+        <v>0.002118539175409188</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7459,25 +7459,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.418401611669922</v>
+        <v>0.378033758727203</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3821256938063454</v>
+        <v>0.3948417330132951</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.381125636492835</v>
+        <v>4.371122571078349</v>
       </c>
       <c r="P67" t="n">
-        <v>4.34406181085281</v>
+        <v>4.339379530579538</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8652052824349274</v>
+        <v>0.8953818411368462</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02655512234624559</v>
+        <v>0.02339458828307652</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.8071641175971108</v>
+        <v>0.7187069804915085</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007633185508364196</v>
+        <v>0.0009219160372857722</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.6252317559356262</v>
+        <v>0.7141588546977088</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.06307984279609716</v>
+        <v>0.05508984899955284</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7694401471717121</v>
+        <v>0.6668454057309083</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.00263059201364216</v>
+        <v>0.003162165218828757</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6608983700798354</v>
+        <v>0.6538971006555838</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01277267836156645</v>
+        <v>0.01290386046948996</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8106537736777357</v>
+        <v>0.8334959102843912</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.009011606001879655</v>
+        <v>0.008450576145094158</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.8067049225180842</v>
+        <v>0.8587792381770776</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001173345039910578</v>
+        <v>0.0001002916210320744</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7567,25 +7567,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4256809874704212</v>
+        <v>0.3818260119870678</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3705203685982623</v>
+        <v>0.3806272564507771</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.452681279498788</v>
+        <v>4.412285529802531</v>
       </c>
       <c r="P68" t="n">
-        <v>4.341592065566686</v>
+        <v>4.339675967763494</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.8049131111357513</v>
+        <v>0.850144148681274</v>
       </c>
       <c r="R68" t="n">
-        <v>0.02946429375497725</v>
+        <v>0.02582372253932241</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.4850167914312021</v>
+        <v>0.3405068013847646</v>
       </c>
       <c r="X68" t="n">
-        <v>0.00117357672073808</v>
+        <v>0.00132806738801465</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4747389252301797</v>
+        <v>0.6038380891145212</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07049963336404443</v>
+        <v>0.06122596067672573</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.4663226440179072</v>
+        <v>0.3237094162941404</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003898741778773778</v>
+        <v>0.004388860270192974</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.6887807616993085</v>
+        <v>0.6480917258126857</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.008203606518553111</v>
+        <v>0.008723411199317063</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6970705455301829</v>
+        <v>0.6957599236785921</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01241140337891528</v>
+        <v>0.0124382232892692</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.249383837800332</v>
+        <v>0.392780066212191</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0007699954760900591</v>
+        <v>0.000692551746791683</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7675,25 +7675,25 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1578375667668122</v>
+        <v>0.1011765085600368</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2142730074772703</v>
+        <v>0.1771833945991779</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.342039872316217</v>
+        <v>4.336669816495358</v>
       </c>
       <c r="P69" t="n">
-        <v>4.303413304182833</v>
+        <v>4.293816703300208</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.973466531904749</v>
+        <v>0.9723700197053096</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009546926213408365</v>
+        <v>0.00974219558485041</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9649308018052815</v>
+        <v>0.9662528374517387</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01037470226615612</v>
+        <v>0.01017727139120128</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.458396391489205</v>
+        <v>0.4256171120647994</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.004673542140826365</v>
+        <v>0.004812892205250306</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8640858595624259</v>
+        <v>0.8563731327617941</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01492885483844594</v>
+        <v>0.01534659449124235</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9076361642234667</v>
+        <v>0.8977165977517902</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009221236553957691</v>
+        <v>0.009703776059976778</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5180123767864011</v>
+        <v>0.5235518753573127</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004282598159577627</v>
+        <v>0.004257917027968281</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7779,25 +7779,25 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548404427189273</v>
+        <v>0.09853776886812335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2798005208792019</v>
+        <v>0.2509557916829193</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.394470536415335</v>
+        <v>4.406147207166384</v>
       </c>
       <c r="P70" t="n">
-        <v>4.362379885776532</v>
+        <v>4.351469129086955</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.965987268471406</v>
+        <v>0.9657806898956811</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009050518857660008</v>
+        <v>0.009077961714299646</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.9105946226162333</v>
+        <v>0.9199835835155253</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01335122210202667</v>
+        <v>0.01263073865750221</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9219389840196544</v>
+        <v>0.9217559607563544</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003240914039709335</v>
+        <v>0.003244711168008335</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9627215048588192</v>
+        <v>0.9541645992777731</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.008767193713566931</v>
+        <v>0.009721469817497557</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8229355510279825</v>
+        <v>0.8181221774585553</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01178566153984561</v>
+        <v>0.01194477991049761</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7529163503012019</v>
+        <v>0.764536528087583</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002243947189856084</v>
+        <v>0.00219054612158454</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7883,25 +7883,25 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259506110927289</v>
+        <v>0.2686805224204179</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3486347098873965</v>
+        <v>0.3297962845322103</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.436154054572222</v>
+        <v>4.434548768386005</v>
       </c>
       <c r="P71" t="n">
-        <v>4.440396206872959</v>
+        <v>4.434211644840024</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9607948920053613</v>
+        <v>0.9609546735475067</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01081126529064855</v>
+        <v>0.01078921198759127</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9432467069920062</v>
+        <v>0.9441063864742447</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01417833387835802</v>
+        <v>0.01407053984044895</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7407857206215123</v>
+        <v>0.7367902280790937</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004509935243005926</v>
+        <v>0.004544560082242368</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9024282342438994</v>
+        <v>0.9119903640483601</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009962459724770861</v>
+        <v>0.009461709465718737</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8435488309205408</v>
+        <v>0.8377375913220934</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01621164397155933</v>
+        <v>0.01650998240497623</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9354870836204331</v>
+        <v>0.914895187568743</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009922773973696391</v>
+        <v>0.001139690219685772</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -7987,25 +7987,25 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3237573962818418</v>
+        <v>0.2657819781201773</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4159121970215693</v>
+        <v>0.3859035770342941</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.514536388254673</v>
+        <v>4.534002379268917</v>
       </c>
       <c r="P72" t="n">
-        <v>4.505731237331502</v>
+        <v>4.499376278439726</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9584956209223118</v>
+        <v>0.9568340883953047</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01163393906122562</v>
+        <v>0.01186452300052458</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8706524050963869</v>
+        <v>0.8758639166168503</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01502090190897186</v>
+        <v>0.01471518920374563</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.8083387442247059</v>
+        <v>0.7990727877130628</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004822252502559896</v>
+        <v>0.004937443760387808</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9535455239329719</v>
+        <v>0.9546346828963432</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006754353341282688</v>
+        <v>0.006674703350368066</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8567071382991861</v>
+        <v>0.8431211361650002</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.01949923937294363</v>
+        <v>0.02040269843360602</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9028636026677657</v>
+        <v>0.8991037925144849</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001421074192962858</v>
+        <v>0.001448315494902864</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8091,25 +8091,25 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08006297265283152</v>
+        <v>0.04025470310716591</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08137571817139509</v>
+        <v>0.05542117802268435</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.341883758983041</v>
+        <v>4.333373537311013</v>
       </c>
       <c r="P73" t="n">
-        <v>4.328693886773427</v>
+        <v>4.324640731115323</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9939987049766698</v>
+        <v>0.9937193844994046</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005151985406082198</v>
+        <v>0.005270517247422762</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9490814218129882</v>
+        <v>0.9485109185939504</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007747658999801856</v>
+        <v>0.007790941361724895</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.6117652657776269</v>
+        <v>0.6027109001381328</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001245555888451064</v>
+        <v>0.001259996533246099</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9649111723746878</v>
+        <v>0.9608021383216085</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.006284897670915332</v>
+        <v>0.006642705055605563</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8256670362030982</v>
+        <v>0.8207553972729323</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005105101308953068</v>
+        <v>0.005176517095687594</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>-0.07106758937209445</v>
+        <v>-0.091893121412705</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002361173556815051</v>
+        <v>0.002384018039688969</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8195,25 +8195,25 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08447647533141782</v>
+        <v>0.04323964746410821</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1658804054347571</v>
+        <v>0.1274458247866428</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.39908900615176</v>
+        <v>4.405756290037518</v>
       </c>
       <c r="P74" t="n">
-        <v>4.387802555380378</v>
+        <v>4.379712337778502</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9727065298452893</v>
+        <v>0.9726461780845732</v>
       </c>
       <c r="R74" t="n">
-        <v>0.007826088519988738</v>
+        <v>0.00783473632799332</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.8506090202983611</v>
+        <v>0.8723670845858802</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.009234324034623946</v>
+        <v>0.008535407643795696</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8619261917317049</v>
+        <v>0.8584673660464516</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001234818403252835</v>
+        <v>0.001250189180903526</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.89799882772458</v>
+        <v>0.8904970138345185</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01257587552172969</v>
+        <v>0.01303012642947772</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8601894009539437</v>
+        <v>0.8567224801864809</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007560234051106085</v>
+        <v>0.007653396609706793</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.703507128170933</v>
+        <v>0.702816039256052</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.002032487811158591</v>
+        <v>0.002034855173822414</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8299,25 +8299,25 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.207879713293752</v>
+        <v>0.1486427815751791</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2635591019267816</v>
+        <v>0.2370916170858763</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.205773976883957</v>
+        <v>4.1963263632822</v>
       </c>
       <c r="P75" t="n">
-        <v>4.285134295724109</v>
+        <v>4.272932627071964</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9700352220929257</v>
+        <v>0.9697173268663822</v>
       </c>
       <c r="R75" t="n">
-        <v>0.006836281025551389</v>
+        <v>0.006872448280910571</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8952312768612467</v>
+        <v>0.896371979642713</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01156611815438031</v>
+        <v>0.01150298093888978</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8435216367826263</v>
+        <v>0.8261306726317332</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002386865501858177</v>
+        <v>0.00251600956130023</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9316537784967639</v>
+        <v>0.9255611263427016</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.006861349718007638</v>
+        <v>0.007160645872290858</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8718459282597438</v>
+        <v>0.8741274049922191</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006790499346298951</v>
+        <v>0.006729783621730512</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9732191547832254</v>
+        <v>0.9751621987414116</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.001006217616439601</v>
+        <v>0.0009690280554602878</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8403,25 +8403,25 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053128902279143</v>
+        <v>0.006369178025073023</v>
       </c>
       <c r="L76" t="n">
-        <v>0.0250756029909988</v>
+        <v>0.01259155464968998</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.358945393733942</v>
+        <v>4.366980938685304</v>
       </c>
       <c r="P76" t="n">
-        <v>4.318133971111876</v>
+        <v>4.315888310047732</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9931292052762066</v>
+        <v>0.9931999035966245</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005201321881827598</v>
+        <v>0.00517449270283785</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9362500312685267</v>
+        <v>0.9422554291902928</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.007183577508202707</v>
+        <v>0.006836855053352809</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.8852010893653117</v>
+        <v>0.8902913330828138</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0009341454155121317</v>
+        <v>0.0009132003563093025</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9547729376552964</v>
+        <v>0.9528115573660599</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008977589323897476</v>
+        <v>0.009170190705087324</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9887546082770504</v>
+        <v>0.9886575446726396</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0008912618170783924</v>
+        <v>0.0008950999771133029</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.568544772413443</v>
+        <v>0.5667353952839325</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001183585832576119</v>
+        <v>0.001186065011115881</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8507,25 +8507,25 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03789390692492493</v>
+        <v>0.01471419240858703</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08293632886498861</v>
+        <v>0.0488212880141077</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.275909837651753</v>
+        <v>4.278059968673261</v>
       </c>
       <c r="P77" t="n">
-        <v>4.243293106379868</v>
+        <v>4.23828495687153</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9728371946158348</v>
+        <v>0.9692699449780862</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009883149324401437</v>
+        <v>0.01051210560460476</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.5403022448950849</v>
+        <v>0.4553818783772714</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.01235283065536421</v>
+        <v>0.01344548090973197</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-0.6297403391754275</v>
+        <v>-0.5832811292205164</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.00124843063454326</v>
+        <v>0.001230507392512299</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9210674752498865</v>
+        <v>0.9027644922647839</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01217914913857419</v>
+        <v>0.01351765613954515</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1692933316843996</v>
+        <v>0.1621997641485069</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01361096832113987</v>
+        <v>0.0136689581830279</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8749901634310162</v>
+        <v>0.8716404885131864</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0008012903431373562</v>
+        <v>0.0008119547761249507</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8611,25 +8611,25 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02722131315634268</v>
+        <v>0.009270839155371313</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07764629252821463</v>
+        <v>0.04556172815359773</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.411801604657093</v>
+        <v>4.408817932135783</v>
       </c>
       <c r="P78" t="n">
-        <v>4.3775281730888</v>
+        <v>4.362432991648956</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9790410756732091</v>
+        <v>0.9767966556308738</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01051275169436136</v>
+        <v>0.01106132632374648</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.1225301556099971</v>
+        <v>0.0197310722319366</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.01135571208248658</v>
+        <v>0.01200247724435576</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.7096709745839889</v>
+        <v>0.04211667085445869</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.0006302489600751789</v>
+        <v>0.001144783120083672</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8348689263672254</v>
+        <v>0.8096227107736678</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01671127413344865</v>
+        <v>0.01794331704929406</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.2437225258503379</v>
+        <v>-0.2434742649665742</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01174896745641607</v>
+        <v>0.01174779484445083</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-1.722751445451205</v>
+        <v>-1.945690003028069</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.002436269859700756</v>
+        <v>0.002534048415073153</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8709,31 +8709,31 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.291298707758667</v>
+        <v>0.2303690117158935</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3304035059681816</v>
+        <v>0.2922512004012426</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.395075630781815</v>
+        <v>4.373390288550217</v>
       </c>
       <c r="P79" t="n">
-        <v>4.439066110577246</v>
+        <v>4.375242757853916</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9810896195208271</v>
+        <v>0.9808907815267717</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02022836194988157</v>
+        <v>0.02033443197628049</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9173823247709172</v>
+        <v>0.9163598831413424</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04464535478460659</v>
+        <v>0.04492076140010511</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.3691180979314987</v>
+        <v>0.3157445816382826</v>
       </c>
       <c r="X79" t="n">
-        <v>0.00223543930990148</v>
+        <v>0.002328080384607792</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9955889158578903</v>
+        <v>0.9976432624425374</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.005190526931061067</v>
+        <v>0.003793974338787635</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.5906689916039923</v>
+        <v>0.5309433655666522</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.0048355634456624</v>
+        <v>0.005176335353715041</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9850466385376752</v>
+        <v>0.9910869176209304</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.00392341162287957</v>
+        <v>0.003029063788607225</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8652278378842142</v>
+        <v>0.84848294102597</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.009810176261362718</v>
+        <v>0.01040177554415342</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8817,31 +8817,31 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1623021847871931</v>
+        <v>0.1039261725912166</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2458325049296386</v>
+        <v>0.2174564914215158</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.51750010072576</v>
+        <v>4.528963221921294</v>
       </c>
       <c r="P80" t="n">
-        <v>4.474103812650267</v>
+        <v>4.424729193308102</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9937421742225868</v>
+        <v>0.9946325656416439</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01093382183032316</v>
+        <v>0.01012613305600414</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9791557110882316</v>
+        <v>0.9822787328478095</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02292650890581743</v>
+        <v>0.02113935697584573</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.7965904666481212</v>
+        <v>0.775825729595033</v>
       </c>
       <c r="X80" t="n">
-        <v>0.001206420214992126</v>
+        <v>0.001266501873173817</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9983500140171362</v>
+        <v>0.9992277168480969</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.002607957713187918</v>
+        <v>0.001784221208935005</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.8223784533859008</v>
+        <v>0.8016301743872633</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.003506633486720634</v>
+        <v>0.003705786184713432</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9764504627317075</v>
+        <v>0.9841639170237896</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.008139651575354715</v>
+        <v>0.006674803903250156</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.969382218542139</v>
+        <v>0.9585997926081051</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.005732609682370402</v>
+        <v>0.00666602244157188</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8925,87 +8925,87 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.281196440943406</v>
+        <v>0.2166350389501655</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2614933935880142</v>
+        <v>0.237244827662883</v>
       </c>
       <c r="M81" t="n">
-        <v>0.005183724718742067</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0001036744943748413</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.547853617806929</v>
+        <v>4.522784247933544</v>
       </c>
       <c r="P81" t="n">
-        <v>4.585223414227971</v>
+        <v>4.545004841620153</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9915070434125417</v>
+        <v>0.9924686950891002</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01252407980522361</v>
+        <v>0.01179373838038089</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9755491937755753</v>
+        <v>0.9780906020423523</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02343333266215862</v>
+        <v>0.02218210148416111</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9789298012528225</v>
+        <v>0.9856585831245859</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009566661091336063</v>
+        <v>0.007892636524348936</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.7594040422916682</v>
+        <v>0.7150037744037052</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.002978510949065003</v>
+        <v>0.003241713218457269</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9579940932269724</v>
+        <v>0.9555727072063726</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.006575337073305629</v>
+        <v>0.006762196152289902</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9611088731917771</v>
+        <v>0.9639256919131974</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009566305746989707</v>
+        <v>0.00921335910363166</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9029,87 +9029,87 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2355470167542912</v>
+        <v>0.1707707294026821</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1488024249767209</v>
+        <v>0.1534844868966426</v>
       </c>
       <c r="M82" t="n">
-        <v>0.1740023896155605</v>
+        <v>0.260231725092805</v>
       </c>
       <c r="N82" t="n">
-        <v>0.008462144799708044</v>
+        <v>0.01279781486373742</v>
       </c>
       <c r="O82" t="n">
-        <v>4.463853060787375</v>
+        <v>4.419990824310435</v>
       </c>
       <c r="P82" t="n">
-        <v>4.585312245728836</v>
+        <v>4.603449453659397</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9684451220406297</v>
+        <v>0.9752231633788621</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02396284150736804</v>
+        <v>0.02123381315114793</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9128186336580602</v>
+        <v>0.9327913894947402</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04609860470264915</v>
+        <v>0.04047514407006057</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9473579185218206</v>
+        <v>0.9659391238217472</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01536275753884477</v>
+        <v>0.01235749825593458</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>0.3239863661843387</v>
+        <v>0.4024204494975525</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.002413137069901971</v>
+        <v>0.002268830895066713</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.6782834484682327</v>
+        <v>0.7005787097969773</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.02040593406829236</v>
+        <v>0.01968616472536993</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9685626653524042</v>
+        <v>0.9746631130178618</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.009368447848503682</v>
+        <v>0.008410492186960265</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9133,29 +9133,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.189934792401037</v>
+        <v>0.1273374851235748</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1826267284946377</v>
+        <v>0.1574197316565873</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.578578953049799</v>
+        <v>4.56844405665582</v>
       </c>
       <c r="P83" t="n">
-        <v>4.571960649035538</v>
+        <v>4.569037027833398</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.975739278735116</v>
+        <v>0.9751081141222492</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01864810179250103</v>
+        <v>0.01888911790275169</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9247478164506443</v>
+        <v>0.9222373462486447</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03555231950112275</v>
+        <v>0.03614048060730951</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9595067108214487</v>
+        <v>0.9581677611297498</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.009703482150566864</v>
+        <v>0.009862604937353268</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.2721584302524647</v>
+        <v>0.2494938805516836</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.009535197718484453</v>
+        <v>0.00968252006466992</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.92071581695676</v>
+        <v>0.9210452685771884</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01080899162941539</v>
+        <v>0.01078651076869192</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8756106397787032</v>
+        <v>0.8773307600014617</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01314835423107227</v>
+        <v>0.01305712647088978</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9235,29 +9235,29 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.171344845273151</v>
+        <v>0.08008330526260318</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3144608188889046</v>
+        <v>0.2339625120726014</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.585710978228106</v>
+        <v>3.382055805903954</v>
       </c>
       <c r="P84" t="n">
-        <v>4.51504935164796</v>
+        <v>4.437642616238247</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9903344577308121</v>
+        <v>0.9893889808462896</v>
       </c>
       <c r="R84" t="n">
-        <v>0.01154526369606604</v>
+        <v>0.01209676640713226</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9873913956404577</v>
+        <v>0.9818384689355362</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01501815830575804</v>
+        <v>0.01802434112438521</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9933130550836702</v>
+        <v>0.9903913707915402</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.005578859917414843</v>
+        <v>0.006687477007709755</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.5270393210160504</v>
+        <v>0.1560998600167813</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.006226371265389735</v>
+        <v>0.008317026411614874</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.7830435084276691</v>
+        <v>0.8289018488084052</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.01919678194774724</v>
+        <v>0.01704765970182989</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9975782452931089</v>
+        <v>0.9978179844197249</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.0015851422332806</v>
+        <v>0.0015046382308956</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9337,29 +9337,31 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2347111018878213</v>
+        <v>0.232649974815383</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2950582658013271</v>
+        <v>0.250511276483206</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9370,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.499856930037251</v>
+        <v>4.312526024436617</v>
       </c>
       <c r="P85" t="n">
-        <v>4.494335338061362</v>
+        <v>4.386010107012114</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9804738895804873</v>
+        <v>0.9919833692155775</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01746361459638317</v>
+        <v>0.01132669231564241</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9535757123586837</v>
+        <v>0.9741551929558522</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02766144752124787</v>
+        <v>0.02268930815332858</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9918666485371912</v>
+        <v>0.9943428358976947</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.006949897789780429</v>
+        <v>0.00611754595124686</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>-0.08764342376728562</v>
+        <v>0.4911778107117194</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.01629711392139493</v>
+        <v>0.005681289089860726</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.572784553447327</v>
+        <v>0.9649199472882828</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.02111067502000964</v>
+        <v>0.005759909587219552</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9997841094756301</v>
+        <v>0.9635814892915352</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.0004193967435592211</v>
+        <v>0.004877203804264377</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9439,29 +9441,31 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1247724149338163</v>
+        <v>0.1063207427095769</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1593436216466051</v>
+        <v>0.1880447549481098</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9474,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.570462719990509</v>
+        <v>4.515115790775487</v>
       </c>
       <c r="P86" t="n">
-        <v>4.515742961794027</v>
+        <v>4.437239690074709</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9903940418722199</v>
+        <v>0.9925981720188748</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01168937498319476</v>
+        <v>0.0107009497129165</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9850744497473672</v>
+        <v>0.9812567749842462</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01698183892126025</v>
+        <v>0.02129180191579711</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9963065060987834</v>
+        <v>0.9984018985385641</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003535138875647679</v>
+        <v>0.002542298956410744</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>-0.3773211717237219</v>
+        <v>0.7217579806729524</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.01756688986452823</v>
+        <v>0.004433773488736337</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9812247563569276</v>
+        <v>0.9713078457630941</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.007005455428793422</v>
+        <v>0.008855102484899964</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9766567408923517</v>
+        <v>0.9864908326718069</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004965415611374016</v>
+        <v>0.003830969018280812</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9541,85 +9545,87 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836932525307708</v>
+        <v>0.1610958338338375</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3212089024650849</v>
+        <v>0.1448216016129386</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>0.1223045557522026</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>0.002856342167409669</v>
       </c>
       <c r="O87" t="n">
-        <v>4.671001137082393</v>
+        <v>4.405149236767546</v>
       </c>
       <c r="P87" t="n">
-        <v>4.625012894559749</v>
+        <v>4.601956009721136</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9528373348785328</v>
+        <v>0.9735442403167598</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02434600038411214</v>
+        <v>0.02175105143675758</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9101216501858823</v>
+        <v>0.9380158558398716</v>
       </c>
       <c r="U87" t="n">
-        <v>0.0388729705995589</v>
+        <v>0.0410668870056478</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8400135795326471</v>
+        <v>0.9696934534635518</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.02235533897543889</v>
+        <v>0.0119412578726084</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.7703664535196264</v>
+        <v>0.6369181625685918</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.005617000820560498</v>
+        <v>0.002357276758445043</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.3036929249166189</v>
+        <v>0.7201232876085817</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.02948283276357546</v>
+        <v>0.02114066741537441</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9794633256672065</v>
+        <v>0.9718313777269071</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.007209821328705651</v>
+        <v>0.009163720457555187</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9643,85 +9649,87 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2269187336146035</v>
+        <v>0.2250426157877557</v>
       </c>
       <c r="L88" t="n">
-        <v>0.161092772703215</v>
+        <v>0.2455647430807811</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>0.1281526446851361</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>0.005220805678624416</v>
       </c>
       <c r="O88" t="n">
-        <v>4.508038569021577</v>
+        <v>4.524622090472267</v>
       </c>
       <c r="P88" t="n">
-        <v>4.616014896168517</v>
+        <v>4.546103447712063</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9911677522753494</v>
+        <v>0.9900355419419342</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01101857129381207</v>
+        <v>0.01342976129890124</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9747456996005284</v>
+        <v>0.9729569051725564</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02002917169113984</v>
+        <v>0.02555136961047557</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9859123750878857</v>
+        <v>0.9820054653145825</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.006715563222680828</v>
+        <v>0.009124981345775987</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.5661360560631665</v>
+        <v>0.8198786157694252</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.004108756738976216</v>
+        <v>0.002601277412069926</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9549355258833319</v>
+        <v>0.9528350395858618</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.006327415812534392</v>
+        <v>0.007104804862773954</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9499380395057382</v>
+        <v>0.9578592347489734</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01019117196147346</v>
+        <v>0.01041200138699526</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9745,85 +9753,85 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3488188784207902</v>
+        <v>0.288273972655646</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3411761504532672</v>
+        <v>0.2786754448391243</v>
       </c>
       <c r="M89" t="n">
-        <v>0.04057975262183888</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0.0008115950524367776</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.501604676162365</v>
+        <v>4.432624839498226</v>
       </c>
       <c r="P89" t="n">
-        <v>4.601841240036634</v>
+        <v>4.569431898943232</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9957349728921592</v>
+        <v>0.9943210498084879</v>
       </c>
       <c r="R89" t="n">
-        <v>0.007728440403138749</v>
+        <v>0.008917949208094489</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9944766261694264</v>
+        <v>0.9889930706442677</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01015651458759061</v>
+        <v>0.01433757052632945</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9956230963153566</v>
+        <v>0.998788711450207</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.005041758082311287</v>
+        <v>0.002652297978809652</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.7664862038334285</v>
+        <v>0.6272530919138146</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.004683077138536186</v>
+        <v>0.005916733708474843</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9539081176324975</v>
+        <v>0.9669916136853502</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.005216075606604636</v>
+        <v>0.004414116629007492</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9416031832680545</v>
+        <v>0.9369552771399985</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01099687164499745</v>
+        <v>0.01142612418247824</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9849,83 +9857,87 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5583518477656447</v>
+        <v>0.5704623921017763</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5219359551048091</v>
+        <v>0.5276839381766966</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6485924380199451</v>
+        <v>0.2154800172188763</v>
       </c>
       <c r="N90" t="n">
-        <v>0.1245034669297462</v>
+        <v>0.0110094962370653</v>
       </c>
       <c r="O90" t="n">
-        <v>4.519091781875822</v>
+        <v>4.52559509792863</v>
       </c>
       <c r="P90" t="n">
-        <v>4.27504208100537</v>
+        <v>4.293620750820976</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9895720182869033</v>
+        <v>0.9838315563476747</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01350330005250666</v>
+        <v>0.01509710077755905</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9805878235629527</v>
+        <v>0.9644110614838658</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02256435905850731</v>
+        <v>0.02747504475512449</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5.204170427930421e-18</v>
+      </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9880291793120841</v>
+        <v>0.9891917953139684</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01413406304948875</v>
+        <v>0.01129768647507088</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8292730326799973</v>
+        <v>0.8622797792821821</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004707581940714791</v>
+        <v>0.005770199896903018</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9946266928499801</v>
+        <v>0.9576314894709501</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005583300049998928</v>
+        <v>0.0006795423774626261</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9842748942254244</v>
+        <v>0.9821947515384316</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.004110336932945308</v>
+        <v>0.004103933177888492</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
